--- a/Khmer_Food_And_Shops_List.xlsx
+++ b/Khmer_Food_And_Shops_List.xlsx
@@ -4,8 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Top 100 Foods (ម្ហូប១០០មុខ)" sheetId="1" r:id="rId1"/>
-    <sheet name="All 235 Foods (ម្ហូបទាំងអស់)" sheetId="2" r:id="rId2"/>
+    <sheet name="All 230 Foods (ម្ហូបទាំងអស់)" sheetId="2" r:id="rId2"/>
     <sheet name="All 215 Shops (ហាងទាំងអស់)" sheetId="3" r:id="rId3"/>
+    <sheet name="119 Destinations (ទេសចរណ៍)" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -400,6 +401,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G101"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2734,6 +2744,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G229"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8011,7 +8030,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:J216"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="55.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8024,18 +8055,24 @@
         <v>ឈ្មោះហាងខ្មែរ (Khmer Shop Name)</v>
       </c>
       <c r="D1" t="str">
-        <v>ឈ្មោះអង់គ្លេស (English Name)</v>
+        <v>ឈ្មោះហាងអង់គ្លេស (English Shop Name)</v>
       </c>
       <c r="E1" t="str">
-        <v>ខេត្ត/រាជធានី (Province)</v>
+        <v>ខេត្ត/រាជធានីខ្មែរ (Khmer Province)</v>
       </c>
       <c r="F1" t="str">
+        <v>ខេត្ត/រាជធានីអង់គ្លេស (English Province)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>អាសយដ្ឋានខ្មែរ (Khmer Address)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>អាសយដ្ឋានអង់គ្លេស (English Address)</v>
+      </c>
+      <c r="I1" t="str">
         <v>កម្រិតតម្លៃ (Price Level)</v>
       </c>
-      <c r="G1" t="str">
-        <v>អាសយដ្ឋាន (Address)</v>
-      </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>លេខទូរស័ព្ទ (Phone)</v>
       </c>
     </row>
@@ -8047,7 +8084,7 @@
         <v>rest-1</v>
       </c>
       <c r="C2" t="str">
-        <v>ភោជនីយដ្ឋាន ម្លិះ (Malis Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន ម្លិះ</v>
       </c>
       <c r="D2" t="str">
         <v>Malis Restaurant Phnom Penh</v>
@@ -8056,12 +8093,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F2" t="str">
-        <v>$$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G2" t="str">
         <v>ផ្ទះលេខ ១៣៦ មហាវិថីព្រះនរោត្តម សង្កាត់ទន្លេបាសាក់ ខណ្ឌចំការមន</v>
       </c>
       <c r="H2" t="str">
+        <v>No. 136 Norodom Blvd, Sangkat Tonle Bassac, Khan Chamkarmon, Phnom Penh</v>
+      </c>
+      <c r="I2" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J2" t="str">
         <v>015 814 888</v>
       </c>
     </row>
@@ -8073,7 +8116,7 @@
         <v>rest-2</v>
       </c>
       <c r="C3" t="str">
-        <v>ភោជនីយដ្ឋាន រំដេង (Romdeng Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន រំដេង</v>
       </c>
       <c r="D3" t="str">
         <v>Romdeng Restaurant Phnom Penh</v>
@@ -8082,12 +8125,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F3" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G3" t="str">
         <v>ផ្ទះលេខ ៧៤ ផ្លូវ ១៧៤ សង្កាត់ផ្សារថ្មី ៣ ខណ្ឌដូនពេញ</v>
       </c>
       <c r="H3" t="str">
+        <v>No. 74 Street 174, Sangkat Phsar Thmey 3, Khan Daun Penh, Phnom Penh</v>
+      </c>
+      <c r="I3" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J3" t="str">
         <v>092 219 509</v>
       </c>
     </row>
@@ -8099,7 +8148,7 @@
         <v>rest-3</v>
       </c>
       <c r="C4" t="str">
-        <v>ភោជនីយដ្ឋាន អេឡឹវិន វ័ន ឃីតឆិន (Eleven One Kitchen)</v>
+        <v>ភោជនីយដ្ឋាន អេឡឹវិន វ័ន ឃីតឆិន</v>
       </c>
       <c r="D4" t="str">
         <v>Eleven One Kitchen BKK1</v>
@@ -8108,12 +8157,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F4" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G4" t="str">
         <v>ផ្ទះលេខ ៣៧ ផ្លូវ ៣៣៤ សង្កាត់បឹងកេងកង ១</v>
       </c>
       <c r="H4" t="str">
+        <v>No. 37 Street 334, BKK1, Khan Boeng Keng Kang, Phnom Penh</v>
+      </c>
+      <c r="I4" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J4" t="str">
         <v>086 516 111</v>
       </c>
     </row>
@@ -8125,7 +8180,7 @@
         <v>rest-4</v>
       </c>
       <c r="C5" t="str">
-        <v>ភោជនីយដ្ឋាន ក្រវាញ (Kravanh Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន ក្រវាញ</v>
       </c>
       <c r="D5" t="str">
         <v>Kravanh Authentic Khmer Restaurant</v>
@@ -8134,12 +8189,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F5" t="str">
-        <v>$$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G5" t="str">
         <v>ផ្ទះលេខ ១១២ ផ្លូវព្រះសុធារស សង្កាត់ជ័យជំនះ</v>
       </c>
       <c r="H5" t="str">
+        <v>No. 112 Sothearos Blvd, Sangkat Chey Chumneah, Phnom Penh</v>
+      </c>
+      <c r="I5" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J5" t="str">
         <v>012 841 846</v>
       </c>
     </row>
@@ -8151,7 +8212,7 @@
         <v>rest-5</v>
       </c>
       <c r="C6" t="str">
-        <v>ភោជនីយដ្ឋាន ខ្មែរសុរិន្ទ (Khmer Surin Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន ខ្មែរសុរិន្ទ</v>
       </c>
       <c r="D6" t="str">
         <v>Khmer Surin Restaurant BKK1</v>
@@ -8160,12 +8221,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F6" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G6" t="str">
         <v>ផ្ទះលេខ ៩ ផ្លូវ ៥៧ សង្កាត់បឹងកេងកង ១</v>
       </c>
       <c r="H6" t="str">
+        <v>No. 9 Street 57, BKK1, Phnom Penh</v>
+      </c>
+      <c r="I6" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J6" t="str">
         <v>012 888 560</v>
       </c>
     </row>
@@ -8177,7 +8244,7 @@
         <v>rest-6</v>
       </c>
       <c r="C7" t="str">
-        <v>ភោជនីយដ្ឋាន សុវណ្ណា សាច់អាំង (Sovanna BBQ)</v>
+        <v>ភោជនីយដ្ឋាន សុវណ្ណា សាច់អាំង</v>
       </c>
       <c r="D7" t="str">
         <v>Sovanna Restaurant &amp; BBQ Phnom Penh</v>
@@ -8186,12 +8253,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F7" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G7" t="str">
         <v>ផ្លូវ ២១ សង្កាត់ទន្លេបាសាក់ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H7" t="str">
+        <v>Street 21, Sangkat Tonle Bassac, Phnom Penh</v>
+      </c>
+      <c r="I7" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J7" t="str">
         <v>012 840 055</v>
       </c>
     </row>
@@ -8203,7 +8276,7 @@
         <v>rest-7</v>
       </c>
       <c r="C8" t="str">
-        <v>ភោជនីយដ្ឋាន វ័ន ម៉រ (One More Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន វ័ន ម៉រ</v>
       </c>
       <c r="D8" t="str">
         <v>One More Restaurant Toul Kork</v>
@@ -8212,12 +8285,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F8" t="str">
-        <v>$$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G8" t="str">
         <v>ផ្លូវ ៣១៥ សង្កាត់បឹងកក់ ១ ខណ្ឌទួលគោក</v>
       </c>
       <c r="H8" t="str">
+        <v>Street 315, Boeng Kak 1, Toul Kork, Phnom Penh</v>
+      </c>
+      <c r="I8" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J8" t="str">
         <v>023 888 222</v>
       </c>
     </row>
@@ -8229,7 +8308,7 @@
         <v>rest-8</v>
       </c>
       <c r="C9" t="str">
-        <v>ភោជនីយដ្ឋាន មុខមុនី (Mok Mony)</v>
+        <v>ភោជនីយដ្ឋាន មុខមុនី</v>
       </c>
       <c r="D9" t="str">
         <v>Mok Mony Restaurant Phnom Penh</v>
@@ -8238,12 +8317,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F9" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G9" t="str">
         <v>ផ្ទះលេខ ៦៣ ផ្លូវ ២៩ សង្កាត់ទន្លេបាសាក់</v>
       </c>
       <c r="H9" t="str">
+        <v>No. 63 Street 29, Tonle Bassac, Phnom Penh</v>
+      </c>
+      <c r="I9" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J9" t="str">
         <v>095 970 888</v>
       </c>
     </row>
@@ -8255,7 +8340,7 @@
         <v>rest-9</v>
       </c>
       <c r="C10" t="str">
-        <v>ភោជនីយដ្ឋាន ហ្វ្រេន ដឹ រេស្ត៊ូរ៉ង់ (Friends the Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន ហ្វ្រេន ដឹ រេស្ត៊ូរ៉ង់</v>
       </c>
       <c r="D10" t="str">
         <v>Friends the Restaurant Phnom Penh</v>
@@ -8264,12 +8349,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F10" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G10" t="str">
         <v>ផ្ទះលេខ ២១៥ ផ្លូវលេខ ១៣ សង្កាត់ជ័យជំនះ</v>
       </c>
       <c r="H10" t="str">
+        <v>No. 215 Street 13, near National Museum, Phnom Penh</v>
+      </c>
+      <c r="I10" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J10" t="str">
         <v>012 802 072</v>
       </c>
     </row>
@@ -8281,7 +8372,7 @@
         <v>rest-10</v>
       </c>
       <c r="C11" t="str">
-        <v>ភោជនីយដ្ឋាន បុប្ផាភ្នំពេញ ទីតានិច (Bopha Phnom Penh Titanic)</v>
+        <v>ភោជនីយដ្ឋាន បុប្ផាភ្នំពេញ ទីតានិច</v>
       </c>
       <c r="D11" t="str">
         <v>Bopha Phnom Penh Titanic Riverside</v>
@@ -8290,12 +8381,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F11" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G11" t="str">
         <v>វិថីព្រះស៊ីសុវត្ថិ សង្កាត់ផ្សារចាស់ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H11" t="str">
+        <v>Sisowath Quay, riverside, Phnom Penh</v>
+      </c>
+      <c r="I11" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J11" t="str">
         <v>023 427 209</v>
       </c>
     </row>
@@ -8307,7 +8404,7 @@
         <v>rest-11</v>
       </c>
       <c r="C12" t="str">
-        <v>ហាងអាហារ ស្ករត្នោត (The Sugar Palm Siem Reap)</v>
+        <v>ហាងអាហារ ស្ករត្នោត</v>
       </c>
       <c r="D12" t="str">
         <v>The Sugar Palm Siem Reap</v>
@@ -8316,12 +8413,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F12" t="str">
-        <v>$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G12" t="str">
         <v>ផ្លូវតាវ៉ាន់ ភូមិវត្តបូព៌ ក្រុងសៀមរាប</v>
       </c>
       <c r="H12" t="str">
+        <v>Taphul Village / Wat Bo area, Siem Reap, Cambodia</v>
+      </c>
+      <c r="I12" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J12" t="str">
         <v>063 964 838</v>
       </c>
     </row>
@@ -8333,7 +8436,7 @@
         <v>rest-12</v>
       </c>
       <c r="C13" t="str">
-        <v>ភោជនីយដ្ឋាន ចន្ទ្រា (Chanrey Tree)</v>
+        <v>ភោជនីយដ្ឋាន ចន្ទ្រា</v>
       </c>
       <c r="D13" t="str">
         <v>Chanrey Tree Riverside Siem Reap</v>
@@ -8342,12 +8445,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F13" t="str">
-        <v>$$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G13" t="str">
         <v>ផ្លូវមាត់ស្ទឹងពោធិ៍ ក្រុងសៀមរាប</v>
       </c>
       <c r="H13" t="str">
+        <v>Pokambor Avenue, Riverside, Siem Reap</v>
+      </c>
+      <c r="I13" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J13" t="str">
         <v>063 967 997</v>
       </c>
     </row>
@@ -8359,7 +8468,7 @@
         <v>rest-13</v>
       </c>
       <c r="C14" t="str">
-        <v>ភោជនីយដ្ឋាន គ្វីហ្ស៊ីន វត្តដំណាក់ (Cuisine Wat Damnak)</v>
+        <v>ភោជនីយដ្ឋាន គ្វីហ្ស៊ីន វត្តដំណាក់</v>
       </c>
       <c r="D14" t="str">
         <v>Cuisine Wat Damnak Siem Reap</v>
@@ -8368,12 +8477,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F14" t="str">
-        <v>$$$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G14" t="str">
         <v>ភូមិវត្តដំណាក់ ក្រុងសៀមរាប</v>
       </c>
       <c r="H14" t="str">
+        <v>Wat Damnak Village, Siem Reap, Cambodia</v>
+      </c>
+      <c r="I14" t="str">
+        <v>$$$$</v>
+      </c>
+      <c r="J14" t="str">
         <v>077 347 705</v>
       </c>
     </row>
@@ -8385,7 +8500,7 @@
         <v>rest-14</v>
       </c>
       <c r="C15" t="str">
-        <v>ភោជនីយដ្ឋាន ម៉ារ៉ុម (Marum Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន ម៉ារ៉ុម</v>
       </c>
       <c r="D15" t="str">
         <v>Marum Training Restaurant Siem Reap</v>
@@ -8394,12 +8509,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F15" t="str">
-        <v>$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G15" t="str">
         <v>ផ្ទះលេខ ៨A ផ្លូវ ៧ មករា ភូមិវត្តបូព៌ ក្រុងសៀមរាប</v>
       </c>
       <c r="H15" t="str">
+        <v>No. 8A, Phum Slokram, Wat Bo area, Siem Reap</v>
+      </c>
+      <c r="I15" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J15" t="str">
         <v>017 363 284</v>
       </c>
     </row>
@@ -8411,7 +8532,7 @@
         <v>rest-15</v>
       </c>
       <c r="C16" t="str">
-        <v>ភោជនីយដ្ឋាន ហេវិន (Haven Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន ហេវិន</v>
       </c>
       <c r="D16" t="str">
         <v>Haven Restaurant Siem Reap</v>
@@ -8420,12 +8541,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F16" t="str">
-        <v>$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G16" t="str">
         <v>ផ្លូវសូកូឡា ភូមិវត្តបូព៌ ក្រុងសៀមរាប</v>
       </c>
       <c r="H16" t="str">
+        <v>Chocolate Road, Wat Damnak Area, Siem Reap</v>
+      </c>
+      <c r="I16" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J16" t="str">
         <v>078 340 140</v>
       </c>
     </row>
@@ -8437,7 +8564,7 @@
         <v>rest-16</v>
       </c>
       <c r="C17" t="str">
-        <v>ភោជនីយដ្ឋាន វីរោធ (Viroth's Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន វីរោធ</v>
       </c>
       <c r="D17" t="str">
         <v>Viroth's Restaurant Siem Reap</v>
@@ -8446,12 +8573,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F17" t="str">
-        <v>$$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G17" t="str">
         <v>ផ្លូវវត្តបូព៌ ក្រុងសៀមរាប</v>
       </c>
       <c r="H17" t="str">
+        <v>Wat Bo Road, Siem Reap</v>
+      </c>
+      <c r="I17" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J17" t="str">
         <v>012 826 346</v>
       </c>
     </row>
@@ -8463,7 +8596,7 @@
         <v>rest-17</v>
       </c>
       <c r="C18" t="str">
-        <v>ភោជនីយដ្ឋាន ស្ពូនស៍ ខេមបូឌា (Spoons Cambodia)</v>
+        <v>ភោជនីយដ្ឋាន ស្ពូនស៍ ខេមបូឌា</v>
       </c>
       <c r="D18" t="str">
         <v>Spoons Cambodia Training Restaurant</v>
@@ -8472,12 +8605,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F18" t="str">
-        <v>$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G18" t="str">
         <v>ភូមិវត្តបូព៌ ក្រុងសៀមរាប</v>
       </c>
       <c r="H18" t="str">
+        <v>Wat Bo Village, Siem Reap</v>
+      </c>
+      <c r="I18" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J18" t="str">
         <v>076 226 2662</v>
       </c>
     </row>
@@ -8489,7 +8628,7 @@
         <v>rest-18</v>
       </c>
       <c r="C19" t="str">
-        <v>ភោជនីយដ្ឋាន ពោធិ៍ (Pou Restaurant and Bar)</v>
+        <v>ភោជនីយដ្ឋាន ពោធិ៍</v>
       </c>
       <c r="D19" t="str">
         <v>Pou Restaurant and Bar Siem Reap</v>
@@ -8498,12 +8637,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F19" t="str">
-        <v>$$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G19" t="str">
         <v>ផ្លូវវត្តបូព៌ ក្រុងសៀមរាប</v>
       </c>
       <c r="H19" t="str">
+        <v>Wat Bo Road, Siem Reap</v>
+      </c>
+      <c r="I19" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J19" t="str">
         <v>012 368 765</v>
       </c>
     </row>
@@ -8515,7 +8660,7 @@
         <v>rest-19</v>
       </c>
       <c r="C20" t="str">
-        <v>ភោជនីយដ្ឋាន គីមលី គ្រឿងសមុទ្រកែប (Kimly Seafood Kep)</v>
+        <v>ភោជនីយដ្ឋាន គីមលី គ្រឿងសមុទ្រកែប</v>
       </c>
       <c r="D20" t="str">
         <v>Kimly Seafood Restaurant Crab Market Kep</v>
@@ -8524,12 +8669,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F20" t="str">
-        <v>$$</v>
+        <v>Kep</v>
       </c>
       <c r="G20" t="str">
         <v>ផ្សារក្តាមខេត្តកែប ជាប់មាត់សមុទ្រ ក្រុងកែប</v>
       </c>
       <c r="H20" t="str">
+        <v>Crab Market Waterfront, Kep, Cambodia</v>
+      </c>
+      <c r="I20" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J20" t="str">
         <v>012 858 003</v>
       </c>
     </row>
@@ -8541,7 +8692,7 @@
         <v>rest-20</v>
       </c>
       <c r="C21" t="str">
-        <v>ហាង ហូលី ក្រាប កែប (Holy Crab Kep)</v>
+        <v>ហាង ហូលី ក្រាប កែប</v>
       </c>
       <c r="D21" t="str">
         <v>Holy Crab Restaurant Kep</v>
@@ -8550,12 +8701,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F21" t="str">
-        <v>$$</v>
+        <v>Kep</v>
       </c>
       <c r="G21" t="str">
         <v>ផ្សារក្តាមកែប ក្រុងកែប</v>
       </c>
       <c r="H21" t="str">
+        <v>Crab Market Waterfront, Kep City</v>
+      </c>
+      <c r="I21" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J21" t="str">
         <v>097 912 3456</v>
       </c>
     </row>
@@ -8567,7 +8724,7 @@
         <v>rest-21</v>
       </c>
       <c r="C22" t="str">
-        <v>ភោជនីយដ្ឋាន រីឃីធីឃីថាវី កំពត (Rikitikitavi Kampot)</v>
+        <v>ភោជនីយដ្ឋាន រីឃីធីឃីថាវី កំពត</v>
       </c>
       <c r="D22" t="str">
         <v>Rikitikitavi Riverside Kampot</v>
@@ -8576,12 +8733,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F22" t="str">
-        <v>$$</v>
+        <v>Kampot</v>
       </c>
       <c r="G22" t="str">
         <v>ផ្លូវមាត់ព្រែកកំពត ក្រុងកំពត</v>
       </c>
       <c r="H22" t="str">
+        <v>Riverside Road, Kampot City, Cambodia</v>
+      </c>
+      <c r="I22" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J22" t="str">
         <v>012 235 102</v>
       </c>
     </row>
@@ -8593,7 +8756,7 @@
         <v>rest-22</v>
       </c>
       <c r="C23" t="str">
-        <v>អាតេលីយេ កំពត (Atelier Kampot)</v>
+        <v>អាតេលីយេ កំពត</v>
       </c>
       <c r="D23" t="str">
         <v>Atelier Kampot French &amp; Khmer</v>
@@ -8602,12 +8765,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F23" t="str">
-        <v>$$$</v>
+        <v>Kampot</v>
       </c>
       <c r="G23" t="str">
         <v>ផ្លូវមាត់ព្រែក ក្រុងកំពត</v>
       </c>
       <c r="H23" t="str">
+        <v>Riverside Street, Kampot City</v>
+      </c>
+      <c r="I23" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J23" t="str">
         <v>096 339 9888</v>
       </c>
     </row>
@@ -8619,7 +8788,7 @@
         <v>rest-23</v>
       </c>
       <c r="C24" t="str">
-        <v>ភោជនីយដ្ឋាន សេលីងក្លឹប កែប (Sailing Club Kep)</v>
+        <v>ភោជនីយដ្ឋាន សេលីងក្លឹប កែប</v>
       </c>
       <c r="D24" t="str">
         <v>The Sailing Club Kep</v>
@@ -8628,12 +8797,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F24" t="str">
-        <v>$$$</v>
+        <v>Kep</v>
       </c>
       <c r="G24" t="str">
         <v>ឆ្នេរខេត្តកែប ក្រុងកែប</v>
       </c>
       <c r="H24" t="str">
+        <v>Phum Thmey, Sangkat Prey Thom, Kep</v>
+      </c>
+      <c r="I24" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J24" t="str">
         <v>078 888 556</v>
       </c>
     </row>
@@ -8645,7 +8820,7 @@
         <v>rest-24</v>
       </c>
       <c r="C25" t="str">
-        <v>ហាងបាយ ម្លប់ស្វាយ បាត់ដំបង (Mlop Svay)</v>
+        <v>ហាងបាយ ម្លប់ស្វាយ បាត់ដំបង</v>
       </c>
       <c r="D25" t="str">
         <v>Mlop Svay Restaurant Battambang</v>
@@ -8654,12 +8829,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F25" t="str">
-        <v>$</v>
+        <v>Battambang</v>
       </c>
       <c r="G25" t="str">
         <v>ផ្លូវមាត់ស្ទឹងសង្កែ ក្រុងបាត់ដំបង</v>
       </c>
       <c r="H25" t="str">
+        <v>Sangkae River East Bank, Battambang City</v>
+      </c>
+      <c r="I25" t="str">
+        <v>$</v>
+      </c>
+      <c r="J25" t="str">
         <v>053 952 777</v>
       </c>
     </row>
@@ -8671,7 +8852,7 @@
         <v>rest-25</v>
       </c>
       <c r="C26" t="str">
-        <v>ភោជនីយដ្ឋាន ចានបាយ (Jaan Bai Restaurant)</v>
+        <v>ភោជនីយដ្ឋាន ចានបាយ</v>
       </c>
       <c r="D26" t="str">
         <v>Jaan Bai Restaurant Battambang</v>
@@ -8680,12 +8861,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F26" t="str">
-        <v>$$</v>
+        <v>Battambang</v>
       </c>
       <c r="G26" t="str">
         <v>ផ្លូវលេខ ២ ជិតផ្សារណាត់ ក្រុងបាត់ដំបង</v>
       </c>
       <c r="H26" t="str">
+        <v>Street 2, near Psar Nat, Battambang</v>
+      </c>
+      <c r="I26" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J26" t="str">
         <v>070 283 262</v>
       </c>
     </row>
@@ -8697,7 +8884,7 @@
         <v>rest-26</v>
       </c>
       <c r="C27" t="str">
-        <v>ហាងបាយ ណារី ឃីតឆិន (Nary Kitchen Battambang)</v>
+        <v>ហាងបាយ ណារី ឃីតឆិន</v>
       </c>
       <c r="D27" t="str">
         <v>Nary Kitchen &amp; Cooking School</v>
@@ -8706,12 +8893,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F27" t="str">
-        <v>$</v>
+        <v>Battambang</v>
       </c>
       <c r="G27" t="str">
         <v>ផ្លូវ ១១១ ក្រុងបាត់ដំបង</v>
       </c>
       <c r="H27" t="str">
+        <v>Street 111, Battambang City</v>
+      </c>
+      <c r="I27" t="str">
+        <v>$</v>
+      </c>
+      <c r="J27" t="str">
         <v>012 763 950</v>
       </c>
     </row>
@@ -8723,7 +8916,7 @@
         <v>rest-27</v>
       </c>
       <c r="C28" t="str">
-        <v>ភោជនីយដ្ឋាន សន្ទាន់ (Sandan Restaurant Sihanoukville)</v>
+        <v>ភោជនីយដ្ឋាន សន្ទាន់</v>
       </c>
       <c r="D28" t="str">
         <v>Sandan Training Restaurant Sihanoukville</v>
@@ -8732,12 +8925,18 @@
         <v>ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="F28" t="str">
-        <v>$$</v>
+        <v>Preah Sihanouk</v>
       </c>
       <c r="G28" t="str">
         <v>ផ្លូវក្បែរឆ្នេរអូរឈើទាល ក្រុងព្រះសីហនុ</v>
       </c>
       <c r="H28" t="str">
+        <v>Near Ochheuteal Beach, Sihanoukville</v>
+      </c>
+      <c r="I28" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J28" t="str">
         <v>034 934 744</v>
       </c>
     </row>
@@ -8749,7 +8948,7 @@
         <v>rest-28</v>
       </c>
       <c r="C29" t="str">
-        <v>ហាងបាយ ស្មាញ (Smile Restaurant Kampong Cham)</v>
+        <v>ហាងបាយ ស្មាញ</v>
       </c>
       <c r="D29" t="str">
         <v>Smile Restaurant Kampong Cham</v>
@@ -8758,12 +8957,18 @@
         <v>ខេត្តកំពង់ចាម</v>
       </c>
       <c r="F29" t="str">
-        <v>$</v>
+        <v>Kampong Cham</v>
       </c>
       <c r="G29" t="str">
         <v>ផ្លូវមាត់ទន្លេមេគង្គ ក្រុងកំពង់ចាម</v>
       </c>
       <c r="H29" t="str">
+        <v>Riverside Road, Kampong Cham City</v>
+      </c>
+      <c r="I29" t="str">
+        <v>$</v>
+      </c>
+      <c r="J29" t="str">
         <v>042 941 456</v>
       </c>
     </row>
@@ -8775,7 +8980,7 @@
         <v>rest-29</v>
       </c>
       <c r="C30" t="str">
-        <v>ហាងបាយ ហ្គ្រីនហោស៍ សែនមនោរម្យ (Greenhouse Mondulkiri)</v>
+        <v>ហាងបាយ ហ្គ្រីនហោស៍ សែនមនោរម្យ</v>
       </c>
       <c r="D30" t="str">
         <v>Greenhouse Restaurant Sen Monorom</v>
@@ -8784,12 +8989,18 @@
         <v>ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="F30" t="str">
-        <v>$</v>
+        <v>Mondulkiri</v>
       </c>
       <c r="G30" t="str">
         <v>ក្រុងសែនមនោរម្យ ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="H30" t="str">
+        <v>Sen Monorom City Center, Mondulkiri</v>
+      </c>
+      <c r="I30" t="str">
+        <v>$</v>
+      </c>
+      <c r="J30" t="str">
         <v>073 956 789</v>
       </c>
     </row>
@@ -8801,7 +9012,7 @@
         <v>rest-30</v>
       </c>
       <c r="C31" t="str">
-        <v>ភោជនីយដ្ឋាន អូតូ មាត់សមុទ្រកោះកុង (Otto Seaside Koh Kong)</v>
+        <v>ភោជនីយដ្ឋាន អូតូ មាត់សមុទ្រកោះកុង</v>
       </c>
       <c r="D31" t="str">
         <v>Otto Seaside Seafood Koh Kong</v>
@@ -8810,12 +9021,18 @@
         <v>ខេត្តកោះកុង</v>
       </c>
       <c r="F31" t="str">
-        <v>$$</v>
+        <v>Koh Kong</v>
       </c>
       <c r="G31" t="str">
         <v>ភូមិ១ ឃុំស្មាច់មានជ័យ ក្រុងខេមរភូមិន្ទ ខេត្តកោះកុង</v>
       </c>
       <c r="H31" t="str">
+        <v>Smach Mean Chey, Khemarak Phoumin, Koh Kong</v>
+      </c>
+      <c r="I31" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J31" t="str">
         <v>035 936 123</v>
       </c>
     </row>
@@ -8827,7 +9044,7 @@
         <v>rest-31</v>
       </c>
       <c r="C32" t="str">
-        <v>ហាងបាយ បង្កងទឹកសាបតាកែវ (Takeo Giant Prawn Eatery)</v>
+        <v>ហាងបាយ បង្កងទឹកសាបតាកែវ</v>
       </c>
       <c r="D32" t="str">
         <v>Takeo River Prawn House</v>
@@ -8836,12 +9053,18 @@
         <v>ខេត្តតាកែវ</v>
       </c>
       <c r="F32" t="str">
-        <v>$$$</v>
+        <v>Takeo</v>
       </c>
       <c r="G32" t="str">
         <v>ក្រុងដូនកែវ ខេត្តតាកែវ</v>
       </c>
       <c r="H32" t="str">
+        <v>Doun Kaev City, Takeo Province</v>
+      </c>
+      <c r="I32" t="str">
+        <v>$$$</v>
+      </c>
+      <c r="J32" t="str">
         <v>032 931 222</v>
       </c>
     </row>
@@ -8853,7 +9076,7 @@
         <v>rest-32</v>
       </c>
       <c r="C33" t="str">
-        <v>ភោជនីយដ្ឋាន ផ្សោតទន្លេមេគង្គ ក្រចេះ (Kratie Dolphin Cafe)</v>
+        <v>ភោជនីយដ្ឋាន ផ្សោតទន្លេមេគង្គ ក្រចេះ</v>
       </c>
       <c r="D33" t="str">
         <v>Kratie Mekong Dolphin Restaurant</v>
@@ -8862,12 +9085,18 @@
         <v>ខេត្តក្រចេះ</v>
       </c>
       <c r="F33" t="str">
-        <v>$</v>
+        <v>Kratie</v>
       </c>
       <c r="G33" t="str">
         <v>ផ្លូវមាត់ទន្លេ ឃុំសំបុក ស្រុកចិត្របុរី ខេត្តក្រចេះ</v>
       </c>
       <c r="H33" t="str">
+        <v>River Road, Sambok, Kratie Province</v>
+      </c>
+      <c r="I33" t="str">
+        <v>$</v>
+      </c>
+      <c r="J33" t="str">
         <v>072 971 333</v>
       </c>
     </row>
@@ -8879,7 +9108,7 @@
         <v>rest-33</v>
       </c>
       <c r="C34" t="str">
-        <v>ហាងបាយ ស្ទឹងពោធិ៍សាត់ (Pursat River Restaurant)</v>
+        <v>ហាងបាយ ស្ទឹងពោធិ៍សាត់</v>
       </c>
       <c r="D34" t="str">
         <v>Pursat River View Restaurant</v>
@@ -8888,12 +9117,18 @@
         <v>ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="F34" t="str">
-        <v>$</v>
+        <v>Pursat</v>
       </c>
       <c r="G34" t="str">
         <v>មាត់ស្ទឹងពោធិ៍សាត់ ក្រុងពោធិ៍សាត់</v>
       </c>
       <c r="H34" t="str">
+        <v>Pursat Riverfront, Pursat City</v>
+      </c>
+      <c r="I34" t="str">
+        <v>$</v>
+      </c>
+      <c r="J34" t="str">
         <v>052 951 111</v>
       </c>
     </row>
@@ -8905,7 +9140,7 @@
         <v>rest-34</v>
       </c>
       <c r="C35" t="str">
-        <v>ភោជនីយដ្ឋាន បឹងយក្សឡោម រតនគិរី (Yeak Laom Cafe Ratanakiri)</v>
+        <v>ភោជនីយដ្ឋាន បឹងយក្សឡោម រតនគិរី</v>
       </c>
       <c r="D35" t="str">
         <v>Yeak Laom Lake Restaurant Banlung</v>
@@ -8914,12 +9149,18 @@
         <v>ខេត្តរតនគិរី</v>
       </c>
       <c r="F35" t="str">
-        <v>$</v>
+        <v>Ratanakiri</v>
       </c>
       <c r="G35" t="str">
         <v>បឹងយក្សឡោម ក្រុងបានលុង ខេត្តរតនគិរី</v>
       </c>
       <c r="H35" t="str">
+        <v>Yeak Laom Lake, Banlung City, Ratanakiri</v>
+      </c>
+      <c r="I35" t="str">
+        <v>$</v>
+      </c>
+      <c r="J35" t="str">
         <v>075 974 222</v>
       </c>
     </row>
@@ -8931,7 +9172,7 @@
         <v>rest-35</v>
       </c>
       <c r="C36" t="str">
-        <v>ហាងបាយ ស្ទឹងសែន កំពង់ធំ (Steung Saen Restaurant)</v>
+        <v>ហាងបាយ ស្ទឹងសែន កំពង់ធំ</v>
       </c>
       <c r="D36" t="str">
         <v>Steung Saen Restaurant Kampong Thom</v>
@@ -8940,12 +9181,18 @@
         <v>ខេត្តកំពង់ធំ</v>
       </c>
       <c r="F36" t="str">
-        <v>$</v>
+        <v>Kampong Thom</v>
       </c>
       <c r="G36" t="str">
         <v>ក្រុងស្ទឹងសែន ខេត្តកំពង់ធំ</v>
       </c>
       <c r="H36" t="str">
+        <v>Steung Saen City, Kampong Thom</v>
+      </c>
+      <c r="I36" t="str">
+        <v>$</v>
+      </c>
+      <c r="J36" t="str">
         <v>062 961 888</v>
       </c>
     </row>
@@ -8957,7 +9204,7 @@
         <v>rest-36</v>
       </c>
       <c r="C37" t="str">
-        <v>ហាងបាយ កំពង់ឆ្នាំង ឆ្នាំងដី (Kampong Chhnang Claypot)</v>
+        <v>ហាងបាយ កំពង់ឆ្នាំង ឆ្នាំងដី</v>
       </c>
       <c r="D37" t="str">
         <v>Kampong Chhnang Claypot Kitchen</v>
@@ -8966,12 +9213,18 @@
         <v>ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="F37" t="str">
-        <v>$</v>
+        <v>Kampong Chhnang</v>
       </c>
       <c r="G37" t="str">
         <v>ក្រុងកំពង់ឆ្នាំង ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="H37" t="str">
+        <v>Kampong Chhnang City Center</v>
+      </c>
+      <c r="I37" t="str">
+        <v>$</v>
+      </c>
+      <c r="J37" t="str">
         <v>026 988 123</v>
       </c>
     </row>
@@ -8983,7 +9236,7 @@
         <v>rest-37</v>
       </c>
       <c r="C38" t="str">
-        <v>ហាងទាខ្វៃ តាខ្មៅ (Ta Khmao Roast Duck House)</v>
+        <v>ហាងទាខ្វៃ តាខ្មៅ</v>
       </c>
       <c r="D38" t="str">
         <v>Ta Khmao Roast Duck House Kandal</v>
@@ -8992,12 +9245,18 @@
         <v>ខេត្តកណ្តាល</v>
       </c>
       <c r="F38" t="str">
-        <v>$$</v>
+        <v>Kandal</v>
       </c>
       <c r="G38" t="str">
         <v>ក្រុងតាខ្មៅ ខេត្តកណ្តាល</v>
       </c>
       <c r="H38" t="str">
+        <v>Ta Khmao City, Kandal Province</v>
+      </c>
+      <c r="I38" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J38" t="str">
         <v>024 985 456</v>
       </c>
     </row>
@@ -9009,7 +9268,7 @@
         <v>rest-38</v>
       </c>
       <c r="C39" t="str">
-        <v>ហាងបាយ ត្រីប៉ាស៊ីអ៊ី ស្ទឹងត្រែង (Stung Treng Mekong Fish)</v>
+        <v>ហាងបាយ ត្រីប៉ាស៊ីអ៊ី ស្ទឹងត្រែង</v>
       </c>
       <c r="D39" t="str">
         <v>Stung Treng Mekong Pas-ee Fish Restaurant</v>
@@ -9018,12 +9277,18 @@
         <v>ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="F39" t="str">
-        <v>$$</v>
+        <v>Stung Treng</v>
       </c>
       <c r="G39" t="str">
         <v>ផ្លូវមាត់ទន្លេសេកុង ក្រុងស្ទឹងត្រែង</v>
       </c>
       <c r="H39" t="str">
+        <v>Sekong Riverfront, Stung Treng City</v>
+      </c>
+      <c r="I39" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J39" t="str">
         <v>074 973 111</v>
       </c>
     </row>
@@ -9035,7 +9300,7 @@
         <v>rest-39</v>
       </c>
       <c r="C40" t="str">
-        <v>ហាងបាយ ជើងភ្នំដងរែក ព្រះវិហារ (Dangrek Preah Vihear Rest)</v>
+        <v>ហាងបាយ ជើងភ្នំដងរែក ព្រះវិហារ</v>
       </c>
       <c r="D40" t="str">
         <v>Dangrek Foothill Restaurant Preah Vihear</v>
@@ -9044,12 +9309,18 @@
         <v>ខេត្តព្រះវិហារ</v>
       </c>
       <c r="F40" t="str">
-        <v>$</v>
+        <v>Preah Vihear</v>
       </c>
       <c r="G40" t="str">
         <v>ស្រុកជាំក្សាន្ត ខេត្តព្រះវិហារ</v>
       </c>
       <c r="H40" t="str">
+        <v>Choam Khsant District, Preah Vihear</v>
+      </c>
+      <c r="I40" t="str">
+        <v>$</v>
+      </c>
+      <c r="J40" t="str">
         <v>064 956 777</v>
       </c>
     </row>
@@ -9061,7 +9332,7 @@
         <v>rest-40</v>
       </c>
       <c r="C41" t="str">
-        <v>ហាងបាយ ត្បូងប៉ៃលិន (Pailin Gem View Restaurant)</v>
+        <v>ហាងបាយ ត្បូងប៉ៃលិន</v>
       </c>
       <c r="D41" t="str">
         <v>Pailin Mountain Gem Restaurant</v>
@@ -9070,12 +9341,18 @@
         <v>ខេត្តប៉ៃលិន</v>
       </c>
       <c r="F41" t="str">
-        <v>$</v>
+        <v>Pailin</v>
       </c>
       <c r="G41" t="str">
         <v>ក្រុងប៉ៃលិន ខេត្តប៉ៃលិន</v>
       </c>
       <c r="H41" t="str">
+        <v>Pailin City Center, Pailin Province</v>
+      </c>
+      <c r="I41" t="str">
+        <v>$</v>
+      </c>
+      <c r="J41" t="str">
         <v>055 956 333</v>
       </c>
     </row>
@@ -9096,12 +9373,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F42" t="str">
-        <v>$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G42" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H42" t="str">
+        <v>Central Market Area, Phnom Penh</v>
+      </c>
+      <c r="I42" t="str">
+        <v>$</v>
+      </c>
+      <c r="J42" t="str">
         <v>095 387 733</v>
       </c>
     </row>
@@ -9122,12 +9405,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F43" t="str">
-        <v>$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G43" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តសៀមរាប</v>
       </c>
       <c r="H43" t="str">
+        <v>Central Market Area, Siem Reap</v>
+      </c>
+      <c r="I43" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J43" t="str">
         <v>096 394 746</v>
       </c>
     </row>
@@ -9148,12 +9437,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F44" t="str">
-        <v>$</v>
+        <v>Battambang</v>
       </c>
       <c r="G44" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបាត់ដំបង</v>
       </c>
       <c r="H44" t="str">
+        <v>Central Market Area, Battambang</v>
+      </c>
+      <c r="I44" t="str">
+        <v>$</v>
+      </c>
+      <c r="J44" t="str">
         <v>097 401 759</v>
       </c>
     </row>
@@ -9174,12 +9469,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F45" t="str">
-        <v>$</v>
+        <v>Kampot</v>
       </c>
       <c r="G45" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពត</v>
       </c>
       <c r="H45" t="str">
+        <v>Central Market Area, Kampot</v>
+      </c>
+      <c r="I45" t="str">
+        <v>$</v>
+      </c>
+      <c r="J45" t="str">
         <v>098 408 772</v>
       </c>
     </row>
@@ -9200,12 +9501,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F46" t="str">
-        <v>$$</v>
+        <v>Kep</v>
       </c>
       <c r="G46" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកែប</v>
       </c>
       <c r="H46" t="str">
+        <v>Central Market Area, Kep</v>
+      </c>
+      <c r="I46" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J46" t="str">
         <v>090 415 785</v>
       </c>
     </row>
@@ -9226,12 +9533,18 @@
         <v>ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="F47" t="str">
-        <v>$</v>
+        <v>Preah Sihanouk</v>
       </c>
       <c r="G47" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="H47" t="str">
+        <v>Central Market Area, Preah Sihanouk</v>
+      </c>
+      <c r="I47" t="str">
+        <v>$</v>
+      </c>
+      <c r="J47" t="str">
         <v>091 422 798</v>
       </c>
     </row>
@@ -9252,12 +9565,18 @@
         <v>ខេត្តកំពង់ចាម</v>
       </c>
       <c r="F48" t="str">
-        <v>$</v>
+        <v>Kampong Cham</v>
       </c>
       <c r="G48" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ចាម</v>
       </c>
       <c r="H48" t="str">
+        <v>Central Market Area, Kampong Cham</v>
+      </c>
+      <c r="I48" t="str">
+        <v>$</v>
+      </c>
+      <c r="J48" t="str">
         <v>092 429 811</v>
       </c>
     </row>
@@ -9278,12 +9597,18 @@
         <v>ខេត្តកណ្តាល</v>
       </c>
       <c r="F49" t="str">
-        <v>$$</v>
+        <v>Kandal</v>
       </c>
       <c r="G49" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកណ្តាល</v>
       </c>
       <c r="H49" t="str">
+        <v>Central Market Area, Kandal</v>
+      </c>
+      <c r="I49" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J49" t="str">
         <v>093 436 824</v>
       </c>
     </row>
@@ -9304,12 +9629,18 @@
         <v>ខេត្តតាកែវ</v>
       </c>
       <c r="F50" t="str">
-        <v>$</v>
+        <v>Takeo</v>
       </c>
       <c r="G50" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តតាកែវ</v>
       </c>
       <c r="H50" t="str">
+        <v>Central Market Area, Takeo</v>
+      </c>
+      <c r="I50" t="str">
+        <v>$</v>
+      </c>
+      <c r="J50" t="str">
         <v>094 443 837</v>
       </c>
     </row>
@@ -9330,12 +9661,18 @@
         <v>ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="F51" t="str">
-        <v>$</v>
+        <v>Pursat</v>
       </c>
       <c r="G51" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="H51" t="str">
+        <v>Central Market Area, Pursat</v>
+      </c>
+      <c r="I51" t="str">
+        <v>$</v>
+      </c>
+      <c r="J51" t="str">
         <v>095 450 850</v>
       </c>
     </row>
@@ -9356,12 +9693,18 @@
         <v>ខេត្តកំពង់ធំ</v>
       </c>
       <c r="F52" t="str">
-        <v>$$</v>
+        <v>Kampong Thom</v>
       </c>
       <c r="G52" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ធំ</v>
       </c>
       <c r="H52" t="str">
+        <v>Central Market Area, Kampong Thom</v>
+      </c>
+      <c r="I52" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J52" t="str">
         <v>096 457 863</v>
       </c>
     </row>
@@ -9382,12 +9725,18 @@
         <v>ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="F53" t="str">
-        <v>$</v>
+        <v>Kampong Chhnang</v>
       </c>
       <c r="G53" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="H53" t="str">
+        <v>Central Market Area, Kampong Chhnang</v>
+      </c>
+      <c r="I53" t="str">
+        <v>$</v>
+      </c>
+      <c r="J53" t="str">
         <v>097 464 876</v>
       </c>
     </row>
@@ -9408,12 +9757,18 @@
         <v>ខេត្តកោះកុង</v>
       </c>
       <c r="F54" t="str">
-        <v>$</v>
+        <v>Koh Kong</v>
       </c>
       <c r="G54" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកោះកុង</v>
       </c>
       <c r="H54" t="str">
+        <v>Central Market Area, Koh Kong</v>
+      </c>
+      <c r="I54" t="str">
+        <v>$</v>
+      </c>
+      <c r="J54" t="str">
         <v>098 471 889</v>
       </c>
     </row>
@@ -9434,12 +9789,18 @@
         <v>ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="F55" t="str">
-        <v>$$</v>
+        <v>Mondulkiri</v>
       </c>
       <c r="G55" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="H55" t="str">
+        <v>Central Market Area, Mondulkiri</v>
+      </c>
+      <c r="I55" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J55" t="str">
         <v>090 478 902</v>
       </c>
     </row>
@@ -9460,12 +9821,18 @@
         <v>ខេត្តរតនគិរី</v>
       </c>
       <c r="F56" t="str">
-        <v>$</v>
+        <v>Ratanakiri</v>
       </c>
       <c r="G56" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តរតនគិរី</v>
       </c>
       <c r="H56" t="str">
+        <v>Central Market Area, Ratanakiri</v>
+      </c>
+      <c r="I56" t="str">
+        <v>$</v>
+      </c>
+      <c r="J56" t="str">
         <v>091 485 915</v>
       </c>
     </row>
@@ -9486,12 +9853,18 @@
         <v>ខេត្តក្រចេះ</v>
       </c>
       <c r="F57" t="str">
-        <v>$</v>
+        <v>Kratie</v>
       </c>
       <c r="G57" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តក្រចេះ</v>
       </c>
       <c r="H57" t="str">
+        <v>Central Market Area, Kratie</v>
+      </c>
+      <c r="I57" t="str">
+        <v>$</v>
+      </c>
+      <c r="J57" t="str">
         <v>092 492 928</v>
       </c>
     </row>
@@ -9512,12 +9885,18 @@
         <v>ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="F58" t="str">
-        <v>$$</v>
+        <v>Stung Treng</v>
       </c>
       <c r="G58" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="H58" t="str">
+        <v>Central Market Area, Stung Treng</v>
+      </c>
+      <c r="I58" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J58" t="str">
         <v>093 499 941</v>
       </c>
     </row>
@@ -9538,12 +9917,18 @@
         <v>ខេត្តព្រះវិហារ</v>
       </c>
       <c r="F59" t="str">
-        <v>$</v>
+        <v>Preah Vihear</v>
       </c>
       <c r="G59" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះវិហារ</v>
       </c>
       <c r="H59" t="str">
+        <v>Central Market Area, Preah Vihear</v>
+      </c>
+      <c r="I59" t="str">
+        <v>$</v>
+      </c>
+      <c r="J59" t="str">
         <v>094 506 954</v>
       </c>
     </row>
@@ -9564,12 +9949,18 @@
         <v>ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="F60" t="str">
-        <v>$</v>
+        <v>Banteay Meanchey</v>
       </c>
       <c r="G60" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="H60" t="str">
+        <v>Central Market Area, Banteay Meanchey</v>
+      </c>
+      <c r="I60" t="str">
+        <v>$</v>
+      </c>
+      <c r="J60" t="str">
         <v>095 513 967</v>
       </c>
     </row>
@@ -9590,12 +9981,18 @@
         <v>ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="F61" t="str">
-        <v>$$</v>
+        <v>Oddar Meanchey</v>
       </c>
       <c r="G61" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="H61" t="str">
+        <v>Central Market Area, Oddar Meanchey</v>
+      </c>
+      <c r="I61" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J61" t="str">
         <v>096 520 980</v>
       </c>
     </row>
@@ -9616,12 +10013,18 @@
         <v>ខេត្តប៉ៃលិន</v>
       </c>
       <c r="F62" t="str">
-        <v>$</v>
+        <v>Pailin</v>
       </c>
       <c r="G62" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តប៉ៃលិន</v>
       </c>
       <c r="H62" t="str">
+        <v>Central Market Area, Pailin</v>
+      </c>
+      <c r="I62" t="str">
+        <v>$</v>
+      </c>
+      <c r="J62" t="str">
         <v>097 527 993</v>
       </c>
     </row>
@@ -9642,12 +10045,18 @@
         <v>ខេត្តព្រៃវែង</v>
       </c>
       <c r="F63" t="str">
-        <v>$</v>
+        <v>Prey Veng</v>
       </c>
       <c r="G63" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រៃវែង</v>
       </c>
       <c r="H63" t="str">
+        <v>Central Market Area, Prey Veng</v>
+      </c>
+      <c r="I63" t="str">
+        <v>$</v>
+      </c>
+      <c r="J63" t="str">
         <v>098 534 206</v>
       </c>
     </row>
@@ -9668,12 +10077,18 @@
         <v>ខេត្តស្វាយរៀង</v>
       </c>
       <c r="F64" t="str">
-        <v>$$</v>
+        <v>Svay Rieng</v>
       </c>
       <c r="G64" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្វាយរៀង</v>
       </c>
       <c r="H64" t="str">
+        <v>Central Market Area, Svay Rieng</v>
+      </c>
+      <c r="I64" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J64" t="str">
         <v>090 541 219</v>
       </c>
     </row>
@@ -9694,12 +10109,18 @@
         <v>ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="F65" t="str">
-        <v>$</v>
+        <v>Kampong Speu</v>
       </c>
       <c r="G65" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="H65" t="str">
+        <v>Central Market Area, Kampong Speu</v>
+      </c>
+      <c r="I65" t="str">
+        <v>$</v>
+      </c>
+      <c r="J65" t="str">
         <v>091 548 232</v>
       </c>
     </row>
@@ -9720,12 +10141,18 @@
         <v>ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="F66" t="str">
-        <v>$</v>
+        <v>Tboung Khmum</v>
       </c>
       <c r="G66" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="H66" t="str">
+        <v>Central Market Area, Tboung Khmum</v>
+      </c>
+      <c r="I66" t="str">
+        <v>$</v>
+      </c>
+      <c r="J66" t="str">
         <v>092 555 245</v>
       </c>
     </row>
@@ -9746,12 +10173,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F67" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G67" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H67" t="str">
+        <v>Central Market Area, Phnom Penh</v>
+      </c>
+      <c r="I67" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J67" t="str">
         <v>093 562 258</v>
       </c>
     </row>
@@ -9772,12 +10205,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F68" t="str">
-        <v>$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G68" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តសៀមរាប</v>
       </c>
       <c r="H68" t="str">
+        <v>Central Market Area, Siem Reap</v>
+      </c>
+      <c r="I68" t="str">
+        <v>$</v>
+      </c>
+      <c r="J68" t="str">
         <v>094 569 271</v>
       </c>
     </row>
@@ -9798,12 +10237,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F69" t="str">
-        <v>$</v>
+        <v>Battambang</v>
       </c>
       <c r="G69" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបាត់ដំបង</v>
       </c>
       <c r="H69" t="str">
+        <v>Central Market Area, Battambang</v>
+      </c>
+      <c r="I69" t="str">
+        <v>$</v>
+      </c>
+      <c r="J69" t="str">
         <v>095 576 284</v>
       </c>
     </row>
@@ -9824,12 +10269,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F70" t="str">
-        <v>$$</v>
+        <v>Kampot</v>
       </c>
       <c r="G70" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពត</v>
       </c>
       <c r="H70" t="str">
+        <v>Central Market Area, Kampot</v>
+      </c>
+      <c r="I70" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J70" t="str">
         <v>096 583 297</v>
       </c>
     </row>
@@ -9850,12 +10301,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F71" t="str">
-        <v>$</v>
+        <v>Kep</v>
       </c>
       <c r="G71" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកែប</v>
       </c>
       <c r="H71" t="str">
+        <v>Central Market Area, Kep</v>
+      </c>
+      <c r="I71" t="str">
+        <v>$</v>
+      </c>
+      <c r="J71" t="str">
         <v>097 590 310</v>
       </c>
     </row>
@@ -9876,12 +10333,18 @@
         <v>ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="F72" t="str">
-        <v>$</v>
+        <v>Preah Sihanouk</v>
       </c>
       <c r="G72" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="H72" t="str">
+        <v>Central Market Area, Preah Sihanouk</v>
+      </c>
+      <c r="I72" t="str">
+        <v>$</v>
+      </c>
+      <c r="J72" t="str">
         <v>098 597 323</v>
       </c>
     </row>
@@ -9902,12 +10365,18 @@
         <v>ខេត្តកំពង់ចាម</v>
       </c>
       <c r="F73" t="str">
-        <v>$$</v>
+        <v>Kampong Cham</v>
       </c>
       <c r="G73" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ចាម</v>
       </c>
       <c r="H73" t="str">
+        <v>Central Market Area, Kampong Cham</v>
+      </c>
+      <c r="I73" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J73" t="str">
         <v>090 604 336</v>
       </c>
     </row>
@@ -9928,12 +10397,18 @@
         <v>ខេត្តកណ្តាល</v>
       </c>
       <c r="F74" t="str">
-        <v>$</v>
+        <v>Kandal</v>
       </c>
       <c r="G74" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកណ្តាល</v>
       </c>
       <c r="H74" t="str">
+        <v>Central Market Area, Kandal</v>
+      </c>
+      <c r="I74" t="str">
+        <v>$</v>
+      </c>
+      <c r="J74" t="str">
         <v>091 611 349</v>
       </c>
     </row>
@@ -9954,12 +10429,18 @@
         <v>ខេត្តតាកែវ</v>
       </c>
       <c r="F75" t="str">
-        <v>$</v>
+        <v>Takeo</v>
       </c>
       <c r="G75" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តតាកែវ</v>
       </c>
       <c r="H75" t="str">
+        <v>Central Market Area, Takeo</v>
+      </c>
+      <c r="I75" t="str">
+        <v>$</v>
+      </c>
+      <c r="J75" t="str">
         <v>092 618 362</v>
       </c>
     </row>
@@ -9980,12 +10461,18 @@
         <v>ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="F76" t="str">
-        <v>$$</v>
+        <v>Pursat</v>
       </c>
       <c r="G76" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="H76" t="str">
+        <v>Central Market Area, Pursat</v>
+      </c>
+      <c r="I76" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J76" t="str">
         <v>093 625 375</v>
       </c>
     </row>
@@ -10006,12 +10493,18 @@
         <v>ខេត្តកំពង់ធំ</v>
       </c>
       <c r="F77" t="str">
-        <v>$</v>
+        <v>Kampong Thom</v>
       </c>
       <c r="G77" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ធំ</v>
       </c>
       <c r="H77" t="str">
+        <v>Central Market Area, Kampong Thom</v>
+      </c>
+      <c r="I77" t="str">
+        <v>$</v>
+      </c>
+      <c r="J77" t="str">
         <v>094 632 388</v>
       </c>
     </row>
@@ -10032,12 +10525,18 @@
         <v>ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="F78" t="str">
-        <v>$</v>
+        <v>Kampong Chhnang</v>
       </c>
       <c r="G78" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="H78" t="str">
+        <v>Central Market Area, Kampong Chhnang</v>
+      </c>
+      <c r="I78" t="str">
+        <v>$</v>
+      </c>
+      <c r="J78" t="str">
         <v>095 639 401</v>
       </c>
     </row>
@@ -10058,12 +10557,18 @@
         <v>ខេត្តកោះកុង</v>
       </c>
       <c r="F79" t="str">
-        <v>$$</v>
+        <v>Koh Kong</v>
       </c>
       <c r="G79" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកោះកុង</v>
       </c>
       <c r="H79" t="str">
+        <v>Central Market Area, Koh Kong</v>
+      </c>
+      <c r="I79" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J79" t="str">
         <v>096 646 414</v>
       </c>
     </row>
@@ -10084,12 +10589,18 @@
         <v>ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="F80" t="str">
-        <v>$</v>
+        <v>Mondulkiri</v>
       </c>
       <c r="G80" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="H80" t="str">
+        <v>Central Market Area, Mondulkiri</v>
+      </c>
+      <c r="I80" t="str">
+        <v>$</v>
+      </c>
+      <c r="J80" t="str">
         <v>097 653 427</v>
       </c>
     </row>
@@ -10110,12 +10621,18 @@
         <v>ខេត្តរតនគិរី</v>
       </c>
       <c r="F81" t="str">
-        <v>$</v>
+        <v>Ratanakiri</v>
       </c>
       <c r="G81" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តរតនគិរី</v>
       </c>
       <c r="H81" t="str">
+        <v>Central Market Area, Ratanakiri</v>
+      </c>
+      <c r="I81" t="str">
+        <v>$</v>
+      </c>
+      <c r="J81" t="str">
         <v>098 660 440</v>
       </c>
     </row>
@@ -10136,12 +10653,18 @@
         <v>ខេត្តក្រចេះ</v>
       </c>
       <c r="F82" t="str">
-        <v>$$</v>
+        <v>Kratie</v>
       </c>
       <c r="G82" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តក្រចេះ</v>
       </c>
       <c r="H82" t="str">
+        <v>Central Market Area, Kratie</v>
+      </c>
+      <c r="I82" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J82" t="str">
         <v>090 667 453</v>
       </c>
     </row>
@@ -10162,12 +10685,18 @@
         <v>ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="F83" t="str">
-        <v>$</v>
+        <v>Stung Treng</v>
       </c>
       <c r="G83" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="H83" t="str">
+        <v>Central Market Area, Stung Treng</v>
+      </c>
+      <c r="I83" t="str">
+        <v>$</v>
+      </c>
+      <c r="J83" t="str">
         <v>091 674 466</v>
       </c>
     </row>
@@ -10188,12 +10717,18 @@
         <v>ខេត្តព្រះវិហារ</v>
       </c>
       <c r="F84" t="str">
-        <v>$</v>
+        <v>Preah Vihear</v>
       </c>
       <c r="G84" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះវិហារ</v>
       </c>
       <c r="H84" t="str">
+        <v>Central Market Area, Preah Vihear</v>
+      </c>
+      <c r="I84" t="str">
+        <v>$</v>
+      </c>
+      <c r="J84" t="str">
         <v>092 681 479</v>
       </c>
     </row>
@@ -10214,12 +10749,18 @@
         <v>ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="F85" t="str">
-        <v>$$</v>
+        <v>Banteay Meanchey</v>
       </c>
       <c r="G85" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="H85" t="str">
+        <v>Central Market Area, Banteay Meanchey</v>
+      </c>
+      <c r="I85" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J85" t="str">
         <v>093 688 492</v>
       </c>
     </row>
@@ -10240,12 +10781,18 @@
         <v>ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="F86" t="str">
-        <v>$</v>
+        <v>Oddar Meanchey</v>
       </c>
       <c r="G86" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="H86" t="str">
+        <v>Central Market Area, Oddar Meanchey</v>
+      </c>
+      <c r="I86" t="str">
+        <v>$</v>
+      </c>
+      <c r="J86" t="str">
         <v>094 695 505</v>
       </c>
     </row>
@@ -10266,12 +10813,18 @@
         <v>ខេត្តប៉ៃលិន</v>
       </c>
       <c r="F87" t="str">
-        <v>$</v>
+        <v>Pailin</v>
       </c>
       <c r="G87" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តប៉ៃលិន</v>
       </c>
       <c r="H87" t="str">
+        <v>Central Market Area, Pailin</v>
+      </c>
+      <c r="I87" t="str">
+        <v>$</v>
+      </c>
+      <c r="J87" t="str">
         <v>095 702 518</v>
       </c>
     </row>
@@ -10292,12 +10845,18 @@
         <v>ខេត្តព្រៃវែង</v>
       </c>
       <c r="F88" t="str">
-        <v>$$</v>
+        <v>Prey Veng</v>
       </c>
       <c r="G88" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រៃវែង</v>
       </c>
       <c r="H88" t="str">
+        <v>Central Market Area, Prey Veng</v>
+      </c>
+      <c r="I88" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J88" t="str">
         <v>096 709 531</v>
       </c>
     </row>
@@ -10318,12 +10877,18 @@
         <v>ខេត្តស្វាយរៀង</v>
       </c>
       <c r="F89" t="str">
-        <v>$</v>
+        <v>Svay Rieng</v>
       </c>
       <c r="G89" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្វាយរៀង</v>
       </c>
       <c r="H89" t="str">
+        <v>Central Market Area, Svay Rieng</v>
+      </c>
+      <c r="I89" t="str">
+        <v>$</v>
+      </c>
+      <c r="J89" t="str">
         <v>097 716 544</v>
       </c>
     </row>
@@ -10344,12 +10909,18 @@
         <v>ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="F90" t="str">
-        <v>$</v>
+        <v>Kampong Speu</v>
       </c>
       <c r="G90" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="H90" t="str">
+        <v>Central Market Area, Kampong Speu</v>
+      </c>
+      <c r="I90" t="str">
+        <v>$</v>
+      </c>
+      <c r="J90" t="str">
         <v>098 723 557</v>
       </c>
     </row>
@@ -10370,12 +10941,18 @@
         <v>ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="F91" t="str">
-        <v>$$</v>
+        <v>Tboung Khmum</v>
       </c>
       <c r="G91" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="H91" t="str">
+        <v>Central Market Area, Tboung Khmum</v>
+      </c>
+      <c r="I91" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J91" t="str">
         <v>090 730 570</v>
       </c>
     </row>
@@ -10396,12 +10973,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F92" t="str">
-        <v>$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G92" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H92" t="str">
+        <v>Central Market Area, Phnom Penh</v>
+      </c>
+      <c r="I92" t="str">
+        <v>$</v>
+      </c>
+      <c r="J92" t="str">
         <v>091 737 583</v>
       </c>
     </row>
@@ -10422,12 +11005,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F93" t="str">
-        <v>$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G93" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តសៀមរាប</v>
       </c>
       <c r="H93" t="str">
+        <v>Central Market Area, Siem Reap</v>
+      </c>
+      <c r="I93" t="str">
+        <v>$</v>
+      </c>
+      <c r="J93" t="str">
         <v>092 744 596</v>
       </c>
     </row>
@@ -10448,12 +11037,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F94" t="str">
-        <v>$$</v>
+        <v>Battambang</v>
       </c>
       <c r="G94" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបាត់ដំបង</v>
       </c>
       <c r="H94" t="str">
+        <v>Central Market Area, Battambang</v>
+      </c>
+      <c r="I94" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J94" t="str">
         <v>093 751 609</v>
       </c>
     </row>
@@ -10474,12 +11069,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F95" t="str">
-        <v>$</v>
+        <v>Kampot</v>
       </c>
       <c r="G95" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពត</v>
       </c>
       <c r="H95" t="str">
+        <v>Central Market Area, Kampot</v>
+      </c>
+      <c r="I95" t="str">
+        <v>$</v>
+      </c>
+      <c r="J95" t="str">
         <v>094 758 622</v>
       </c>
     </row>
@@ -10500,12 +11101,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F96" t="str">
-        <v>$</v>
+        <v>Kep</v>
       </c>
       <c r="G96" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកែប</v>
       </c>
       <c r="H96" t="str">
+        <v>Central Market Area, Kep</v>
+      </c>
+      <c r="I96" t="str">
+        <v>$</v>
+      </c>
+      <c r="J96" t="str">
         <v>095 765 635</v>
       </c>
     </row>
@@ -10526,12 +11133,18 @@
         <v>ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="F97" t="str">
-        <v>$$</v>
+        <v>Preah Sihanouk</v>
       </c>
       <c r="G97" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="H97" t="str">
+        <v>Central Market Area, Preah Sihanouk</v>
+      </c>
+      <c r="I97" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J97" t="str">
         <v>096 772 648</v>
       </c>
     </row>
@@ -10552,12 +11165,18 @@
         <v>ខេត្តកំពង់ចាម</v>
       </c>
       <c r="F98" t="str">
-        <v>$</v>
+        <v>Kampong Cham</v>
       </c>
       <c r="G98" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ចាម</v>
       </c>
       <c r="H98" t="str">
+        <v>Central Market Area, Kampong Cham</v>
+      </c>
+      <c r="I98" t="str">
+        <v>$</v>
+      </c>
+      <c r="J98" t="str">
         <v>097 779 661</v>
       </c>
     </row>
@@ -10578,12 +11197,18 @@
         <v>ខេត្តកណ្តាល</v>
       </c>
       <c r="F99" t="str">
-        <v>$</v>
+        <v>Kandal</v>
       </c>
       <c r="G99" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកណ្តាល</v>
       </c>
       <c r="H99" t="str">
+        <v>Central Market Area, Kandal</v>
+      </c>
+      <c r="I99" t="str">
+        <v>$</v>
+      </c>
+      <c r="J99" t="str">
         <v>098 786 674</v>
       </c>
     </row>
@@ -10604,12 +11229,18 @@
         <v>ខេត្តតាកែវ</v>
       </c>
       <c r="F100" t="str">
-        <v>$$</v>
+        <v>Takeo</v>
       </c>
       <c r="G100" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តតាកែវ</v>
       </c>
       <c r="H100" t="str">
+        <v>Central Market Area, Takeo</v>
+      </c>
+      <c r="I100" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J100" t="str">
         <v>090 793 687</v>
       </c>
     </row>
@@ -10630,12 +11261,18 @@
         <v>ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="F101" t="str">
-        <v>$</v>
+        <v>Pursat</v>
       </c>
       <c r="G101" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="H101" t="str">
+        <v>Central Market Area, Pursat</v>
+      </c>
+      <c r="I101" t="str">
+        <v>$</v>
+      </c>
+      <c r="J101" t="str">
         <v>091 800 700</v>
       </c>
     </row>
@@ -10656,12 +11293,18 @@
         <v>ខេត្តកំពង់ធំ</v>
       </c>
       <c r="F102" t="str">
-        <v>$</v>
+        <v>Kampong Thom</v>
       </c>
       <c r="G102" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ធំ</v>
       </c>
       <c r="H102" t="str">
+        <v>Central Market Area, Kampong Thom</v>
+      </c>
+      <c r="I102" t="str">
+        <v>$</v>
+      </c>
+      <c r="J102" t="str">
         <v>092 807 713</v>
       </c>
     </row>
@@ -10682,12 +11325,18 @@
         <v>ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="F103" t="str">
-        <v>$$</v>
+        <v>Kampong Chhnang</v>
       </c>
       <c r="G103" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="H103" t="str">
+        <v>Central Market Area, Kampong Chhnang</v>
+      </c>
+      <c r="I103" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J103" t="str">
         <v>093 814 726</v>
       </c>
     </row>
@@ -10708,12 +11357,18 @@
         <v>ខេត្តកោះកុង</v>
       </c>
       <c r="F104" t="str">
-        <v>$</v>
+        <v>Koh Kong</v>
       </c>
       <c r="G104" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកោះកុង</v>
       </c>
       <c r="H104" t="str">
+        <v>Central Market Area, Koh Kong</v>
+      </c>
+      <c r="I104" t="str">
+        <v>$</v>
+      </c>
+      <c r="J104" t="str">
         <v>094 821 739</v>
       </c>
     </row>
@@ -10734,12 +11389,18 @@
         <v>ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="F105" t="str">
-        <v>$</v>
+        <v>Mondulkiri</v>
       </c>
       <c r="G105" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="H105" t="str">
+        <v>Central Market Area, Mondulkiri</v>
+      </c>
+      <c r="I105" t="str">
+        <v>$</v>
+      </c>
+      <c r="J105" t="str">
         <v>095 828 752</v>
       </c>
     </row>
@@ -10760,12 +11421,18 @@
         <v>ខេត្តរតនគិរី</v>
       </c>
       <c r="F106" t="str">
-        <v>$$</v>
+        <v>Ratanakiri</v>
       </c>
       <c r="G106" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តរតនគិរី</v>
       </c>
       <c r="H106" t="str">
+        <v>Central Market Area, Ratanakiri</v>
+      </c>
+      <c r="I106" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J106" t="str">
         <v>096 835 765</v>
       </c>
     </row>
@@ -10786,12 +11453,18 @@
         <v>ខេត្តក្រចេះ</v>
       </c>
       <c r="F107" t="str">
-        <v>$</v>
+        <v>Kratie</v>
       </c>
       <c r="G107" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តក្រចេះ</v>
       </c>
       <c r="H107" t="str">
+        <v>Central Market Area, Kratie</v>
+      </c>
+      <c r="I107" t="str">
+        <v>$</v>
+      </c>
+      <c r="J107" t="str">
         <v>097 842 778</v>
       </c>
     </row>
@@ -10812,12 +11485,18 @@
         <v>ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="F108" t="str">
-        <v>$</v>
+        <v>Stung Treng</v>
       </c>
       <c r="G108" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="H108" t="str">
+        <v>Central Market Area, Stung Treng</v>
+      </c>
+      <c r="I108" t="str">
+        <v>$</v>
+      </c>
+      <c r="J108" t="str">
         <v>098 849 791</v>
       </c>
     </row>
@@ -10838,12 +11517,18 @@
         <v>ខេត្តព្រះវិហារ</v>
       </c>
       <c r="F109" t="str">
-        <v>$$</v>
+        <v>Preah Vihear</v>
       </c>
       <c r="G109" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះវិហារ</v>
       </c>
       <c r="H109" t="str">
+        <v>Central Market Area, Preah Vihear</v>
+      </c>
+      <c r="I109" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J109" t="str">
         <v>090 856 804</v>
       </c>
     </row>
@@ -10864,12 +11549,18 @@
         <v>ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="F110" t="str">
-        <v>$</v>
+        <v>Banteay Meanchey</v>
       </c>
       <c r="G110" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="H110" t="str">
+        <v>Central Market Area, Banteay Meanchey</v>
+      </c>
+      <c r="I110" t="str">
+        <v>$</v>
+      </c>
+      <c r="J110" t="str">
         <v>091 863 817</v>
       </c>
     </row>
@@ -10890,12 +11581,18 @@
         <v>ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="F111" t="str">
-        <v>$</v>
+        <v>Oddar Meanchey</v>
       </c>
       <c r="G111" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="H111" t="str">
+        <v>Central Market Area, Oddar Meanchey</v>
+      </c>
+      <c r="I111" t="str">
+        <v>$</v>
+      </c>
+      <c r="J111" t="str">
         <v>092 870 830</v>
       </c>
     </row>
@@ -10916,12 +11613,18 @@
         <v>ខេត្តប៉ៃលិន</v>
       </c>
       <c r="F112" t="str">
-        <v>$$</v>
+        <v>Pailin</v>
       </c>
       <c r="G112" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តប៉ៃលិន</v>
       </c>
       <c r="H112" t="str">
+        <v>Central Market Area, Pailin</v>
+      </c>
+      <c r="I112" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J112" t="str">
         <v>093 877 843</v>
       </c>
     </row>
@@ -10942,12 +11645,18 @@
         <v>ខេត្តព្រៃវែង</v>
       </c>
       <c r="F113" t="str">
-        <v>$</v>
+        <v>Prey Veng</v>
       </c>
       <c r="G113" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រៃវែង</v>
       </c>
       <c r="H113" t="str">
+        <v>Central Market Area, Prey Veng</v>
+      </c>
+      <c r="I113" t="str">
+        <v>$</v>
+      </c>
+      <c r="J113" t="str">
         <v>094 884 856</v>
       </c>
     </row>
@@ -10968,12 +11677,18 @@
         <v>ខេត្តស្វាយរៀង</v>
       </c>
       <c r="F114" t="str">
-        <v>$</v>
+        <v>Svay Rieng</v>
       </c>
       <c r="G114" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្វាយរៀង</v>
       </c>
       <c r="H114" t="str">
+        <v>Central Market Area, Svay Rieng</v>
+      </c>
+      <c r="I114" t="str">
+        <v>$</v>
+      </c>
+      <c r="J114" t="str">
         <v>095 891 869</v>
       </c>
     </row>
@@ -10994,12 +11709,18 @@
         <v>ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="F115" t="str">
-        <v>$$</v>
+        <v>Kampong Speu</v>
       </c>
       <c r="G115" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="H115" t="str">
+        <v>Central Market Area, Kampong Speu</v>
+      </c>
+      <c r="I115" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J115" t="str">
         <v>096 898 882</v>
       </c>
     </row>
@@ -11020,12 +11741,18 @@
         <v>ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="F116" t="str">
-        <v>$</v>
+        <v>Tboung Khmum</v>
       </c>
       <c r="G116" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="H116" t="str">
+        <v>Central Market Area, Tboung Khmum</v>
+      </c>
+      <c r="I116" t="str">
+        <v>$</v>
+      </c>
+      <c r="J116" t="str">
         <v>097 905 895</v>
       </c>
     </row>
@@ -11046,12 +11773,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F117" t="str">
-        <v>$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G117" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H117" t="str">
+        <v>Central Market Area, Phnom Penh</v>
+      </c>
+      <c r="I117" t="str">
+        <v>$</v>
+      </c>
+      <c r="J117" t="str">
         <v>098 912 908</v>
       </c>
     </row>
@@ -11072,12 +11805,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F118" t="str">
-        <v>$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G118" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តសៀមរាប</v>
       </c>
       <c r="H118" t="str">
+        <v>Central Market Area, Siem Reap</v>
+      </c>
+      <c r="I118" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J118" t="str">
         <v>090 919 921</v>
       </c>
     </row>
@@ -11098,12 +11837,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F119" t="str">
-        <v>$</v>
+        <v>Battambang</v>
       </c>
       <c r="G119" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបាត់ដំបង</v>
       </c>
       <c r="H119" t="str">
+        <v>Central Market Area, Battambang</v>
+      </c>
+      <c r="I119" t="str">
+        <v>$</v>
+      </c>
+      <c r="J119" t="str">
         <v>091 926 934</v>
       </c>
     </row>
@@ -11124,12 +11869,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F120" t="str">
-        <v>$</v>
+        <v>Kampot</v>
       </c>
       <c r="G120" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពត</v>
       </c>
       <c r="H120" t="str">
+        <v>Central Market Area, Kampot</v>
+      </c>
+      <c r="I120" t="str">
+        <v>$</v>
+      </c>
+      <c r="J120" t="str">
         <v>092 933 947</v>
       </c>
     </row>
@@ -11150,12 +11901,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F121" t="str">
-        <v>$$</v>
+        <v>Kep</v>
       </c>
       <c r="G121" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកែប</v>
       </c>
       <c r="H121" t="str">
+        <v>Central Market Area, Kep</v>
+      </c>
+      <c r="I121" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J121" t="str">
         <v>093 940 960</v>
       </c>
     </row>
@@ -11176,12 +11933,18 @@
         <v>ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="F122" t="str">
-        <v>$</v>
+        <v>Preah Sihanouk</v>
       </c>
       <c r="G122" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="H122" t="str">
+        <v>Central Market Area, Preah Sihanouk</v>
+      </c>
+      <c r="I122" t="str">
+        <v>$</v>
+      </c>
+      <c r="J122" t="str">
         <v>094 947 973</v>
       </c>
     </row>
@@ -11202,12 +11965,18 @@
         <v>ខេត្តកំពង់ចាម</v>
       </c>
       <c r="F123" t="str">
-        <v>$</v>
+        <v>Kampong Cham</v>
       </c>
       <c r="G123" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ចាម</v>
       </c>
       <c r="H123" t="str">
+        <v>Central Market Area, Kampong Cham</v>
+      </c>
+      <c r="I123" t="str">
+        <v>$</v>
+      </c>
+      <c r="J123" t="str">
         <v>095 954 986</v>
       </c>
     </row>
@@ -11228,12 +11997,18 @@
         <v>ខេត្តកណ្តាល</v>
       </c>
       <c r="F124" t="str">
-        <v>$$</v>
+        <v>Kandal</v>
       </c>
       <c r="G124" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកណ្តាល</v>
       </c>
       <c r="H124" t="str">
+        <v>Central Market Area, Kandal</v>
+      </c>
+      <c r="I124" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J124" t="str">
         <v>096 961 999</v>
       </c>
     </row>
@@ -11254,12 +12029,18 @@
         <v>ខេត្តតាកែវ</v>
       </c>
       <c r="F125" t="str">
-        <v>$</v>
+        <v>Takeo</v>
       </c>
       <c r="G125" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តតាកែវ</v>
       </c>
       <c r="H125" t="str">
+        <v>Central Market Area, Takeo</v>
+      </c>
+      <c r="I125" t="str">
+        <v>$</v>
+      </c>
+      <c r="J125" t="str">
         <v>097 968 212</v>
       </c>
     </row>
@@ -11280,12 +12061,18 @@
         <v>ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="F126" t="str">
-        <v>$</v>
+        <v>Pursat</v>
       </c>
       <c r="G126" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="H126" t="str">
+        <v>Central Market Area, Pursat</v>
+      </c>
+      <c r="I126" t="str">
+        <v>$</v>
+      </c>
+      <c r="J126" t="str">
         <v>098 975 225</v>
       </c>
     </row>
@@ -11306,12 +12093,18 @@
         <v>ខេត្តកំពង់ធំ</v>
       </c>
       <c r="F127" t="str">
-        <v>$$</v>
+        <v>Kampong Thom</v>
       </c>
       <c r="G127" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ធំ</v>
       </c>
       <c r="H127" t="str">
+        <v>Central Market Area, Kampong Thom</v>
+      </c>
+      <c r="I127" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J127" t="str">
         <v>090 982 238</v>
       </c>
     </row>
@@ -11332,12 +12125,18 @@
         <v>ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="F128" t="str">
-        <v>$</v>
+        <v>Kampong Chhnang</v>
       </c>
       <c r="G128" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="H128" t="str">
+        <v>Central Market Area, Kampong Chhnang</v>
+      </c>
+      <c r="I128" t="str">
+        <v>$</v>
+      </c>
+      <c r="J128" t="str">
         <v>091 989 251</v>
       </c>
     </row>
@@ -11358,12 +12157,18 @@
         <v>ខេត្តកោះកុង</v>
       </c>
       <c r="F129" t="str">
-        <v>$</v>
+        <v>Koh Kong</v>
       </c>
       <c r="G129" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកោះកុង</v>
       </c>
       <c r="H129" t="str">
+        <v>Central Market Area, Koh Kong</v>
+      </c>
+      <c r="I129" t="str">
+        <v>$</v>
+      </c>
+      <c r="J129" t="str">
         <v>092 996 264</v>
       </c>
     </row>
@@ -11384,12 +12189,18 @@
         <v>ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="F130" t="str">
-        <v>$$</v>
+        <v>Mondulkiri</v>
       </c>
       <c r="G130" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="H130" t="str">
+        <v>Central Market Area, Mondulkiri</v>
+      </c>
+      <c r="I130" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J130" t="str">
         <v>093 103 277</v>
       </c>
     </row>
@@ -11410,12 +12221,18 @@
         <v>ខេត្តរតនគិរី</v>
       </c>
       <c r="F131" t="str">
-        <v>$</v>
+        <v>Ratanakiri</v>
       </c>
       <c r="G131" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តរតនគិរី</v>
       </c>
       <c r="H131" t="str">
+        <v>Central Market Area, Ratanakiri</v>
+      </c>
+      <c r="I131" t="str">
+        <v>$</v>
+      </c>
+      <c r="J131" t="str">
         <v>094 110 290</v>
       </c>
     </row>
@@ -11436,12 +12253,18 @@
         <v>ខេត្តក្រចេះ</v>
       </c>
       <c r="F132" t="str">
-        <v>$</v>
+        <v>Kratie</v>
       </c>
       <c r="G132" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តក្រចេះ</v>
       </c>
       <c r="H132" t="str">
+        <v>Central Market Area, Kratie</v>
+      </c>
+      <c r="I132" t="str">
+        <v>$</v>
+      </c>
+      <c r="J132" t="str">
         <v>095 117 303</v>
       </c>
     </row>
@@ -11462,12 +12285,18 @@
         <v>ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="F133" t="str">
-        <v>$$</v>
+        <v>Stung Treng</v>
       </c>
       <c r="G133" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="H133" t="str">
+        <v>Central Market Area, Stung Treng</v>
+      </c>
+      <c r="I133" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J133" t="str">
         <v>096 124 316</v>
       </c>
     </row>
@@ -11488,12 +12317,18 @@
         <v>ខេត្តព្រះវិហារ</v>
       </c>
       <c r="F134" t="str">
-        <v>$</v>
+        <v>Preah Vihear</v>
       </c>
       <c r="G134" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះវិហារ</v>
       </c>
       <c r="H134" t="str">
+        <v>Central Market Area, Preah Vihear</v>
+      </c>
+      <c r="I134" t="str">
+        <v>$</v>
+      </c>
+      <c r="J134" t="str">
         <v>097 131 329</v>
       </c>
     </row>
@@ -11514,12 +12349,18 @@
         <v>ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="F135" t="str">
-        <v>$</v>
+        <v>Banteay Meanchey</v>
       </c>
       <c r="G135" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="H135" t="str">
+        <v>Central Market Area, Banteay Meanchey</v>
+      </c>
+      <c r="I135" t="str">
+        <v>$</v>
+      </c>
+      <c r="J135" t="str">
         <v>098 138 342</v>
       </c>
     </row>
@@ -11540,12 +12381,18 @@
         <v>ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="F136" t="str">
-        <v>$$</v>
+        <v>Oddar Meanchey</v>
       </c>
       <c r="G136" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="H136" t="str">
+        <v>Central Market Area, Oddar Meanchey</v>
+      </c>
+      <c r="I136" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J136" t="str">
         <v>090 145 355</v>
       </c>
     </row>
@@ -11566,12 +12413,18 @@
         <v>ខេត្តប៉ៃលិន</v>
       </c>
       <c r="F137" t="str">
-        <v>$</v>
+        <v>Pailin</v>
       </c>
       <c r="G137" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តប៉ៃលិន</v>
       </c>
       <c r="H137" t="str">
+        <v>Central Market Area, Pailin</v>
+      </c>
+      <c r="I137" t="str">
+        <v>$</v>
+      </c>
+      <c r="J137" t="str">
         <v>091 152 368</v>
       </c>
     </row>
@@ -11592,12 +12445,18 @@
         <v>ខេត្តព្រៃវែង</v>
       </c>
       <c r="F138" t="str">
-        <v>$</v>
+        <v>Prey Veng</v>
       </c>
       <c r="G138" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រៃវែង</v>
       </c>
       <c r="H138" t="str">
+        <v>Central Market Area, Prey Veng</v>
+      </c>
+      <c r="I138" t="str">
+        <v>$</v>
+      </c>
+      <c r="J138" t="str">
         <v>092 159 381</v>
       </c>
     </row>
@@ -11618,12 +12477,18 @@
         <v>ខេត្តស្វាយរៀង</v>
       </c>
       <c r="F139" t="str">
-        <v>$$</v>
+        <v>Svay Rieng</v>
       </c>
       <c r="G139" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្វាយរៀង</v>
       </c>
       <c r="H139" t="str">
+        <v>Central Market Area, Svay Rieng</v>
+      </c>
+      <c r="I139" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J139" t="str">
         <v>093 166 394</v>
       </c>
     </row>
@@ -11644,12 +12509,18 @@
         <v>ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="F140" t="str">
-        <v>$</v>
+        <v>Kampong Speu</v>
       </c>
       <c r="G140" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="H140" t="str">
+        <v>Central Market Area, Kampong Speu</v>
+      </c>
+      <c r="I140" t="str">
+        <v>$</v>
+      </c>
+      <c r="J140" t="str">
         <v>094 173 407</v>
       </c>
     </row>
@@ -11670,12 +12541,18 @@
         <v>ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="F141" t="str">
-        <v>$</v>
+        <v>Tboung Khmum</v>
       </c>
       <c r="G141" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="H141" t="str">
+        <v>Central Market Area, Tboung Khmum</v>
+      </c>
+      <c r="I141" t="str">
+        <v>$</v>
+      </c>
+      <c r="J141" t="str">
         <v>095 180 420</v>
       </c>
     </row>
@@ -11696,12 +12573,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F142" t="str">
-        <v>$$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G142" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H142" t="str">
+        <v>Central Market Area, Phnom Penh</v>
+      </c>
+      <c r="I142" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J142" t="str">
         <v>096 187 433</v>
       </c>
     </row>
@@ -11722,12 +12605,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F143" t="str">
-        <v>$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G143" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តសៀមរាប</v>
       </c>
       <c r="H143" t="str">
+        <v>Central Market Area, Siem Reap</v>
+      </c>
+      <c r="I143" t="str">
+        <v>$</v>
+      </c>
+      <c r="J143" t="str">
         <v>097 194 446</v>
       </c>
     </row>
@@ -11748,12 +12637,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F144" t="str">
-        <v>$</v>
+        <v>Battambang</v>
       </c>
       <c r="G144" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបាត់ដំបង</v>
       </c>
       <c r="H144" t="str">
+        <v>Central Market Area, Battambang</v>
+      </c>
+      <c r="I144" t="str">
+        <v>$</v>
+      </c>
+      <c r="J144" t="str">
         <v>098 201 459</v>
       </c>
     </row>
@@ -11774,12 +12669,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F145" t="str">
-        <v>$$</v>
+        <v>Kampot</v>
       </c>
       <c r="G145" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពត</v>
       </c>
       <c r="H145" t="str">
+        <v>Central Market Area, Kampot</v>
+      </c>
+      <c r="I145" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J145" t="str">
         <v>090 208 472</v>
       </c>
     </row>
@@ -11800,12 +12701,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F146" t="str">
-        <v>$</v>
+        <v>Kep</v>
       </c>
       <c r="G146" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកែប</v>
       </c>
       <c r="H146" t="str">
+        <v>Central Market Area, Kep</v>
+      </c>
+      <c r="I146" t="str">
+        <v>$</v>
+      </c>
+      <c r="J146" t="str">
         <v>091 215 485</v>
       </c>
     </row>
@@ -11826,12 +12733,18 @@
         <v>ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="F147" t="str">
-        <v>$</v>
+        <v>Preah Sihanouk</v>
       </c>
       <c r="G147" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="H147" t="str">
+        <v>Central Market Area, Preah Sihanouk</v>
+      </c>
+      <c r="I147" t="str">
+        <v>$</v>
+      </c>
+      <c r="J147" t="str">
         <v>092 222 498</v>
       </c>
     </row>
@@ -11852,12 +12765,18 @@
         <v>ខេត្តកំពង់ចាម</v>
       </c>
       <c r="F148" t="str">
-        <v>$$</v>
+        <v>Kampong Cham</v>
       </c>
       <c r="G148" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ចាម</v>
       </c>
       <c r="H148" t="str">
+        <v>Central Market Area, Kampong Cham</v>
+      </c>
+      <c r="I148" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J148" t="str">
         <v>093 229 511</v>
       </c>
     </row>
@@ -11878,12 +12797,18 @@
         <v>ខេត្តកណ្តាល</v>
       </c>
       <c r="F149" t="str">
-        <v>$</v>
+        <v>Kandal</v>
       </c>
       <c r="G149" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកណ្តាល</v>
       </c>
       <c r="H149" t="str">
+        <v>Central Market Area, Kandal</v>
+      </c>
+      <c r="I149" t="str">
+        <v>$</v>
+      </c>
+      <c r="J149" t="str">
         <v>094 236 524</v>
       </c>
     </row>
@@ -11904,12 +12829,18 @@
         <v>ខេត្តតាកែវ</v>
       </c>
       <c r="F150" t="str">
-        <v>$</v>
+        <v>Takeo</v>
       </c>
       <c r="G150" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តតាកែវ</v>
       </c>
       <c r="H150" t="str">
+        <v>Central Market Area, Takeo</v>
+      </c>
+      <c r="I150" t="str">
+        <v>$</v>
+      </c>
+      <c r="J150" t="str">
         <v>095 243 537</v>
       </c>
     </row>
@@ -11930,12 +12861,18 @@
         <v>ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="F151" t="str">
-        <v>$$</v>
+        <v>Pursat</v>
       </c>
       <c r="G151" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="H151" t="str">
+        <v>Central Market Area, Pursat</v>
+      </c>
+      <c r="I151" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J151" t="str">
         <v>096 250 550</v>
       </c>
     </row>
@@ -11956,12 +12893,18 @@
         <v>ខេត្តកំពង់ធំ</v>
       </c>
       <c r="F152" t="str">
-        <v>$</v>
+        <v>Kampong Thom</v>
       </c>
       <c r="G152" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ធំ</v>
       </c>
       <c r="H152" t="str">
+        <v>Central Market Area, Kampong Thom</v>
+      </c>
+      <c r="I152" t="str">
+        <v>$</v>
+      </c>
+      <c r="J152" t="str">
         <v>097 257 563</v>
       </c>
     </row>
@@ -11982,12 +12925,18 @@
         <v>ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="F153" t="str">
-        <v>$</v>
+        <v>Kampong Chhnang</v>
       </c>
       <c r="G153" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="H153" t="str">
+        <v>Central Market Area, Kampong Chhnang</v>
+      </c>
+      <c r="I153" t="str">
+        <v>$</v>
+      </c>
+      <c r="J153" t="str">
         <v>098 264 576</v>
       </c>
     </row>
@@ -12008,12 +12957,18 @@
         <v>ខេត្តកោះកុង</v>
       </c>
       <c r="F154" t="str">
-        <v>$$</v>
+        <v>Koh Kong</v>
       </c>
       <c r="G154" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកោះកុង</v>
       </c>
       <c r="H154" t="str">
+        <v>Central Market Area, Koh Kong</v>
+      </c>
+      <c r="I154" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J154" t="str">
         <v>090 271 589</v>
       </c>
     </row>
@@ -12034,12 +12989,18 @@
         <v>ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="F155" t="str">
-        <v>$</v>
+        <v>Mondulkiri</v>
       </c>
       <c r="G155" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="H155" t="str">
+        <v>Central Market Area, Mondulkiri</v>
+      </c>
+      <c r="I155" t="str">
+        <v>$</v>
+      </c>
+      <c r="J155" t="str">
         <v>091 278 602</v>
       </c>
     </row>
@@ -12060,12 +13021,18 @@
         <v>ខេត្តរតនគិរី</v>
       </c>
       <c r="F156" t="str">
-        <v>$</v>
+        <v>Ratanakiri</v>
       </c>
       <c r="G156" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តរតនគិរី</v>
       </c>
       <c r="H156" t="str">
+        <v>Central Market Area, Ratanakiri</v>
+      </c>
+      <c r="I156" t="str">
+        <v>$</v>
+      </c>
+      <c r="J156" t="str">
         <v>092 285 615</v>
       </c>
     </row>
@@ -12086,12 +13053,18 @@
         <v>ខេត្តក្រចេះ</v>
       </c>
       <c r="F157" t="str">
-        <v>$$</v>
+        <v>Kratie</v>
       </c>
       <c r="G157" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តក្រចេះ</v>
       </c>
       <c r="H157" t="str">
+        <v>Central Market Area, Kratie</v>
+      </c>
+      <c r="I157" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J157" t="str">
         <v>093 292 628</v>
       </c>
     </row>
@@ -12112,12 +13085,18 @@
         <v>ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="F158" t="str">
-        <v>$</v>
+        <v>Stung Treng</v>
       </c>
       <c r="G158" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="H158" t="str">
+        <v>Central Market Area, Stung Treng</v>
+      </c>
+      <c r="I158" t="str">
+        <v>$</v>
+      </c>
+      <c r="J158" t="str">
         <v>094 299 641</v>
       </c>
     </row>
@@ -12138,12 +13117,18 @@
         <v>ខេត្តព្រះវិហារ</v>
       </c>
       <c r="F159" t="str">
-        <v>$</v>
+        <v>Preah Vihear</v>
       </c>
       <c r="G159" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះវិហារ</v>
       </c>
       <c r="H159" t="str">
+        <v>Central Market Area, Preah Vihear</v>
+      </c>
+      <c r="I159" t="str">
+        <v>$</v>
+      </c>
+      <c r="J159" t="str">
         <v>095 306 654</v>
       </c>
     </row>
@@ -12164,12 +13149,18 @@
         <v>ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="F160" t="str">
-        <v>$$</v>
+        <v>Banteay Meanchey</v>
       </c>
       <c r="G160" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="H160" t="str">
+        <v>Central Market Area, Banteay Meanchey</v>
+      </c>
+      <c r="I160" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J160" t="str">
         <v>096 313 667</v>
       </c>
     </row>
@@ -12190,12 +13181,18 @@
         <v>ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="F161" t="str">
-        <v>$</v>
+        <v>Oddar Meanchey</v>
       </c>
       <c r="G161" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="H161" t="str">
+        <v>Central Market Area, Oddar Meanchey</v>
+      </c>
+      <c r="I161" t="str">
+        <v>$</v>
+      </c>
+      <c r="J161" t="str">
         <v>097 320 680</v>
       </c>
     </row>
@@ -12216,12 +13213,18 @@
         <v>ខេត្តប៉ៃលិន</v>
       </c>
       <c r="F162" t="str">
-        <v>$</v>
+        <v>Pailin</v>
       </c>
       <c r="G162" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តប៉ៃលិន</v>
       </c>
       <c r="H162" t="str">
+        <v>Central Market Area, Pailin</v>
+      </c>
+      <c r="I162" t="str">
+        <v>$</v>
+      </c>
+      <c r="J162" t="str">
         <v>098 327 693</v>
       </c>
     </row>
@@ -12242,12 +13245,18 @@
         <v>ខេត្តព្រៃវែង</v>
       </c>
       <c r="F163" t="str">
-        <v>$$</v>
+        <v>Prey Veng</v>
       </c>
       <c r="G163" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រៃវែង</v>
       </c>
       <c r="H163" t="str">
+        <v>Central Market Area, Prey Veng</v>
+      </c>
+      <c r="I163" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J163" t="str">
         <v>090 334 706</v>
       </c>
     </row>
@@ -12268,12 +13277,18 @@
         <v>ខេត្តស្វាយរៀង</v>
       </c>
       <c r="F164" t="str">
-        <v>$</v>
+        <v>Svay Rieng</v>
       </c>
       <c r="G164" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្វាយរៀង</v>
       </c>
       <c r="H164" t="str">
+        <v>Central Market Area, Svay Rieng</v>
+      </c>
+      <c r="I164" t="str">
+        <v>$</v>
+      </c>
+      <c r="J164" t="str">
         <v>091 341 719</v>
       </c>
     </row>
@@ -12294,12 +13309,18 @@
         <v>ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="F165" t="str">
-        <v>$</v>
+        <v>Kampong Speu</v>
       </c>
       <c r="G165" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="H165" t="str">
+        <v>Central Market Area, Kampong Speu</v>
+      </c>
+      <c r="I165" t="str">
+        <v>$</v>
+      </c>
+      <c r="J165" t="str">
         <v>092 348 732</v>
       </c>
     </row>
@@ -12320,12 +13341,18 @@
         <v>ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="F166" t="str">
-        <v>$$</v>
+        <v>Tboung Khmum</v>
       </c>
       <c r="G166" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="H166" t="str">
+        <v>Central Market Area, Tboung Khmum</v>
+      </c>
+      <c r="I166" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J166" t="str">
         <v>093 355 745</v>
       </c>
     </row>
@@ -12346,12 +13373,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F167" t="str">
-        <v>$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G167" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H167" t="str">
+        <v>Central Market Area, Phnom Penh</v>
+      </c>
+      <c r="I167" t="str">
+        <v>$</v>
+      </c>
+      <c r="J167" t="str">
         <v>094 362 758</v>
       </c>
     </row>
@@ -12372,12 +13405,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F168" t="str">
-        <v>$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G168" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តសៀមរាប</v>
       </c>
       <c r="H168" t="str">
+        <v>Central Market Area, Siem Reap</v>
+      </c>
+      <c r="I168" t="str">
+        <v>$</v>
+      </c>
+      <c r="J168" t="str">
         <v>095 369 771</v>
       </c>
     </row>
@@ -12398,12 +13437,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F169" t="str">
-        <v>$$</v>
+        <v>Battambang</v>
       </c>
       <c r="G169" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបាត់ដំបង</v>
       </c>
       <c r="H169" t="str">
+        <v>Central Market Area, Battambang</v>
+      </c>
+      <c r="I169" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J169" t="str">
         <v>096 376 784</v>
       </c>
     </row>
@@ -12424,12 +13469,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F170" t="str">
-        <v>$</v>
+        <v>Kampot</v>
       </c>
       <c r="G170" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពត</v>
       </c>
       <c r="H170" t="str">
+        <v>Central Market Area, Kampot</v>
+      </c>
+      <c r="I170" t="str">
+        <v>$</v>
+      </c>
+      <c r="J170" t="str">
         <v>097 383 797</v>
       </c>
     </row>
@@ -12450,12 +13501,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F171" t="str">
-        <v>$</v>
+        <v>Kep</v>
       </c>
       <c r="G171" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកែប</v>
       </c>
       <c r="H171" t="str">
+        <v>Central Market Area, Kep</v>
+      </c>
+      <c r="I171" t="str">
+        <v>$</v>
+      </c>
+      <c r="J171" t="str">
         <v>098 390 810</v>
       </c>
     </row>
@@ -12476,12 +13533,18 @@
         <v>ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="F172" t="str">
-        <v>$$</v>
+        <v>Preah Sihanouk</v>
       </c>
       <c r="G172" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="H172" t="str">
+        <v>Central Market Area, Preah Sihanouk</v>
+      </c>
+      <c r="I172" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J172" t="str">
         <v>090 397 823</v>
       </c>
     </row>
@@ -12502,12 +13565,18 @@
         <v>ខេត្តកំពង់ចាម</v>
       </c>
       <c r="F173" t="str">
-        <v>$</v>
+        <v>Kampong Cham</v>
       </c>
       <c r="G173" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ចាម</v>
       </c>
       <c r="H173" t="str">
+        <v>Central Market Area, Kampong Cham</v>
+      </c>
+      <c r="I173" t="str">
+        <v>$</v>
+      </c>
+      <c r="J173" t="str">
         <v>091 404 836</v>
       </c>
     </row>
@@ -12528,12 +13597,18 @@
         <v>ខេត្តកណ្តាល</v>
       </c>
       <c r="F174" t="str">
-        <v>$</v>
+        <v>Kandal</v>
       </c>
       <c r="G174" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកណ្តាល</v>
       </c>
       <c r="H174" t="str">
+        <v>Central Market Area, Kandal</v>
+      </c>
+      <c r="I174" t="str">
+        <v>$</v>
+      </c>
+      <c r="J174" t="str">
         <v>092 411 849</v>
       </c>
     </row>
@@ -12554,12 +13629,18 @@
         <v>ខេត្តតាកែវ</v>
       </c>
       <c r="F175" t="str">
-        <v>$$</v>
+        <v>Takeo</v>
       </c>
       <c r="G175" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តតាកែវ</v>
       </c>
       <c r="H175" t="str">
+        <v>Central Market Area, Takeo</v>
+      </c>
+      <c r="I175" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J175" t="str">
         <v>093 418 862</v>
       </c>
     </row>
@@ -12580,12 +13661,18 @@
         <v>ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="F176" t="str">
-        <v>$</v>
+        <v>Pursat</v>
       </c>
       <c r="G176" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="H176" t="str">
+        <v>Central Market Area, Pursat</v>
+      </c>
+      <c r="I176" t="str">
+        <v>$</v>
+      </c>
+      <c r="J176" t="str">
         <v>094 425 875</v>
       </c>
     </row>
@@ -12606,12 +13693,18 @@
         <v>ខេត្តកំពង់ធំ</v>
       </c>
       <c r="F177" t="str">
-        <v>$</v>
+        <v>Kampong Thom</v>
       </c>
       <c r="G177" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ធំ</v>
       </c>
       <c r="H177" t="str">
+        <v>Central Market Area, Kampong Thom</v>
+      </c>
+      <c r="I177" t="str">
+        <v>$</v>
+      </c>
+      <c r="J177" t="str">
         <v>095 432 888</v>
       </c>
     </row>
@@ -12632,12 +13725,18 @@
         <v>ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="F178" t="str">
-        <v>$$</v>
+        <v>Kampong Chhnang</v>
       </c>
       <c r="G178" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="H178" t="str">
+        <v>Central Market Area, Kampong Chhnang</v>
+      </c>
+      <c r="I178" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J178" t="str">
         <v>096 439 901</v>
       </c>
     </row>
@@ -12658,12 +13757,18 @@
         <v>ខេត្តកោះកុង</v>
       </c>
       <c r="F179" t="str">
-        <v>$</v>
+        <v>Koh Kong</v>
       </c>
       <c r="G179" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកោះកុង</v>
       </c>
       <c r="H179" t="str">
+        <v>Central Market Area, Koh Kong</v>
+      </c>
+      <c r="I179" t="str">
+        <v>$</v>
+      </c>
+      <c r="J179" t="str">
         <v>097 446 914</v>
       </c>
     </row>
@@ -12684,12 +13789,18 @@
         <v>ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="F180" t="str">
-        <v>$</v>
+        <v>Mondulkiri</v>
       </c>
       <c r="G180" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="H180" t="str">
+        <v>Central Market Area, Mondulkiri</v>
+      </c>
+      <c r="I180" t="str">
+        <v>$</v>
+      </c>
+      <c r="J180" t="str">
         <v>098 453 927</v>
       </c>
     </row>
@@ -12710,12 +13821,18 @@
         <v>ខេត្តរតនគិរី</v>
       </c>
       <c r="F181" t="str">
-        <v>$$</v>
+        <v>Ratanakiri</v>
       </c>
       <c r="G181" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តរតនគិរី</v>
       </c>
       <c r="H181" t="str">
+        <v>Central Market Area, Ratanakiri</v>
+      </c>
+      <c r="I181" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J181" t="str">
         <v>090 460 940</v>
       </c>
     </row>
@@ -12736,12 +13853,18 @@
         <v>ខេត្តក្រចេះ</v>
       </c>
       <c r="F182" t="str">
-        <v>$</v>
+        <v>Kratie</v>
       </c>
       <c r="G182" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តក្រចេះ</v>
       </c>
       <c r="H182" t="str">
+        <v>Central Market Area, Kratie</v>
+      </c>
+      <c r="I182" t="str">
+        <v>$</v>
+      </c>
+      <c r="J182" t="str">
         <v>091 467 953</v>
       </c>
     </row>
@@ -12762,12 +13885,18 @@
         <v>ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="F183" t="str">
-        <v>$</v>
+        <v>Stung Treng</v>
       </c>
       <c r="G183" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="H183" t="str">
+        <v>Central Market Area, Stung Treng</v>
+      </c>
+      <c r="I183" t="str">
+        <v>$</v>
+      </c>
+      <c r="J183" t="str">
         <v>092 474 966</v>
       </c>
     </row>
@@ -12788,12 +13917,18 @@
         <v>ខេត្តព្រះវិហារ</v>
       </c>
       <c r="F184" t="str">
-        <v>$$</v>
+        <v>Preah Vihear</v>
       </c>
       <c r="G184" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះវិហារ</v>
       </c>
       <c r="H184" t="str">
+        <v>Central Market Area, Preah Vihear</v>
+      </c>
+      <c r="I184" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J184" t="str">
         <v>093 481 979</v>
       </c>
     </row>
@@ -12814,12 +13949,18 @@
         <v>ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="F185" t="str">
-        <v>$</v>
+        <v>Banteay Meanchey</v>
       </c>
       <c r="G185" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="H185" t="str">
+        <v>Central Market Area, Banteay Meanchey</v>
+      </c>
+      <c r="I185" t="str">
+        <v>$</v>
+      </c>
+      <c r="J185" t="str">
         <v>094 488 992</v>
       </c>
     </row>
@@ -12840,12 +13981,18 @@
         <v>ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="F186" t="str">
-        <v>$</v>
+        <v>Oddar Meanchey</v>
       </c>
       <c r="G186" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="H186" t="str">
+        <v>Central Market Area, Oddar Meanchey</v>
+      </c>
+      <c r="I186" t="str">
+        <v>$</v>
+      </c>
+      <c r="J186" t="str">
         <v>095 495 205</v>
       </c>
     </row>
@@ -12866,12 +14013,18 @@
         <v>ខេត្តប៉ៃលិន</v>
       </c>
       <c r="F187" t="str">
-        <v>$$</v>
+        <v>Pailin</v>
       </c>
       <c r="G187" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តប៉ៃលិន</v>
       </c>
       <c r="H187" t="str">
+        <v>Central Market Area, Pailin</v>
+      </c>
+      <c r="I187" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J187" t="str">
         <v>096 502 218</v>
       </c>
     </row>
@@ -12892,12 +14045,18 @@
         <v>ខេត្តព្រៃវែង</v>
       </c>
       <c r="F188" t="str">
-        <v>$</v>
+        <v>Prey Veng</v>
       </c>
       <c r="G188" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រៃវែង</v>
       </c>
       <c r="H188" t="str">
+        <v>Central Market Area, Prey Veng</v>
+      </c>
+      <c r="I188" t="str">
+        <v>$</v>
+      </c>
+      <c r="J188" t="str">
         <v>097 509 231</v>
       </c>
     </row>
@@ -12918,12 +14077,18 @@
         <v>ខេត្តស្វាយរៀង</v>
       </c>
       <c r="F189" t="str">
-        <v>$</v>
+        <v>Svay Rieng</v>
       </c>
       <c r="G189" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្វាយរៀង</v>
       </c>
       <c r="H189" t="str">
+        <v>Central Market Area, Svay Rieng</v>
+      </c>
+      <c r="I189" t="str">
+        <v>$</v>
+      </c>
+      <c r="J189" t="str">
         <v>098 516 244</v>
       </c>
     </row>
@@ -12944,12 +14109,18 @@
         <v>ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="F190" t="str">
-        <v>$$</v>
+        <v>Kampong Speu</v>
       </c>
       <c r="G190" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="H190" t="str">
+        <v>Central Market Area, Kampong Speu</v>
+      </c>
+      <c r="I190" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J190" t="str">
         <v>090 523 257</v>
       </c>
     </row>
@@ -12970,12 +14141,18 @@
         <v>ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="F191" t="str">
-        <v>$</v>
+        <v>Tboung Khmum</v>
       </c>
       <c r="G191" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="H191" t="str">
+        <v>Central Market Area, Tboung Khmum</v>
+      </c>
+      <c r="I191" t="str">
+        <v>$</v>
+      </c>
+      <c r="J191" t="str">
         <v>091 530 270</v>
       </c>
     </row>
@@ -12996,12 +14173,18 @@
         <v>រាជធានីភ្នំពេញ</v>
       </c>
       <c r="F192" t="str">
-        <v>$</v>
+        <v>Phnom Penh</v>
       </c>
       <c r="G192" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ រាជធានីភ្នំពេញ</v>
       </c>
       <c r="H192" t="str">
+        <v>Central Market Area, Phnom Penh</v>
+      </c>
+      <c r="I192" t="str">
+        <v>$</v>
+      </c>
+      <c r="J192" t="str">
         <v>092 537 283</v>
       </c>
     </row>
@@ -13022,12 +14205,18 @@
         <v>ខេត្តសៀមរាប</v>
       </c>
       <c r="F193" t="str">
-        <v>$$</v>
+        <v>Siem Reap</v>
       </c>
       <c r="G193" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តសៀមរាប</v>
       </c>
       <c r="H193" t="str">
+        <v>Central Market Area, Siem Reap</v>
+      </c>
+      <c r="I193" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J193" t="str">
         <v>093 544 296</v>
       </c>
     </row>
@@ -13048,12 +14237,18 @@
         <v>ខេត្តបាត់ដំបង</v>
       </c>
       <c r="F194" t="str">
-        <v>$</v>
+        <v>Battambang</v>
       </c>
       <c r="G194" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបាត់ដំបង</v>
       </c>
       <c r="H194" t="str">
+        <v>Central Market Area, Battambang</v>
+      </c>
+      <c r="I194" t="str">
+        <v>$</v>
+      </c>
+      <c r="J194" t="str">
         <v>094 551 309</v>
       </c>
     </row>
@@ -13074,12 +14269,18 @@
         <v>ខេត្តកំពត</v>
       </c>
       <c r="F195" t="str">
-        <v>$</v>
+        <v>Kampot</v>
       </c>
       <c r="G195" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពត</v>
       </c>
       <c r="H195" t="str">
+        <v>Central Market Area, Kampot</v>
+      </c>
+      <c r="I195" t="str">
+        <v>$</v>
+      </c>
+      <c r="J195" t="str">
         <v>095 558 322</v>
       </c>
     </row>
@@ -13100,12 +14301,18 @@
         <v>ខេត្តកែប</v>
       </c>
       <c r="F196" t="str">
-        <v>$$</v>
+        <v>Kep</v>
       </c>
       <c r="G196" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកែប</v>
       </c>
       <c r="H196" t="str">
+        <v>Central Market Area, Kep</v>
+      </c>
+      <c r="I196" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J196" t="str">
         <v>096 565 335</v>
       </c>
     </row>
@@ -13126,12 +14333,18 @@
         <v>ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="F197" t="str">
-        <v>$</v>
+        <v>Preah Sihanouk</v>
       </c>
       <c r="G197" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះសីហនុ</v>
       </c>
       <c r="H197" t="str">
+        <v>Central Market Area, Preah Sihanouk</v>
+      </c>
+      <c r="I197" t="str">
+        <v>$</v>
+      </c>
+      <c r="J197" t="str">
         <v>097 572 348</v>
       </c>
     </row>
@@ -13152,12 +14365,18 @@
         <v>ខេត្តកំពង់ចាម</v>
       </c>
       <c r="F198" t="str">
-        <v>$</v>
+        <v>Kampong Cham</v>
       </c>
       <c r="G198" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ចាម</v>
       </c>
       <c r="H198" t="str">
+        <v>Central Market Area, Kampong Cham</v>
+      </c>
+      <c r="I198" t="str">
+        <v>$</v>
+      </c>
+      <c r="J198" t="str">
         <v>098 579 361</v>
       </c>
     </row>
@@ -13178,12 +14397,18 @@
         <v>ខេត្តកណ្តាល</v>
       </c>
       <c r="F199" t="str">
-        <v>$$</v>
+        <v>Kandal</v>
       </c>
       <c r="G199" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកណ្តាល</v>
       </c>
       <c r="H199" t="str">
+        <v>Central Market Area, Kandal</v>
+      </c>
+      <c r="I199" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J199" t="str">
         <v>090 586 374</v>
       </c>
     </row>
@@ -13204,12 +14429,18 @@
         <v>ខេត្តតាកែវ</v>
       </c>
       <c r="F200" t="str">
-        <v>$</v>
+        <v>Takeo</v>
       </c>
       <c r="G200" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តតាកែវ</v>
       </c>
       <c r="H200" t="str">
+        <v>Central Market Area, Takeo</v>
+      </c>
+      <c r="I200" t="str">
+        <v>$</v>
+      </c>
+      <c r="J200" t="str">
         <v>091 593 387</v>
       </c>
     </row>
@@ -13230,12 +14461,18 @@
         <v>ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="F201" t="str">
-        <v>$</v>
+        <v>Pursat</v>
       </c>
       <c r="G201" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តពោធិ៍សាត់</v>
       </c>
       <c r="H201" t="str">
+        <v>Central Market Area, Pursat</v>
+      </c>
+      <c r="I201" t="str">
+        <v>$</v>
+      </c>
+      <c r="J201" t="str">
         <v>092 600 400</v>
       </c>
     </row>
@@ -13256,12 +14493,18 @@
         <v>ខេត្តកំពង់ធំ</v>
       </c>
       <c r="F202" t="str">
-        <v>$$</v>
+        <v>Kampong Thom</v>
       </c>
       <c r="G202" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ធំ</v>
       </c>
       <c r="H202" t="str">
+        <v>Central Market Area, Kampong Thom</v>
+      </c>
+      <c r="I202" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J202" t="str">
         <v>093 607 413</v>
       </c>
     </row>
@@ -13282,12 +14525,18 @@
         <v>ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="F203" t="str">
-        <v>$</v>
+        <v>Kampong Chhnang</v>
       </c>
       <c r="G203" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ឆ្នាំង</v>
       </c>
       <c r="H203" t="str">
+        <v>Central Market Area, Kampong Chhnang</v>
+      </c>
+      <c r="I203" t="str">
+        <v>$</v>
+      </c>
+      <c r="J203" t="str">
         <v>094 614 426</v>
       </c>
     </row>
@@ -13308,12 +14557,18 @@
         <v>ខេត្តកោះកុង</v>
       </c>
       <c r="F204" t="str">
-        <v>$</v>
+        <v>Koh Kong</v>
       </c>
       <c r="G204" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកោះកុង</v>
       </c>
       <c r="H204" t="str">
+        <v>Central Market Area, Koh Kong</v>
+      </c>
+      <c r="I204" t="str">
+        <v>$</v>
+      </c>
+      <c r="J204" t="str">
         <v>095 621 439</v>
       </c>
     </row>
@@ -13334,12 +14589,18 @@
         <v>ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="F205" t="str">
-        <v>$$</v>
+        <v>Mondulkiri</v>
       </c>
       <c r="G205" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តមណ្ឌលគិរី</v>
       </c>
       <c r="H205" t="str">
+        <v>Central Market Area, Mondulkiri</v>
+      </c>
+      <c r="I205" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J205" t="str">
         <v>096 628 452</v>
       </c>
     </row>
@@ -13360,12 +14621,18 @@
         <v>ខេត្តរតនគិរី</v>
       </c>
       <c r="F206" t="str">
-        <v>$</v>
+        <v>Ratanakiri</v>
       </c>
       <c r="G206" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តរតនគិរី</v>
       </c>
       <c r="H206" t="str">
+        <v>Central Market Area, Ratanakiri</v>
+      </c>
+      <c r="I206" t="str">
+        <v>$</v>
+      </c>
+      <c r="J206" t="str">
         <v>097 635 465</v>
       </c>
     </row>
@@ -13386,12 +14653,18 @@
         <v>ខេត្តក្រចេះ</v>
       </c>
       <c r="F207" t="str">
-        <v>$</v>
+        <v>Kratie</v>
       </c>
       <c r="G207" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តក្រចេះ</v>
       </c>
       <c r="H207" t="str">
+        <v>Central Market Area, Kratie</v>
+      </c>
+      <c r="I207" t="str">
+        <v>$</v>
+      </c>
+      <c r="J207" t="str">
         <v>098 642 478</v>
       </c>
     </row>
@@ -13412,12 +14685,18 @@
         <v>ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="F208" t="str">
-        <v>$$</v>
+        <v>Stung Treng</v>
       </c>
       <c r="G208" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្ទឹងត្រែង</v>
       </c>
       <c r="H208" t="str">
+        <v>Central Market Area, Stung Treng</v>
+      </c>
+      <c r="I208" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J208" t="str">
         <v>090 649 491</v>
       </c>
     </row>
@@ -13438,12 +14717,18 @@
         <v>ខេត្តព្រះវិហារ</v>
       </c>
       <c r="F209" t="str">
-        <v>$</v>
+        <v>Preah Vihear</v>
       </c>
       <c r="G209" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រះវិហារ</v>
       </c>
       <c r="H209" t="str">
+        <v>Central Market Area, Preah Vihear</v>
+      </c>
+      <c r="I209" t="str">
+        <v>$</v>
+      </c>
+      <c r="J209" t="str">
         <v>091 656 504</v>
       </c>
     </row>
@@ -13464,12 +14749,18 @@
         <v>ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="F210" t="str">
-        <v>$</v>
+        <v>Banteay Meanchey</v>
       </c>
       <c r="G210" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តបន្ទាយមានជ័យ</v>
       </c>
       <c r="H210" t="str">
+        <v>Central Market Area, Banteay Meanchey</v>
+      </c>
+      <c r="I210" t="str">
+        <v>$</v>
+      </c>
+      <c r="J210" t="str">
         <v>092 663 517</v>
       </c>
     </row>
@@ -13490,12 +14781,18 @@
         <v>ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="F211" t="str">
-        <v>$$</v>
+        <v>Oddar Meanchey</v>
       </c>
       <c r="G211" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តឧត្តរមានជ័យ</v>
       </c>
       <c r="H211" t="str">
+        <v>Central Market Area, Oddar Meanchey</v>
+      </c>
+      <c r="I211" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J211" t="str">
         <v>093 670 530</v>
       </c>
     </row>
@@ -13516,12 +14813,18 @@
         <v>ខេត្តប៉ៃលិន</v>
       </c>
       <c r="F212" t="str">
-        <v>$</v>
+        <v>Pailin</v>
       </c>
       <c r="G212" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តប៉ៃលិន</v>
       </c>
       <c r="H212" t="str">
+        <v>Central Market Area, Pailin</v>
+      </c>
+      <c r="I212" t="str">
+        <v>$</v>
+      </c>
+      <c r="J212" t="str">
         <v>094 677 543</v>
       </c>
     </row>
@@ -13542,12 +14845,18 @@
         <v>ខេត្តព្រៃវែង</v>
       </c>
       <c r="F213" t="str">
-        <v>$</v>
+        <v>Prey Veng</v>
       </c>
       <c r="G213" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តព្រៃវែង</v>
       </c>
       <c r="H213" t="str">
+        <v>Central Market Area, Prey Veng</v>
+      </c>
+      <c r="I213" t="str">
+        <v>$</v>
+      </c>
+      <c r="J213" t="str">
         <v>095 684 556</v>
       </c>
     </row>
@@ -13568,12 +14877,18 @@
         <v>ខេត្តស្វាយរៀង</v>
       </c>
       <c r="F214" t="str">
-        <v>$$</v>
+        <v>Svay Rieng</v>
       </c>
       <c r="G214" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តស្វាយរៀង</v>
       </c>
       <c r="H214" t="str">
+        <v>Central Market Area, Svay Rieng</v>
+      </c>
+      <c r="I214" t="str">
+        <v>$$</v>
+      </c>
+      <c r="J214" t="str">
         <v>096 691 569</v>
       </c>
     </row>
@@ -13594,12 +14909,18 @@
         <v>ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="F215" t="str">
-        <v>$</v>
+        <v>Kampong Speu</v>
       </c>
       <c r="G215" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តកំពង់ស្ពឺ</v>
       </c>
       <c r="H215" t="str">
+        <v>Central Market Area, Kampong Speu</v>
+      </c>
+      <c r="I215" t="str">
+        <v>$</v>
+      </c>
+      <c r="J215" t="str">
         <v>097 698 582</v>
       </c>
     </row>
@@ -13620,18 +14941,3526 @@
         <v>ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="F216" t="str">
-        <v>$</v>
+        <v>Tboung Khmum</v>
       </c>
       <c r="G216" t="str">
         <v>ភូមិកណ្តាល ឃុំ/សង្កាត់ទីផ្សារ ខេត្តត្បូងឃ្មុំ</v>
       </c>
       <c r="H216" t="str">
+        <v>Central Market Area, Tboung Khmum</v>
+      </c>
+      <c r="I216" t="str">
+        <v>$</v>
+      </c>
+      <c r="J216" t="str">
         <v>098 705 595</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H216"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J216"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I120"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="45.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ល.រ (No)</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Destination ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>ឈ្មោះកន្លែងទេសចរណ៍ (Khmer Name)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>ឈ្មោះជាភាសាអង់គ្លេស (English Name)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ប្រភេទកន្លែង (Category)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ខេត្ត/រាជធានី (Province/City)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>អាសយដ្ឋាន (Address)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>តម្លៃសំបុត្រ/ចូលទស្សនា (Entrance Fee)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>ពេលវេលាល្អសម្រាប់ដើរលេង (Best Time)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>dest-1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ព្រះបរមរាជវាំង និងវត្តព្រះកែវមរកត</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Royal Palace &amp; Silver Pagoda</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F2" t="str">
+        <v>រាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="G2" t="str">
+        <v>មហាវិថីព្រះសុធារស សង្កាត់ជ័យជំនះ ខណ្ឌដូនពេញ</v>
+      </c>
+      <c r="H2" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $10)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៨:០០ - ១១:០០</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>dest-2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>សារមន្ទីរជាតិកម្ពុជា</v>
+      </c>
+      <c r="D3" t="str">
+        <v>National Museum of Cambodia</v>
+      </c>
+      <c r="E3" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F3" t="str">
+        <v>រាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="G3" t="str">
+        <v>ផ្លូវលេខ ១៣ ក្បែរព្រះបរមរាជវាំង សង្កាត់ជ័យជំនះ</v>
+      </c>
+      <c r="H3" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $10)</v>
+      </c>
+      <c r="I3" t="str">
+        <v>ពេញមួយឆ្នាំ ម៉ោង ០៨:០០ - ១៧:០០</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>dest-3</v>
+      </c>
+      <c r="C4" t="str">
+        <v>រមណីយដ្ឋានប្រវត្តិសាស្ត្រវត្តភ្នំដូនពេញ</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Wat Phnom Historical Sanctuary</v>
+      </c>
+      <c r="E4" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F4" t="str">
+        <v>រាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="G4" t="str">
+        <v>រង្វង់មូលវត្តភ្នំ សង្កាត់វត្តភ្នំ ខណ្ឌដូនពេញ</v>
+      </c>
+      <c r="H4" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $1)</v>
+      </c>
+      <c r="I4" t="str">
+        <v>ពេលព្រឹក ឬពេលរសៀលត្រជាក់</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>dest-4</v>
+      </c>
+      <c r="C5" t="str">
+        <v>វិមានឯករាជ្យ និងសួនសម្តេចព្រះសង្ឃរាជ ជួន ណាត</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Independence Monument &amp; Park</v>
+      </c>
+      <c r="E5" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F5" t="str">
+        <v>រាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="G5" t="str">
+        <v>ប្រសព្វមហាវិថីព្រះនរោត្តម និងមហាវិថីព្រះសីហនុ</v>
+      </c>
+      <c r="H5" t="str">
+        <v>ឥតគិតថ្លៃ (ទីធ្លាសាធារណៈ)</v>
+      </c>
+      <c r="I5" t="str">
+        <v>ពេលល្ងាច ម៉ោង ១៧:៣០ ដល់ ២០:០០</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>dest-5</v>
+      </c>
+      <c r="C6" t="str">
+        <v>តំបន់មាត់ទន្លេចតុមុខ និងផ្សាររាត្រីភ្នំពេញ</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Phnom Penh Riverside &amp; Night Market</v>
+      </c>
+      <c r="E6" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F6" t="str">
+        <v>រាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="G6" t="str">
+        <v>តីរវិថីព្រះស៊ីសុវត្ថិ មាត់ទន្លេ ខណ្ឌដូនពេញ</v>
+      </c>
+      <c r="H6" t="str">
+        <v>ឥតគិតថ្លៃដើរលេង (ជិះទូក $5-$10)</v>
+      </c>
+      <c r="I6" t="str">
+        <v>ពេលរសៀល និងពេលរាត្រី</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>dest-6</v>
+      </c>
+      <c r="C7" t="str">
+        <v>សារមន្ទីរឧក្រិដ្ឋកម្មប្រល័យពូជសាសន៍ទួលស្លែង</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Tuol Sleng Genocide Museum (S-21)</v>
+      </c>
+      <c r="E7" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F7" t="str">
+        <v>រាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="G7" t="str">
+        <v>ផ្លូវលេខ ១១៣ សង្កាត់បឹងកេងកង៣ ខណ្ឌបឹងកេងកង</v>
+      </c>
+      <c r="H7" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $5, កាសស្តាប់ $3)</v>
+      </c>
+      <c r="I7" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៨:០០ ដល់ ១១:០០</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>dest-7</v>
+      </c>
+      <c r="C8" t="str">
+        <v>មជ្ឈមណ្ឌលប្រល័យពូជសាសន៍ជើងឯក</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Choeung Ek Genocidal Center</v>
+      </c>
+      <c r="E8" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F8" t="str">
+        <v>រាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="G8" t="str">
+        <v>ភូមិរលួស សង្កាត់ជើងឯក ខណ្ឌដង្កោ</v>
+      </c>
+      <c r="H8" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $6)</v>
+      </c>
+      <c r="I8" t="str">
+        <v>ពេលព្រឹកព្រលឹម</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>dest-8</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ផ្សារធំថ្មី (ស្ថាបត្យកម្មដំបូលមូលបុរាណ)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Central Market (Phsar Thmey)</v>
+      </c>
+      <c r="E9" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F9" t="str">
+        <v>រាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="G9" t="str">
+        <v>វិថីកាល់ម៉ែត សង្កាត់ផ្សារថ្មីទី១ ខណ្ឌដូនពេញ</v>
+      </c>
+      <c r="H9" t="str">
+        <v>ឥតគិតថ្លៃចូលទស្សនា</v>
+      </c>
+      <c r="I9" t="str">
+        <v>ម៉ោង ០៨:០០ ដល់ ១៥:០០</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>dest-9</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ប្រាសាទអង្គរវត្តដ៏អស្ចារ្យ</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Majestic Angkor Wat Temple</v>
+      </c>
+      <c r="E10" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F10" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G10" t="str">
+        <v>រមណីយដ្ឋានអង្គរ ក្រុងសៀមរាប</v>
+      </c>
+      <c r="H10" t="str">
+        <v>ឥតគិតថ្លៃសម្រាប់ជនជាតិខ្មែរ (បរទេស $37/ថ្ងៃ)</v>
+      </c>
+      <c r="I10" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែមីនា (វេលាថ្ងៃរះ ម៉ោង ០៥:០០ ព្រឹក)</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>dest-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ប្រាសាទបាយ័ន (ស្នាមញញឹមអង្គរ)</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Bayon Temple (Smiles of Angkor)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F11" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G11" t="str">
+        <v>កណ្តាលក្រុងអង្គរធំ រមណីយដ្ឋានអង្គរ ខេត្តសៀមរាប</v>
+      </c>
+      <c r="H11" t="str">
+        <v>រួមបញ្ចូលក្នុងសំបុត្រអង្គរ (ខ្មែរឥតគិតថ្លៃ)</v>
+      </c>
+      <c r="I11" t="str">
+        <v>ព្រឹកព្រលឹម ឬពេលរសៀល ម៉ោង ០៣:០០ ដល់ ០៥:៣០</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>dest-11</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ប្រាសាទតាព្រហ្ម (ប្រាសាទឫសឈើយក្ស)</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Ta Prohm Temple (Tomb Raider Temple)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F12" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G12" t="str">
+        <v>ភាគខាងកើតនៃអង្គរធំ រមណីយដ្ឋានអង្គរ</v>
+      </c>
+      <c r="H12" t="str">
+        <v>រួមបញ្ចូលក្នុងសំបុត្រអង្គរ (ខ្មែរឥតគិតថ្លៃ)</v>
+      </c>
+      <c r="I12" t="str">
+        <v>ពេលព្រឹកព្រលឹម ចៀសវាងមនុស្សកុះករ</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>dest-12</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ប្រាសាទបន្ទាយស្រី (រតនភណ្ឌសិល្បៈខ្មែរ)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Banteay Srei (Citadel of Women)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F13" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G13" t="str">
+        <v>ស្រុកបន្ទាយស្រី ចម្ងាយ ៣២ គ.ម ពីក្រុងសៀមរាប</v>
+      </c>
+      <c r="H13" t="str">
+        <v>រួមបញ្ចូលក្នុងសំបុត្រអង្គរ (ខ្មែរឥតគិតថ្លៃ)</v>
+      </c>
+      <c r="I13" t="str">
+        <v>ពេលព្រឹកព្រលឹម ម៉ោង ០៧:៣០ ដល់ ០៩:៣០</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>dest-13</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ឧទ្យានជាតិភ្នំគូលែន និងទឹកធ្លាក់ព្រះអង្គធំ</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Phnom Kulen National Park &amp; Waterfall</v>
+      </c>
+      <c r="E14" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F14" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G14" t="str">
+        <v>ស្រុកស្វាយលើ ចម្ងាយ ៥០ គ.ម ពីក្រុងសៀមរាប</v>
+      </c>
+      <c r="H14" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $20)</v>
+      </c>
+      <c r="I14" t="str">
+        <v>រដូវវស្សា និងរដូវរំហើយ (ទឹកធ្លាក់ហូរខ្លាំង)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>dest-14</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ស្ទឹងលិង្គមួយពាន់ ក្បាលស្ពាន</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Kbal Spean (River of a Thousand Lingas)</v>
+      </c>
+      <c r="E15" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F15" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G15" t="str">
+        <v>ជើងភ្នំគូលែន ស្រុកបន្ទាយស្រី</v>
+      </c>
+      <c r="H15" t="str">
+        <v>រួមបញ្ចូលក្នុងសំបុត្រអង្គរ (ខ្មែរឥតគិតថ្លៃ)</v>
+      </c>
+      <c r="I15" t="str">
+        <v>រដូវវស្សា និងរដូវរំហើយ ខែកក្កដា ដល់ខែធ្នូ</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>dest-15</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ប្រាសាទបាគង (ប្រាសាទភ្នំដំបូងគេ)</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Bakong Temple (First Temple Mountain)</v>
+      </c>
+      <c r="E16" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F16" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G16" t="str">
+        <v>ក្រុមប្រាសាទរលួស ស្រុកប្រាសាទបាគង</v>
+      </c>
+      <c r="H16" t="str">
+        <v>រួមបញ្ចូលក្នុងសំបុត្រអង្គរ (ខ្មែរឥតគិតថ្លៃ)</v>
+      </c>
+      <c r="I16" t="str">
+        <v>ពេលរសៀល ម៉ោង ០៣:៣០ ដល់ ០៥:៣០</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>dest-16</v>
+      </c>
+      <c r="C17" t="str">
+        <v>ប្រាសាទព្រះខ័ន (រាជវាំងបណ្តោះអាសន្នជ័យវរ្ម័នទី៧)</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Preah Khan Temple</v>
+      </c>
+      <c r="E17" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F17" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G17" t="str">
+        <v>ភាគខាងជើងនៃអង្គរធំ រមណីយដ្ឋានអង្គរ</v>
+      </c>
+      <c r="H17" t="str">
+        <v>រួមបញ្ចូលក្នុងសំបុត្រអង្គរ (ខ្មែរឥតគិតថ្លៃ)</v>
+      </c>
+      <c r="I17" t="str">
+        <v>ពេលព្រឹក ឬរសៀលត្រជាក់</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>dest-17</v>
+      </c>
+      <c r="C18" t="str">
+        <v>បឹងទន្លេសាប និងភូមិបណ្តែតទឹកកំពង់ភ្លុក</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Tonle Sap &amp; Kampong Phluk Floating Village</v>
+      </c>
+      <c r="E18" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F18" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G18" t="str">
+        <v>ស្រុកប្រាសាទបាគង ចម្ងាយ ៣០ គ.ម ពីក្រុងសៀមរាប</v>
+      </c>
+      <c r="H18" t="str">
+        <v>ជិះទូក $5-$10 ក្នុងម្នាក់</v>
+      </c>
+      <c r="I18" t="str">
+        <v>រដូវវស្សា និងរដូវសម្រក ខែសីហា ដល់ខែមករា</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>dest-18</v>
+      </c>
+      <c r="C19" t="str">
+        <v>ប្រាសាទបន្ទាយក្តី និងស្រះស្រង់</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Banteay Kdei &amp; Srah Srang</v>
+      </c>
+      <c r="E19" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F19" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G19" t="str">
+        <v>ទល់មុខស្រះស្រង់ រមណីយដ្ឋានអង្គរ</v>
+      </c>
+      <c r="H19" t="str">
+        <v>រួមបញ្ចូលក្នុងសំបុត្រអង្គរ (ខ្មែរឥតគិតថ្លៃ)</v>
+      </c>
+      <c r="I19" t="str">
+        <v>ពេលថ្ងៃរះនៅស្រះស្រង់ ម៉ោង ០៥:៣០ ព្រឹក</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>dest-19</v>
+      </c>
+      <c r="C20" t="str">
+        <v>ប្រាសាទមេបុណ្យខាងកើត និងប្រាសាទប្រែរូប</v>
+      </c>
+      <c r="D20" t="str">
+        <v>East Mebon &amp; Pre Rup Temples</v>
+      </c>
+      <c r="E20" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F20" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G20" t="str">
+        <v>បារាយណ៍ខាងកើត រមណីយដ្ឋានអង្គរ</v>
+      </c>
+      <c r="H20" t="str">
+        <v>រួមបញ្ចូលក្នុងសំបុត្រអង្គរ (ខ្មែរឥតគិតថ្លៃ)</v>
+      </c>
+      <c r="I20" t="str">
+        <v>ពេលរសៀលទស្សនាថ្ងៃលិច ម៉ោង ១៦:៣០ - ១៨:០០</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>dest-20</v>
+      </c>
+      <c r="C21" t="str">
+        <v>ផ្សាររាត្រីអង្គរ និងផ្លូវ Pub Street វប្បធម៌ទេសចរណ៍</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Angkor Night Market &amp; Pub Street Heritage</v>
+      </c>
+      <c r="E21" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F21" t="str">
+        <v>ខេត្តសៀមរាប</v>
+      </c>
+      <c r="G21" t="str">
+        <v>សង្កាត់ស្វាយដង្គំ ក្រុងសៀមរាប</v>
+      </c>
+      <c r="H21" t="str">
+        <v>ឥតគិតថ្លៃដើរទស្សនា</v>
+      </c>
+      <c r="I21" t="str">
+        <v>ពេលរាត្រី ម៉ោង ១៨:០០ ដល់ ២៣:០០</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>dest-21</v>
+      </c>
+      <c r="C22" t="str">
+        <v>ឆ្នេរអូរឈើទាល និងឆ្នេរអូរត្រេះ</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Ochheuteal &amp; Otres Beaches</v>
+      </c>
+      <c r="E22" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F22" t="str">
+        <v>ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="G22" t="str">
+        <v>សង្កាត់លេខ៤ ក្រុងព្រះសីហនុ</v>
+      </c>
+      <c r="H22" t="str">
+        <v>ឥតគិតថ្លៃចូលលេងឆ្នេរ</v>
+      </c>
+      <c r="I22" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែឧសភា (រដូវប្រាំងទឹកថ្លា)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>dest-22</v>
+      </c>
+      <c r="C23" t="str">
+        <v>កោះរ៉ុងឋានសួគ៌ (ឆ្នេរសុខសាន្ត ៤ គីឡូម៉ែត្រ)</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Koh Rong Island (Sok San Long Beach)</v>
+      </c>
+      <c r="E23" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F23" t="str">
+        <v>ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="G23" t="str">
+        <v>ក្រុងកោះរ៉ុង ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="H23" t="str">
+        <v>ទូកអូរប័រឆ្លងកោះ $25 ទៅមក</v>
+      </c>
+      <c r="I23" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែឧសភា</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>dest-23</v>
+      </c>
+      <c r="C24" t="str">
+        <v>កោះរ៉ុងសន្លឹម និងឆ្នេរសារ៉ាសិនបេ</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Koh Rong Sanloem &amp; Saracen Bay</v>
+      </c>
+      <c r="E24" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F24" t="str">
+        <v>ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="G24" t="str">
+        <v>ឈូងសមុទ្រកោះរ៉ុងសន្លឹម ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="H24" t="str">
+        <v>ទូកល្បឿនលឿន $25 ទៅមក</v>
+      </c>
+      <c r="I24" t="str">
+        <v>ខែធ្នូ ដល់ខែមេសា</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>dest-24</v>
+      </c>
+      <c r="C25" t="str">
+        <v>ឧទ្យានជាតិរាម (ព្រៃកោងកាង និងឆ្នេរធម្មជាតិ)</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Ream National Park</v>
+      </c>
+      <c r="E25" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F25" t="str">
+        <v>ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="G25" t="str">
+        <v>ស្រុកព្រៃនប់ ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="H25" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (ជិះទូកតាមព្រែក $15-$25)</v>
+      </c>
+      <c r="I25" t="str">
+        <v>ខែតុលា ដល់ខែមេសា</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>dest-25</v>
+      </c>
+      <c r="C26" t="str">
+        <v>ទឹកធ្លាក់ក្បាលឆាយ</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Kbal Chhay Waterfall</v>
+      </c>
+      <c r="E26" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F26" t="str">
+        <v>ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="G26" t="str">
+        <v>ខណ្ឌព្រៃនប់ ចម្ងាយ ១៦ គ.ម ពីក្រុងព្រះសីហនុ</v>
+      </c>
+      <c r="H26" t="str">
+        <v>សំបុត្រចូល ២,០០០ រៀល</v>
+      </c>
+      <c r="I26" t="str">
+        <v>រដូវវស្សា ខែកក្កដា ដល់ខែវិច្ឆិកា (ទឹកហូរខ្លាំង)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>dest-26</v>
+      </c>
+      <c r="C27" t="str">
+        <v>កោះពស់ និងស្ពានតេជោមរកត</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Morakot Island &amp; Techo Morakot Bridge</v>
+      </c>
+      <c r="E27" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F27" t="str">
+        <v>ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="G27" t="str">
+        <v>សង្កាត់លេខ៣ ក្រុងព្រះសីហនុ</v>
+      </c>
+      <c r="H27" t="str">
+        <v>ឥតគិតថ្លៃដើរទស្សនាលើស្ពាន</v>
+      </c>
+      <c r="I27" t="str">
+        <v>ពេលរសៀល ម៉ោង ១៦:៣០ ដល់ ១៨:៣០</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>dest-27</v>
+      </c>
+      <c r="C28" t="str">
+        <v>កោះតាទាម និងតំបន់ផ្កាថ្មមុជទឹក</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Koh Koun &amp; Coral Diving Reefs</v>
+      </c>
+      <c r="E28" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F28" t="str">
+        <v>ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="G28" t="str">
+        <v>ចន្លោះកោះរ៉ុង និងកោះរ៉ុងសន្លឹម</v>
+      </c>
+      <c r="H28" t="str">
+        <v>កញ្ចប់ Snorkeling $20-$35</v>
+      </c>
+      <c r="I28" t="str">
+        <v>ខែធ្នូ ដល់ខែមេសា (ទឹកថ្លាអាចមើលឃើញ ២០ ម៉ែត្រ)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>dest-28</v>
+      </c>
+      <c r="C29" t="str">
+        <v>ឆ្នេរកោះដែកគោល</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Koh Dek Koul Island</v>
+      </c>
+      <c r="E29" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F29" t="str">
+        <v>ខេត្តព្រះសីហនុ</v>
+      </c>
+      <c r="G29" t="str">
+        <v>ឈូងសមុទ្រក្រុងព្រះសីហនុ</v>
+      </c>
+      <c r="H29" t="str">
+        <v>តាមទូកទេសចរណ៍</v>
+      </c>
+      <c r="I29" t="str">
+        <v>រដូវប្រាំង ខែវិច្ឆិកា ដល់ឧសភា</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>dest-29</v>
+      </c>
+      <c r="C30" t="str">
+        <v>ឧទ្យានជាតិព្រះមុនីវង្សបូកគោ</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Preah Monivong Bokor National Park</v>
+      </c>
+      <c r="E30" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F30" t="str">
+        <v>ខេត្តកំពត</v>
+      </c>
+      <c r="G30" t="str">
+        <v>ភ្នំបូកគោ ក្រុងបូកគោ ខេត្តកំពត</v>
+      </c>
+      <c r="H30" t="str">
+        <v>ឥតគិតថ្លៃចូលទស្សនាភ្នំ</v>
+      </c>
+      <c r="I30" t="str">
+        <v>ពេញមួយឆ្នាំ (អាកាសធាតុត្រជាក់ស្រួល)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>dest-30</v>
+      </c>
+      <c r="C31" t="str">
+        <v>រមណីយដ្ឋានទឹកឈូ និងស្ទឹងកំពត</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Teuk Chhou Rapids &amp; Kampot River</v>
+      </c>
+      <c r="E31" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F31" t="str">
+        <v>ខេត្តកំពត</v>
+      </c>
+      <c r="G31" t="str">
+        <v>ស្រុកទឹកឈូ ចម្ងាយ ៨ គ.ម ពីក្រុងកំពត</v>
+      </c>
+      <c r="H31" t="str">
+        <v>សំបុត្រចូល ២,០០០ រៀល</v>
+      </c>
+      <c r="I31" t="str">
+        <v>រដូវក្តៅ និងរដូវផ្លែឈើ ខែមេសា ដល់កក្កដា</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>dest-31</v>
+      </c>
+      <c r="C32" t="str">
+        <v>ចម្ការម្រេចកំពតធម្មជាតិ (ម្រេចភូមិសាស្ត្រ GI)</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Kampot Organic Pepper Plantations (GI)</v>
+      </c>
+      <c r="E32" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F32" t="str">
+        <v>ខេត្តកំពត</v>
+      </c>
+      <c r="G32" t="str">
+        <v>ស្រុកទឹកឈូ និងស្រុកកំពង់ត្រាច ខេត្តកំពត</v>
+      </c>
+      <c r="H32" t="str">
+        <v>ឥតគិតថ្លៃទស្សនាចម្ការ</v>
+      </c>
+      <c r="I32" t="str">
+        <v>រដូវប្រមូលផលម្រេច ខែមករា ដល់ឧសភា</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>dest-32</v>
+      </c>
+      <c r="C33" t="str">
+        <v>ភ្នំកំពង់ត្រាច និងរូងភ្នំថ្មបុរាណ</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Phnom Kampong Trach Caves</v>
+      </c>
+      <c r="E33" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F33" t="str">
+        <v>ខេត្តកំពត</v>
+      </c>
+      <c r="G33" t="str">
+        <v>ស្រុកកំពង់ត្រាច ចម្ងាយ ៣៨ គ.ម ពីក្រុងកំពត</v>
+      </c>
+      <c r="H33" t="str">
+        <v>ឥតគិតថ្លៃ (ជូនទានមគ្គុទ្ទេសក៍ក្មេងៗ)</v>
+      </c>
+      <c r="I33" t="str">
+        <v>ពេញមួយឆ្នាំ ពេលព្រឹក</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>dest-33</v>
+      </c>
+      <c r="C34" t="str">
+        <v>ទំនប់ម្លិច និងតំបន់អេកូទេសចរណ៍</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Mlech Dam &amp; Eco Lake</v>
+      </c>
+      <c r="E34" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F34" t="str">
+        <v>ខេត្តកំពត</v>
+      </c>
+      <c r="G34" t="str">
+        <v>ស្រុកជុំគិរី ខេត្តកំពត</v>
+      </c>
+      <c r="H34" t="str">
+        <v>ឥតគិតថ្លៃចូលលេង</v>
+      </c>
+      <c r="I34" t="str">
+        <v>រដូវរំហើយ ខែវិច្ឆិកា ដល់កុម្ភៈ (បោះតង់)</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>dest-34</v>
+      </c>
+      <c r="C35" t="str">
+        <v>កំពង់កណ្តាល និងសកម្មភាពជិះទូកកាយ៉ាក់ស្ទឹងកំពត</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Kampot Green Loop Riverfront &amp; Kayaking</v>
+      </c>
+      <c r="E35" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F35" t="str">
+        <v>ខេត្តកំពត</v>
+      </c>
+      <c r="G35" t="str">
+        <v>ដងស្ទឹងកំពត ក្រុងកំពត</v>
+      </c>
+      <c r="H35" t="str">
+        <v>ជួលទូកកាយ៉ាក់ $5/ម៉ោង</v>
+      </c>
+      <c r="I35" t="str">
+        <v>ពេលរសៀល ម៉ោង ១៥:៣០ ដល់ ១៨:៣០</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>dest-35</v>
+      </c>
+      <c r="C36" t="str">
+        <v>ស្រែអំបិលកំពត (បេតិកភណ្ឌកសិ-ទេសចរណ៍)</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Kampot Traditional Salt Fields</v>
+      </c>
+      <c r="E36" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F36" t="str">
+        <v>ខេត្តកំពត</v>
+      </c>
+      <c r="G36" t="str">
+        <v>តាមបណ្តោយផ្លូវទៅកែប ស្រុកទឹកឈូ</v>
+      </c>
+      <c r="H36" t="str">
+        <v>ឥតគិតថ្លៃទស្សនា</v>
+      </c>
+      <c r="I36" t="str">
+        <v>រដូវប្រមូលផលអំបិល ខែមករា ដល់មេសា</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>dest-36</v>
+      </c>
+      <c r="C37" t="str">
+        <v>ភ្នំឈ្ងោក និងប្រាសាទល្អាងសតវត្សរ៍ទី៧</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Phnom Chhngok Cave Temple</v>
+      </c>
+      <c r="E37" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F37" t="str">
+        <v>ខេត្តកំពត</v>
+      </c>
+      <c r="G37" t="str">
+        <v>ឃុំបុស្សត្របែក ស្រុកទឹកឈូ</v>
+      </c>
+      <c r="H37" t="str">
+        <v>សំបុត្រចូល $1</v>
+      </c>
+      <c r="I37" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៨:០០ ដល់ ១១:០០</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>dest-37</v>
+      </c>
+      <c r="C38" t="str">
+        <v>ឆ្នេរកែប និងរូបសំណាកស្រីស្អាតចាំប្តី</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Kep Beach &amp; Sela Thorani Lady Statue</v>
+      </c>
+      <c r="E38" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F38" t="str">
+        <v>ខេត្តកែប</v>
+      </c>
+      <c r="G38" t="str">
+        <v>ក្រុងកែប ខេត្តកែប</v>
+      </c>
+      <c r="H38" t="str">
+        <v>ឥតគិតថ្លៃចូលទស្សនាឆ្នេរ</v>
+      </c>
+      <c r="I38" t="str">
+        <v>ខែវិច្ឆិកា ដល់ឧសភា (ទស្សនាថ្ងៃលិច)</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>dest-38</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ផ្សារក្តាមកែប (រមណីយដ្ឋានម្ហូបគ្រឿងសមុទ្រស្រស់)</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Kep Crab Market (Phsar Kdam)</v>
+      </c>
+      <c r="E39" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F39" t="str">
+        <v>ខេត្តកែប</v>
+      </c>
+      <c r="G39" t="str">
+        <v>មាត់សមុទ្រក្រុងកែប</v>
+      </c>
+      <c r="H39" t="str">
+        <v>ឥតគិតថ្លៃដើរផ្សារ</v>
+      </c>
+      <c r="I39" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៨:០០ ដល់ ១១:០០ និងពេលរសៀល</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>dest-39</v>
+      </c>
+      <c r="C40" t="str">
+        <v>ឧទ្យានជាតិកែប (ផ្លូវដើរព្រៃមើលសមុទ្រ)</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Kep National Park Trail</v>
+      </c>
+      <c r="E40" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F40" t="str">
+        <v>ខេត្តកែប</v>
+      </c>
+      <c r="G40" t="str">
+        <v>ខ្នងភ្នំកែប ក្រុងកែប</v>
+      </c>
+      <c r="H40" t="str">
+        <v>សំបុត្រចូល ២,០០០ រៀល ($1 បរទេស)</v>
+      </c>
+      <c r="I40" t="str">
+        <v>ពេលព្រឹកព្រលឹម ឬរសៀលត្រជាក់</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>dest-40</v>
+      </c>
+      <c r="C41" t="str">
+        <v>កោះទន្សាយ (ឆ្នេរខ្សាច់ស្ងប់ស្ងាត់)</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Rabbit Island (Koh Tonsay)</v>
+      </c>
+      <c r="E41" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F41" t="str">
+        <v>ខេត្តកែប</v>
+      </c>
+      <c r="G41" t="str">
+        <v>ឈូងសមុទ្រកែប ចម្ងាយ ៤.៥ គ.ម ពីកំពង់ផែកែប</v>
+      </c>
+      <c r="H41" t="str">
+        <v>ថ្លៃទូកទៅមក $8-$10 ក្នុងម្នាក់</v>
+      </c>
+      <c r="I41" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែឧសភា</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>dest-41</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ភ្នំសសៀរ និងល្អាងដំរីស</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Phnom Sorsia &amp; White Elephant Cave</v>
+      </c>
+      <c r="E42" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F42" t="str">
+        <v>ខេត្តកែប</v>
+      </c>
+      <c r="G42" t="str">
+        <v>ស្រុកដំណាក់ចង្អើរ ខេត្តកែប</v>
+      </c>
+      <c r="H42" t="str">
+        <v>ឥតគិតថ្លៃ (ជូនទានវត្ត)</v>
+      </c>
+      <c r="I42" t="str">
+        <v>ពេលព្រឹកព្រលឹម ឬរសៀល</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>dest-42</v>
+      </c>
+      <c r="C43" t="str">
+        <v>ភ្នំសំពៅ និងល្អាងប្រចៀវរាប់លាន</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Phnom Sampov &amp; Bat Caves</v>
+      </c>
+      <c r="E43" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F43" t="str">
+        <v>ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="G43" t="str">
+        <v>ស្រុកបាណន់ ចម្ងាយ ១២ គ.ម ពីក្រុងបាត់ដំបង</v>
+      </c>
+      <c r="H43" t="str">
+        <v>ឥតគិតថ្លៃទស្សនាប្រចៀវ ($3 សំបុត្រឡើងភ្នំ)</v>
+      </c>
+      <c r="I43" t="str">
+        <v>ពេលរសៀល ម៉ោង ១៦:៣០ ដល់ ១៨:០០ (ទស្សនាហ្វូងប្រចៀវ)</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>dest-43</v>
+      </c>
+      <c r="C44" t="str">
+        <v>រថភ្លើងឫស្សីបាត់ដំបង (ឡូរី)</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Battambang Bamboo Train (Norry)</v>
+      </c>
+      <c r="E44" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F44" t="str">
+        <v>ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="G44" t="str">
+        <v>ជើងភ្នំបាណន់ ស្រុកបាណន់</v>
+      </c>
+      <c r="H44" t="str">
+        <v>ថ្លៃជិះ $5 ក្នុងម្នាក់ (បរទេស $5)</v>
+      </c>
+      <c r="I44" t="str">
+        <v>ពេលព្រឹក ឬរសៀលត្រជាក់</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>dest-44</v>
+      </c>
+      <c r="C45" t="str">
+        <v>ប្រាសាទបាណន់ (អង្គរវត្តតូចនៃបាត់ដំបង)</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Wat Banan Temple</v>
+      </c>
+      <c r="E45" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F45" t="str">
+        <v>ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="G45" t="str">
+        <v>ស្រុកបាណន់ ចម្ងាយ ២៥ គ.ម ពីក្រុងបាត់ដំបង</v>
+      </c>
+      <c r="H45" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $2)</v>
+      </c>
+      <c r="I45" t="str">
+        <v>ពេលព្រឹកព្រលឹម</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>dest-45</v>
+      </c>
+      <c r="C46" t="str">
+        <v>ប្រាសាទឯកភ្នំ</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Ek Phnom Temple</v>
+      </c>
+      <c r="E46" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F46" t="str">
+        <v>ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="G46" t="str">
+        <v>ឃុំពាមឯក ស្រុកឯកភ្នំ</v>
+      </c>
+      <c r="H46" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $1)</v>
+      </c>
+      <c r="I46" t="str">
+        <v>ពេញមួយឆ្នាំ ពេលព្រឹក</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>dest-46</v>
+      </c>
+      <c r="C47" t="str">
+        <v>ផ្ទះបុរាណវត្តគរ (បេតិកភណ្ឌផ្ទះឈើបុរាណខ្មែរ)</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Wat Kor Ancient Wooden Houses</v>
+      </c>
+      <c r="E47" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F47" t="str">
+        <v>ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="G47" t="str">
+        <v>ភូមិវត្តគរ សង្កាត់វត្តគរ ក្រុងបាត់ដំបង</v>
+      </c>
+      <c r="H47" t="str">
+        <v>ឥតគិតថ្លៃ (ជូនទានម្ចាស់ផ្ទះ $1-$2)</v>
+      </c>
+      <c r="I47" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៨:៣០ ដល់ ១១:០០</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>dest-47</v>
+      </c>
+      <c r="C48" t="str">
+        <v>ទំនប់កំពីងពួយ និងបឹងផ្កាឈូក</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Kamping Puoy Lotus Lake &amp; Reservoir</v>
+      </c>
+      <c r="E48" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F48" t="str">
+        <v>ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="G48" t="str">
+        <v>ស្រុកបាណន់ ចម្ងាយ ៣៥ គ.ម ពីក្រុងបាត់ដំបង</v>
+      </c>
+      <c r="H48" t="str">
+        <v>ឥតគិតថ្លៃ (ជួលទូក $5-$8)</v>
+      </c>
+      <c r="I48" t="str">
+        <v>រដូវផ្កាឈូករីក ខែកក្កដា ដល់ធ្នូ</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>dest-48</v>
+      </c>
+      <c r="C49" t="str">
+        <v>អគារបេតិកភណ្ឌអាណានិគមបារាំងក្រុងបាត់ដំបង</v>
+      </c>
+      <c r="D49" t="str">
+        <v>French Colonial Heritage Quarter</v>
+      </c>
+      <c r="E49" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F49" t="str">
+        <v>ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="G49" t="str">
+        <v>មាត់ស្ទឹងសង្កែ ក្រុងបាត់ដំបង</v>
+      </c>
+      <c r="H49" t="str">
+        <v>ឥតគិតថ្លៃដើរទស្សនា</v>
+      </c>
+      <c r="I49" t="str">
+        <v>ពេលព្រឹក ឬពេលរសៀលទស្សនាស្ថាបត្យកម្ម</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>dest-49</v>
+      </c>
+      <c r="C50" t="str">
+        <v>ភ្នំក្រពើ និងរមណីយដ្ឋានធម្មជាតិ</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Phnom Krapau Natural Resort</v>
+      </c>
+      <c r="E50" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F50" t="str">
+        <v>ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="G50" t="str">
+        <v>ស្រុកបាណន់ ខេត្តបាត់ដំបង</v>
+      </c>
+      <c r="H50" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I50" t="str">
+        <v>ពេលព្រឹកព្រលឹម</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>dest-50</v>
+      </c>
+      <c r="C51" t="str">
+        <v>ទឹកធ្លាក់តាតៃ (រមណីយដ្ឋានធម្មជាតិអេកូ)</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Tatai Waterfall &amp; River Sanctuary</v>
+      </c>
+      <c r="E51" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F51" t="str">
+        <v>ខេត្តកោះកុង</v>
+      </c>
+      <c r="G51" t="str">
+        <v>ស្រុកថ្មបាំង និងស្រុកកោះកុង ចម្ងាយ ២០ គ.ម ពីក្រុងខេមរភូមិន្ទ</v>
+      </c>
+      <c r="H51" t="str">
+        <v>ទូកកាណូតទៅមក $15-$20 ក្នុងមួយទូក</v>
+      </c>
+      <c r="I51" t="str">
+        <v>ខែតុលា ដល់ខែមករា (ទឹកថ្លា និងហូរខ្លាំង)</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>dest-51</v>
+      </c>
+      <c r="C52" t="str">
+        <v>ព្រៃកោងកាងពាមក្រសោប (ស្ពានឈើវែងបំផុត)</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Peam Krasop Mangrove Sanctuary</v>
+      </c>
+      <c r="E52" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F52" t="str">
+        <v>ខេត្តកោះកុង</v>
+      </c>
+      <c r="G52" t="str">
+        <v>ស្រុកមណ្ឌលសីមា ចម្ងាយ ៧ គ.ម ពីក្រុងខេមរភូមិន្ទ</v>
+      </c>
+      <c r="H52" t="str">
+        <v>សំបុត្រ ៣,០០០ រៀល (បរទេស $1.5)</v>
+      </c>
+      <c r="I52" t="str">
+        <v>ពេញមួយឆ្នាំ ពេលរសៀលទស្សនាថ្ងៃលិច</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>dest-52</v>
+      </c>
+      <c r="C53" t="str">
+        <v>កោះស្តេច (ឋានសួគ៌កោះធម្មជាតិ)</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Koh Sdach Archipelago (King Island)</v>
+      </c>
+      <c r="E53" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F53" t="str">
+        <v>ខេត្តកោះកុង</v>
+      </c>
+      <c r="G53" t="str">
+        <v>ស្រុកគិរីសាគរ ខេត្តកោះកុង</v>
+      </c>
+      <c r="H53" t="str">
+        <v>ឥតគិតថ្លៃ (ជួលទូកកម្សាន្តកោះ $25-$40)</v>
+      </c>
+      <c r="I53" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែឧសភា</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>dest-53</v>
+      </c>
+      <c r="C54" t="str">
+        <v>តំបន់អេកូទេសចរណ៍ជីផាត់</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Chi Phat Community Eco-Tourism</v>
+      </c>
+      <c r="E54" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F54" t="str">
+        <v>ខេត្តកោះកុង</v>
+      </c>
+      <c r="G54" t="str">
+        <v>ស្រុកថ្មបាំង ជួរភ្នំក្រវាញខាងត្បូង</v>
+      </c>
+      <c r="H54" t="str">
+        <v>តាមកញ្ចប់សេវាសហគមន៍ ($15-$30/ថ្ងៃ)</v>
+      </c>
+      <c r="I54" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែកុម្ភៈ (រដូវរំហើយដើរព្រៃ)</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>dest-54</v>
+      </c>
+      <c r="C55" t="str">
+        <v>ជួរភ្នំក្រវាញ (ដែនជម្រកសត្វព្រៃ និងព្រៃទឹកភ្លៀង)</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Cardamom Rainforest &amp; Wildlife Sanctuary</v>
+      </c>
+      <c r="E55" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F55" t="str">
+        <v>ខេត្តកោះកុង</v>
+      </c>
+      <c r="G55" t="str">
+        <v>តំបន់ជួរភ្នំក្រវាញ ខេត្តកោះកុង</v>
+      </c>
+      <c r="H55" t="str">
+        <v>តាមមគ្គុទ្ទេសក៍ការពារព្រៃឈើ</v>
+      </c>
+      <c r="I55" t="str">
+        <v>រដូវប្រាំង ខែវិច្ឆិកា ដល់មេសា</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>dest-55</v>
+      </c>
+      <c r="C56" t="str">
+        <v>ឆ្នេរកោះកុងក្រៅ (ឆ្នេរខ្សាច់ធម្មជាតិ ៧ ដំណាក់)</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Koh Kong Krao Outer Island</v>
+      </c>
+      <c r="E56" t="str">
+        <v>ឆ្នេរសមុទ្រ &amp; កោះឋានសួគ៌</v>
+      </c>
+      <c r="F56" t="str">
+        <v>ខេត្តកោះកុង</v>
+      </c>
+      <c r="G56" t="str">
+        <v>ឈូងសមុទ្រកោះកុង ចម្ងាយ ៣០ គ.ម ពីក្រុងខេមរភូមិន្ទ</v>
+      </c>
+      <c r="H56" t="str">
+        <v>ទូកកម្សាន្តឯកជន</v>
+      </c>
+      <c r="I56" t="str">
+        <v>ខែវិច្ឆិកា ដល់ឧសភា</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>dest-56</v>
+      </c>
+      <c r="C57" t="str">
+        <v>ទឹកធ្លាក់ប៊ូស្រា (ស្ដេចទឹកធ្លាក់កម្ពុជា)</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Bousra Waterfall (King of Waterfalls)</v>
+      </c>
+      <c r="E57" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F57" t="str">
+        <v>ខេត្តមណ្ឌលគិរី</v>
+      </c>
+      <c r="G57" t="str">
+        <v>ស្រុកពេជ្រាដា ចម្ងាយ ៤៣ គ.ម ពីក្រុងសែនមនោរម្យ</v>
+      </c>
+      <c r="H57" t="str">
+        <v>សំបុត្រចូល ២,០០០ រៀល (បរទេស $2)</v>
+      </c>
+      <c r="I57" t="str">
+        <v>រដូវវស្សា និងរដូវរំហើយ ខែកក្កដា ដល់មករា</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>dest-57</v>
+      </c>
+      <c r="C58" t="str">
+        <v>ដែនជម្រកសត្វព្រៃកែវសីមា និងជ្រលងដំរី</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Keo Seima Wildlife Sanctuary &amp; Elephant Valley</v>
+      </c>
+      <c r="E58" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F58" t="str">
+        <v>ខេត្តមណ្ឌលគិរី</v>
+      </c>
+      <c r="G58" t="str">
+        <v>ស្រុកកែវសីមា ខេត្តមណ្ឌលគិរី</v>
+      </c>
+      <c r="H58" t="str">
+        <v>កញ្ចប់ទេសចរណ៍អភិរក្សដំរី</v>
+      </c>
+      <c r="I58" t="str">
+        <v>ពេញមួយឆ្នាំ ពិសេសខែវិច្ឆិកា ដល់មីនា</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>dest-58</v>
+      </c>
+      <c r="C59" t="str">
+        <v>ភ្នំដោះក្រមុំ (ចំណុចមើលថ្ងៃលិចក្រុងសែនមនោរម្យ)</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Phnom Doh Kromom Viewpoint</v>
+      </c>
+      <c r="E59" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F59" t="str">
+        <v>ខេត្តមណ្ឌលគិរី</v>
+      </c>
+      <c r="G59" t="str">
+        <v>ក្រុងសែនមនោរម្យ ខេត្តមណ្ឌលគិរី</v>
+      </c>
+      <c r="H59" t="str">
+        <v>ឥតគិតថ្លៃចូលទស្សនា</v>
+      </c>
+      <c r="I59" t="str">
+        <v>ពេលរសៀល ម៉ោង ១៦:៣០ ដល់ ១៨:០០</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>dest-59</v>
+      </c>
+      <c r="C60" t="str">
+        <v>សមុទ្រឈើ (ទេសភាពព្រៃឈើរលកខៀវស្រងាត់)</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Sea of Forests (Samot Chheu)</v>
+      </c>
+      <c r="E60" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F60" t="str">
+        <v>ខេត្តមណ្ឌលគិរី</v>
+      </c>
+      <c r="G60" t="str">
+        <v>ស្រុកអូររាំង ចម្ងាយ ៥ គ.ម ពីក្រុងសែនមនោរម្យ</v>
+      </c>
+      <c r="H60" t="str">
+        <v>ឥតគិតថ្លៃទស្សនា</v>
+      </c>
+      <c r="I60" t="str">
+        <v>ពេលព្រឹកព្រលឹមទស្សនាអ័ព្ទ ឬពេលល្ងាច</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>dest-60</v>
+      </c>
+      <c r="C61" t="str">
+        <v>ទឹកធ្លាក់សែនមនោរម្យ</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Sen Monorom Waterfall</v>
+      </c>
+      <c r="E61" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F61" t="str">
+        <v>ខេត្តមណ្ឌលគិរី</v>
+      </c>
+      <c r="G61" t="str">
+        <v>ជាយក្រុងសែនមនោរម្យ ចម្ងាយ ៥ គ.ម</v>
+      </c>
+      <c r="H61" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I61" t="str">
+        <v>រដូវវស្សា ខែមិថុនា ដល់វិច្ឆិកា</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>dest-61</v>
+      </c>
+      <c r="C62" t="str">
+        <v>ទឹកធ្លាក់ជ្រៃធំ</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Chrey Thom Waterfall</v>
+      </c>
+      <c r="E62" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F62" t="str">
+        <v>ខេត្តមណ្ឌលគិរី</v>
+      </c>
+      <c r="G62" t="str">
+        <v>ស្រុកកែវសីមា ចម្ងាយ ៤៣ គ.ម ពីសែនមនោរម្យ</v>
+      </c>
+      <c r="H62" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I62" t="str">
+        <v>រដូវវស្សា និងដើមរដូវប្រាំង</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>dest-62</v>
+      </c>
+      <c r="C63" t="str">
+        <v>បឹងយក្សឡោម (បឹងភ្នំភ្លើងបុរាណ ៤,០០០ ឆ្នាំ)</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Yeak Laom Volcanic Crater Lake</v>
+      </c>
+      <c r="E63" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F63" t="str">
+        <v>ខេត្តរតនគិរី</v>
+      </c>
+      <c r="G63" t="str">
+        <v>ក្រុងបានលុង ចម្ងាយ ៥ គ.ម ពីកណ្តាលក្រុង</v>
+      </c>
+      <c r="H63" t="str">
+        <v>សំបុត្រ ៤,០០០ រៀល (បរទេស $2)</v>
+      </c>
+      <c r="I63" t="str">
+        <v>ពេញមួយឆ្នាំ (ទឹកថ្លាអាចហែលទឹកបាន)</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>dest-63</v>
+      </c>
+      <c r="C64" t="str">
+        <v>ទឹកធ្លាក់ចាអ៊ុង</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Cha Ong Waterfall</v>
+      </c>
+      <c r="E64" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F64" t="str">
+        <v>ខេត្តរតនគិរី</v>
+      </c>
+      <c r="G64" t="str">
+        <v>ឃុំចាអ៊ុង ស្រុកអូរជុំ ចម្ងាយ ៨ គ.ម ពីបានលុង</v>
+      </c>
+      <c r="H64" t="str">
+        <v>សំបុត្រ ២,០០០ រៀល (បរទេស $1)</v>
+      </c>
+      <c r="I64" t="str">
+        <v>រដូវវស្សា ខែកក្កដា ដល់ធ្នូ</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>dest-64</v>
+      </c>
+      <c r="C65" t="str">
+        <v>ទឹកធ្លាក់កាចាញ</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Ka Chanh Waterfall</v>
+      </c>
+      <c r="E65" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F65" t="str">
+        <v>ខេត្តរតនគិរី</v>
+      </c>
+      <c r="G65" t="str">
+        <v>ស្រុកបានលុង ចម្ងាយ ៦ គ.ម ពីក្រុងបានលុង</v>
+      </c>
+      <c r="H65" t="str">
+        <v>សំបុត្រ ២,០០០ រៀល</v>
+      </c>
+      <c r="I65" t="str">
+        <v>ខែសីហា ដល់កុម្ភៈ</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>dest-65</v>
+      </c>
+      <c r="C66" t="str">
+        <v>ទឹកធ្លាក់កាទៀង</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Ka Tieng Waterfall</v>
+      </c>
+      <c r="E66" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F66" t="str">
+        <v>ខេត្តរតនគិរី</v>
+      </c>
+      <c r="G66" t="str">
+        <v>ស្រុកលំផាត់ ចម្ងាយ ៧ គ.ម ពីបានលុង</v>
+      </c>
+      <c r="H66" t="str">
+        <v>សំបុត្រ ២,០០០ រៀល</v>
+      </c>
+      <c r="I66" t="str">
+        <v>រដូវវស្សា និងដើមរដូវប្រាំង</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>dest-66</v>
+      </c>
+      <c r="C67" t="str">
+        <v>ឧទ្យានជាតិវីរៈជ័យ (បេះដូងព្រៃព្រហ្មចារីឥណ្ឌូចិន)</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Virachey National Park</v>
+      </c>
+      <c r="E67" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F67" t="str">
+        <v>ខេត្តរតនគិរី</v>
+      </c>
+      <c r="G67" t="str">
+        <v>ស្រុកតាវែង និងស្រុកវើនសៃ ព្រំដែនឡាវ-វៀតណាម</v>
+      </c>
+      <c r="H67" t="str">
+        <v>តាមកញ្ចប់ Trekking របស់ឧទ្យានុរក្ស</v>
+      </c>
+      <c r="I67" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែមីនា</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>dest-67</v>
+      </c>
+      <c r="C68" t="str">
+        <v>ប្រាសាទព្រះវិហារ (បេតិកភណ្ឌពិភពលោកយូណេស្កូ)</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Prasat Preah Vihear (UNESCO World Heritage)</v>
+      </c>
+      <c r="E68" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F68" t="str">
+        <v>ខេត្តព្រះវិហារ</v>
+      </c>
+      <c r="G68" t="str">
+        <v>ជួរភ្នំដងរែក ស្រុកជាំក្សាន្ត ខេត្តព្រះវិហារ</v>
+      </c>
+      <c r="H68" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $10, ឡានឡើងភ្នំ $25)</v>
+      </c>
+      <c r="I68" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែមីនា (អាកាសធាតុត្រជាក់លើកំពូលភ្នំ)</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>dest-68</v>
+      </c>
+      <c r="C69" t="str">
+        <v>ប្រាសាទកោះកេរ (ប្រាសាទពីរ៉ាមីតខ្មែរ យូណេស្កូ)</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Koh Ker Pyramid Temple Complex (UNESCO)</v>
+      </c>
+      <c r="E69" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F69" t="str">
+        <v>ខេត្តព្រះវិហារ</v>
+      </c>
+      <c r="G69" t="str">
+        <v>ស្រុកគូលែន ខេត្តព្រះវិហារ</v>
+      </c>
+      <c r="H69" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $15)</v>
+      </c>
+      <c r="I69" t="str">
+        <v>ពេញមួយឆ្នាំ ពេលព្រឹក</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>dest-69</v>
+      </c>
+      <c r="C70" t="str">
+        <v>ប្រាសាទព្រះខ័នកំពង់ស្វាយ (ប្រាសាទផ្ទៃដីធំបំផុត)</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Preah Khan of Kampong Svay (Bakan)</v>
+      </c>
+      <c r="E70" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F70" t="str">
+        <v>ខេត្តព្រះវិហារ</v>
+      </c>
+      <c r="G70" t="str">
+        <v>ស្រុកសង្គមថ្មី ព្រំប្រទល់ខេត្តកំពង់ធំ</v>
+      </c>
+      <c r="H70" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I70" t="str">
+        <v>រដូវប្រាំង ខែវិច្ឆិកា ដល់មេសា</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>dest-70</v>
+      </c>
+      <c r="C71" t="str">
+        <v>ដែនជម្រកសត្វព្រៃគូលែនព្រហ្មទេព</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Kulen Promtep Wildlife Reserve</v>
+      </c>
+      <c r="E71" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F71" t="str">
+        <v>ខេត្តព្រះវិហារ</v>
+      </c>
+      <c r="G71" t="str">
+        <v>ស្រុកត្បែងមានជ័យ និងស្រុកគូលែន</v>
+      </c>
+      <c r="H71" t="str">
+        <v>តាមដំណើរកម្សាន្តអេកូទេសចរណ៍</v>
+      </c>
+      <c r="I71" t="str">
+        <v>ខែធ្នូ ដល់ឧសភា (មើលសត្វស្លាបកម្រ)</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>dest-71</v>
+      </c>
+      <c r="C72" t="str">
+        <v>ទឹកធ្លាក់ព្រះនិម្មិត (ល្បាក់ខោនទន្លេមេគង្គ)</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Preah Nimith Waterfall &amp; Mekong Rapids</v>
+      </c>
+      <c r="E72" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F72" t="str">
+        <v>ខេត្តព្រះវិហារ</v>
+      </c>
+      <c r="G72" t="str">
+        <v>ស្រុកឆែប ព្រំប្រទល់ប្រទេសឡាវ</v>
+      </c>
+      <c r="H72" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I72" t="str">
+        <v>រដូវវស្សា ខែកញ្ញា ដល់វិច្ឆិកា</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>dest-72</v>
+      </c>
+      <c r="C73" t="str">
+        <v>ប្រាសាទសំបូរព្រៃគុក (បេតិកភណ្ឌពិភពលោកយូណេស្កូ)</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Sambor Prei Kuk (UNESCO World Heritage Site)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F73" t="str">
+        <v>ខេត្តកំពង់ធំ</v>
+      </c>
+      <c r="G73" t="str">
+        <v>ស្រុកប្រាសាទសំបូរ ចម្ងាយ ៣០ គ.ម ពីក្រុងស្ទឹងសែន</v>
+      </c>
+      <c r="H73" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $10)</v>
+      </c>
+      <c r="I73" t="str">
+        <v>ពេញមួយឆ្នាំ ពេលព្រឹកត្រជាក់</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>dest-73</v>
+      </c>
+      <c r="C74" t="str">
+        <v>ភ្នំសន្ទុក (ភ្នំសក្ការបូជា និងកាំជណ្តើរ ៨០៩ កាំ)</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Phnom Santuk Holy Mountain &amp; 809 Steps</v>
+      </c>
+      <c r="E74" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F74" t="str">
+        <v>ខេត្តកំពង់ធំ</v>
+      </c>
+      <c r="G74" t="str">
+        <v>ស្រុកសន្ទុក ចម្ងាយ ១៧ គ.ម ពីក្រុងស្ទឹងសែន</v>
+      </c>
+      <c r="H74" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $1)</v>
+      </c>
+      <c r="I74" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៧:៣០ ដល់ ១០:៣០</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>dest-74</v>
+      </c>
+      <c r="C75" t="str">
+        <v>ទំនប់៣០កញ្ញា (រមណីយដ្ឋានមាត់ទឹក)</v>
+      </c>
+      <c r="D75" t="str">
+        <v>30 September Dam &amp; Recreational Lake</v>
+      </c>
+      <c r="E75" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F75" t="str">
+        <v>ខេត្តកំពង់ធំ</v>
+      </c>
+      <c r="G75" t="str">
+        <v>ស្រុកស្ទឹងសែន ខេត្តកំពង់ធំ</v>
+      </c>
+      <c r="H75" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I75" t="str">
+        <v>ពេលរសៀល ម៉ោង ១៦:០០ ដល់ ១៨:៣០</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>dest-75</v>
+      </c>
+      <c r="C76" t="str">
+        <v>ប្រាសាទគុកនគរ</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Kuk Nokor Temple</v>
+      </c>
+      <c r="E76" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F76" t="str">
+        <v>ខេត្តកំពង់ធំ</v>
+      </c>
+      <c r="G76" t="str">
+        <v>ភូមិត្រស់ ឃុំត្រស់ ស្រុកបារាយណ៍</v>
+      </c>
+      <c r="H76" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I76" t="str">
+        <v>ពេញមួយឆ្នាំ</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>dest-76</v>
+      </c>
+      <c r="C77" t="str">
+        <v>ស្ទឹងសែន និងព្រៃជីវចម្រុះធម្មជាតិ</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Stung Sen River Biosphere Reserve</v>
+      </c>
+      <c r="E77" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F77" t="str">
+        <v>ខេត្តកំពង់ធំ</v>
+      </c>
+      <c r="G77" t="str">
+        <v>ក្រុងស្ទឹងសែន និងស្រុកកំពង់ស្វាយ</v>
+      </c>
+      <c r="H77" t="str">
+        <v>តាមទូកទេសចរណ៍</v>
+      </c>
+      <c r="I77" t="str">
+        <v>រដូវវស្សា និងរដូវរំហើយ</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>dest-77</v>
+      </c>
+      <c r="C78" t="str">
+        <v>ស្ពានឫស្សីកោះប៉ែន (ស្ពានឫស្សីវែងបំផុតលើលោក)</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Koh Pen Bamboo Bridge &amp; Island Retreat</v>
+      </c>
+      <c r="E78" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F78" t="str">
+        <v>ខេត្តកំពង់ចាម</v>
+      </c>
+      <c r="G78" t="str">
+        <v>ឆ្លងកាត់ទន្លេមេគង្គ ក្រុងកំពង់ចាម ទៅកាន់កោះប៉ែន</v>
+      </c>
+      <c r="H78" t="str">
+        <v>ឆ្លងស្ពាន ១,០០០ រៀល ($1 បរទេស)</v>
+      </c>
+      <c r="I78" t="str">
+        <v>រដូវប្រាំង ខែធ្នូ ដល់ឧសភា</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>dest-78</v>
+      </c>
+      <c r="C79" t="str">
+        <v>ប្រាសាទនគរបាជ័យ</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Wat Nokor Bachey Temple</v>
+      </c>
+      <c r="E79" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F79" t="str">
+        <v>ខេត្តកំពង់ចាម</v>
+      </c>
+      <c r="G79" t="str">
+        <v>ឃុំអំពិល ស្រុកកំពង់សៀម ចម្ងាយ ២ គ.ម ពីក្រុងកំពង់ចាម</v>
+      </c>
+      <c r="H79" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $1)</v>
+      </c>
+      <c r="I79" t="str">
+        <v>ពេញមួយឆ្នាំ ពេលព្រឹក</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>dest-79</v>
+      </c>
+      <c r="C80" t="str">
+        <v>ភ្នំប្រុស ភ្នំស្រី (រមណីយដ្ឋានរឿងព្រេងខ្មែរ)</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Phnom Pros &amp; Phnom Srei Legends</v>
+      </c>
+      <c r="E80" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F80" t="str">
+        <v>ខេត្តកំពង់ចាម</v>
+      </c>
+      <c r="G80" t="str">
+        <v>ឃុំក្រឡា ស្រុកកំពង់សៀម ចម្ងាយ ៧ គ.ម ពីក្រុងកំពង់ចាម</v>
+      </c>
+      <c r="H80" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I80" t="str">
+        <v>ពេលព្រឹក ឬរសៀល</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>dest-80</v>
+      </c>
+      <c r="C81" t="str">
+        <v>វត្តភ្នំហាន់ជ័យ (អារាមកំពូលភ្នំមាត់ទន្លេមេគង្គ)</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Wat Hanchey Hilltop Pagoda</v>
+      </c>
+      <c r="E81" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F81" t="str">
+        <v>ខេត្តកំពង់ចាម</v>
+      </c>
+      <c r="G81" t="str">
+        <v>ស្រុកកំពង់សៀម ចម្ងាយ ២០ គ.ម ខាងជើងក្រុងកំពង់ចាម</v>
+      </c>
+      <c r="H81" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I81" t="str">
+        <v>ពេលព្រឹកព្រលឹម ឬរសៀល ម៉ោង ១៥:៣០ ដល់ ១៨:០០</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>dest-81</v>
+      </c>
+      <c r="C82" t="str">
+        <v>ហ្លួងព្រះស្តេចកន (រាជធានីស្រឡប់ដូនតីពិជ័យព្រៃនគរ)</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Luang Preah Sdech Kon Historical Citadel</v>
+      </c>
+      <c r="E82" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F82" t="str">
+        <v>ខេត្តត្បូងឃ្មុំ</v>
+      </c>
+      <c r="G82" t="str">
+        <v>ស្រុកពញាក្រែក ខេត្តត្បូងឃ្មុំ</v>
+      </c>
+      <c r="H82" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I82" t="str">
+        <v>ពេលព្រឹក</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>dest-82</v>
+      </c>
+      <c r="C83" t="str">
+        <v>ចម្ការកៅស៊ូជប់ (ចម្ការកៅស៊ូប្រវត្តិសាស្ត្រចំណាស់ជាងគេ)</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Chup Historic Rubber Plantation</v>
+      </c>
+      <c r="E83" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F83" t="str">
+        <v>ខេត្តត្បូងឃ្មុំ</v>
+      </c>
+      <c r="G83" t="str">
+        <v>ស្រុកត្បូងឃ្មុំ ខេត្តត្បូងឃ្មុំ</v>
+      </c>
+      <c r="H83" t="str">
+        <v>ឥតគិតថ្លៃទស្សនា</v>
+      </c>
+      <c r="I83" t="str">
+        <v>ពេលព្រឹកព្រលឹម (ពេលកម្មករកំពុងចៀរជ័រកៅស៊ូ)</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>dest-83</v>
+      </c>
+      <c r="C84" t="str">
+        <v>ភូមិកុលាលភាជន៍ឆ្នាំងដីកណ្តាល</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Traditional Clay Pottery Villages</v>
+      </c>
+      <c r="E84" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F84" t="str">
+        <v>ខេត្តកំពង់ឆ្នាំង</v>
+      </c>
+      <c r="G84" t="str">
+        <v>ភូមិអណ្តូងឫស្សី ស្រុករលាប្អៀរ</v>
+      </c>
+      <c r="H84" t="str">
+        <v>ឥតគិតថ្លៃទស្សនា</v>
+      </c>
+      <c r="I84" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៨:០០ ដល់ ១១:៣០</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>dest-84</v>
+      </c>
+      <c r="C85" t="str">
+        <v>ភ្នំនាងកង្រី (ភ្នំរឿងព្រេងនិទានកង្រី-ពុទ្ធិសែន)</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Phnom Neang Kangrei Legend Hill</v>
+      </c>
+      <c r="E85" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F85" t="str">
+        <v>ខេត្តកំពង់ឆ្នាំង</v>
+      </c>
+      <c r="G85" t="str">
+        <v>ស្រុកកំពង់លែង ទល់មុខក្រុងកំពង់ឆ្នាំង</v>
+      </c>
+      <c r="H85" t="str">
+        <v>ឥតគិតថ្លៃ (ទូកចម្លង ៥០០ រៀល)</v>
+      </c>
+      <c r="I85" t="str">
+        <v>ពេលរសៀលទស្សនាពីមាត់ទន្លេ</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>dest-85</v>
+      </c>
+      <c r="C86" t="str">
+        <v>រមណីយដ្ឋានភ្នំសន្ទូច</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Phnom Santouch Recreational Park</v>
+      </c>
+      <c r="E86" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F86" t="str">
+        <v>ខេត្តកំពង់ឆ្នាំង</v>
+      </c>
+      <c r="G86" t="str">
+        <v>ស្រុករលាប្អៀរ ចម្ងាយ ៣ គ.ម ពីក្រុងកំពង់ឆ្នាំង</v>
+      </c>
+      <c r="H86" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I86" t="str">
+        <v>ពេលរសៀលត្រជាក់</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>dest-86</v>
+      </c>
+      <c r="C87" t="str">
+        <v>ភូមិបណ្តែតទឹកឆ្នុកទ្រូ (មាត់បឹងទន្លេសាប)</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Chhnok Tru Floating Village</v>
+      </c>
+      <c r="E87" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F87" t="str">
+        <v>ខេត្តកំពង់ឆ្នាំង</v>
+      </c>
+      <c r="G87" t="str">
+        <v>ស្រុកបរិបូណ៌ ចម្ងាយ ៤០ គ.ម ពីក្រុងកំពង់ឆ្នាំង</v>
+      </c>
+      <c r="H87" t="str">
+        <v>ជិះទូកកាណូត $10-$15</v>
+      </c>
+      <c r="I87" t="str">
+        <v>រដូវវស្សា ខែកញ្ញា ដល់មករា</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>dest-87</v>
+      </c>
+      <c r="C88" t="str">
+        <v>ផ្លូវបុប្ផាលាក់ខ្លួន ភ្នំ១៥០០ (ផ្លូវពស់វែកភ្នំក្រវាញ)</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Phnom 1500 (Cardamom Cloud Pass)</v>
+      </c>
+      <c r="E88" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F88" t="str">
+        <v>ខេត្តពោធិ៍សាត់</v>
+      </c>
+      <c r="G88" t="str">
+        <v>ស្រុកវាលវែង ចម្ងាយ ១២០ គ.ម ពីក្រុងពោធិ៍សាត់</v>
+      </c>
+      <c r="H88" t="str">
+        <v>ឥតគិតថ្លៃធ្វើដំណើរ</v>
+      </c>
+      <c r="I88" t="str">
+        <v>រដូវវស្សា និងរដូវរំហើយ (អ័ព្ទ និងពពកស្អាតបំផុត)</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>dest-88</v>
+      </c>
+      <c r="C89" t="str">
+        <v>ទឹកធ្លាក់ច្រកល្អៀង (ទឹកធ្លាក់កណ្តាលព្រៃស្រោង)</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Chrok La Eang Waterfall</v>
+      </c>
+      <c r="E89" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F89" t="str">
+        <v>ខេត្តពោធិ៍សាត់</v>
+      </c>
+      <c r="G89" t="str">
+        <v>ស្រុកក្រគរ ចម្ងាយ ៧៣ គ.ម ពីក្រុងពោធិ៍សាត់</v>
+      </c>
+      <c r="H89" t="str">
+        <v>សំបុត្រ ៣,០០០ រៀល</v>
+      </c>
+      <c r="I89" t="str">
+        <v>ខែសីហា ដល់ខែមករា (ទឹកហូរខ្លាំងស្អាត)</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>dest-89</v>
+      </c>
+      <c r="C90" t="str">
+        <v>ភូមិបណ្តែតទឹកកំពង់ហ្លួង (ទីក្រុងបណ្តែតទឹកធំបំផុត)</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Kampong Luong Floating Town</v>
+      </c>
+      <c r="E90" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F90" t="str">
+        <v>ខេត្តពោធិ៍សាត់</v>
+      </c>
+      <c r="G90" t="str">
+        <v>ស្រុកក្រគរ មាត់បឹងទន្លេសាប</v>
+      </c>
+      <c r="H90" t="str">
+        <v>ជិះទូកកាណូត $10-$15</v>
+      </c>
+      <c r="I90" t="str">
+        <v>រដូវវស្សា ខែកញ្ញា ដល់មករា</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>dest-90</v>
+      </c>
+      <c r="C91" t="str">
+        <v>រមណីយដ្ឋានបាក់ត្រា</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Bak Tra Forest Park</v>
+      </c>
+      <c r="E91" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F91" t="str">
+        <v>ខេត្តពោធិ៍សាត់</v>
+      </c>
+      <c r="G91" t="str">
+        <v>ស្រុកភ្នំក្រវាញ ចម្ងាយ ១៦ គ.ម ពីក្រុងពោធិ៍សាត់</v>
+      </c>
+      <c r="H91" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I91" t="str">
+        <v>ពេញមួយឆ្នាំ ពិសេសរដូវក្តៅ</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>dest-91</v>
+      </c>
+      <c r="C92" t="str">
+        <v>ជួរភ្នំក្រវាញកណ្តាល និងអូរសោម</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Osom Sanctuary &amp; Cardamom Heartlands</v>
+      </c>
+      <c r="E92" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F92" t="str">
+        <v>ខេត្តពោធិ៍សាត់</v>
+      </c>
+      <c r="G92" t="str">
+        <v>ឃុំអូរសោម ស្រុកវាលវែង</v>
+      </c>
+      <c r="H92" t="str">
+        <v>តាមសហគមន៍អេកូទេសចរណ៍</v>
+      </c>
+      <c r="I92" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែកុម្ភៈ</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>dest-92</v>
+      </c>
+      <c r="C93" t="str">
+        <v>ភ្នំឱរ៉ាល់ (កំពូលភ្នំខ្ពស់បំផុតនៅកម្ពុជា ១,៨១៣ ម៉ែត្រ)</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Phnom Aural (Highest Peak in Cambodia 1,813m)</v>
+      </c>
+      <c r="E93" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F93" t="str">
+        <v>ខេត្តកំពង់ស្ពឺ</v>
+      </c>
+      <c r="G93" t="str">
+        <v>ស្រុកឱរ៉ាល់ ជួរភ្នំក្រវាញ ខេត្តកំពង់ស្ពឺ</v>
+      </c>
+      <c r="H93" t="str">
+        <v>ថ្លៃមគ្គុទ្ទេសក៍សហគមន៍ឡើងភ្នំ</v>
+      </c>
+      <c r="I93" t="str">
+        <v>ខែវិច្ឆិកា ដល់កុម្ភៈ (រដូវរំហើយត្រជាក់)</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
+        <v>dest-93</v>
+      </c>
+      <c r="C94" t="str">
+        <v>រមណីយដ្ឋានអេកូទេសចរណ៍ចំបក់ និងទឹកធ្លាក់</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Chambok Community Eco-Tourism &amp; Waterfall</v>
+      </c>
+      <c r="E94" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F94" t="str">
+        <v>ខេត្តកំពង់ស្ពឺ</v>
+      </c>
+      <c r="G94" t="str">
+        <v>ស្រុកភ្នំស្រួច ជាប់ឧទ្យានជាតិគិរីរម្យ</v>
+      </c>
+      <c r="H94" t="str">
+        <v>សំបុត្រ ៤,០០០ រៀល (បរទេស $3)</v>
+      </c>
+      <c r="I94" t="str">
+        <v>ខែសីហា ដល់ខែកុម្ភៈ</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
+        <v>dest-94</v>
+      </c>
+      <c r="C95" t="str">
+        <v>ឧទ្យានជាតិព្រះសុរាម្រិត-កុសមៈ គិរីរម្យ (ព្រៃស្រល់ធម្មជាតិ)</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Kirirom National Park (Pine Mountain)</v>
+      </c>
+      <c r="E95" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F95" t="str">
+        <v>ខេត្តកំពង់ស្ពឺ</v>
+      </c>
+      <c r="G95" t="str">
+        <v>ស្រុកភ្នំស្រួច ចម្ងាយ ១១៥ គ.ម ពីរាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="H95" t="str">
+        <v>ឥតគិតថ្លៃចូលឧទ្យាន</v>
+      </c>
+      <c r="I95" t="str">
+        <v>ពេញមួយឆ្នាំ ពិសេសចុងសប្តាហ៍</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
+        <v>dest-95</v>
+      </c>
+      <c r="C96" t="str">
+        <v>ទឹកធ្លាក់ជ្រាវ</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Chreav Cascading Waterfalls</v>
+      </c>
+      <c r="E96" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F96" t="str">
+        <v>ខេត្តកំពង់ស្ពឺ</v>
+      </c>
+      <c r="G96" t="str">
+        <v>ស្រុកឱរ៉ាល់ ខេត្តកំពង់ស្ពឺ</v>
+      </c>
+      <c r="H96" t="str">
+        <v>សំបុត្រ ២,០០០ រៀល</v>
+      </c>
+      <c r="I96" t="str">
+        <v>រដូវវស្សា និងរដូវរំហើយ ខែកក្កដា ដល់មករា</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
+        <v>dest-96</v>
+      </c>
+      <c r="C97" t="str">
+        <v>ភ្នំស្រួច និងទំនប់តេជោធម្មជាតិ</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Phnom Sruoch &amp; Techo Dam Scenic Area</v>
+      </c>
+      <c r="E97" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F97" t="str">
+        <v>ខេត្តកំពង់ស្ពឺ</v>
+      </c>
+      <c r="G97" t="str">
+        <v>ស្រុកភ្នំស្រួច ខេត្តកំពង់ស្ពឺ</v>
+      </c>
+      <c r="H97" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I97" t="str">
+        <v>ពេលរសៀល ម៉ោង ១៦:០០ ដល់ ១៨:៣០</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="str">
+        <v>dest-97</v>
+      </c>
+      <c r="C98" t="str">
+        <v>ភ្នំឧដុង្គ (រាជធានីចាស់ និងចេតិយបុរាណ)</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Oudong Mountain &amp; Royal Necropolis</v>
+      </c>
+      <c r="E98" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F98" t="str">
+        <v>ខេត្តកណ្តាល</v>
+      </c>
+      <c r="G98" t="str">
+        <v>ស្រុកពញាឮ ចម្ងាយ ៤០ គ.ម ពីរាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="H98" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $1)</v>
+      </c>
+      <c r="I98" t="str">
+        <v>ពេលព្រឹកព្រលឹម ឬរសៀលត្រជាក់</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="str">
+        <v>dest-98</v>
+      </c>
+      <c r="C99" t="str">
+        <v>កោះដាច់ (ភូមិតម្បាញសូត្រខ្មែរប្រពៃណី)</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Koh Dach Silk Weaving Island</v>
+      </c>
+      <c r="E99" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F99" t="str">
+        <v>ខេត្តកណ្តាល</v>
+      </c>
+      <c r="G99" t="str">
+        <v>កោះដណ្តែតកណ្តាលទន្លេមេគង្គ ខណ្ឌជ្រោយចង្វារ/ខេត្តកណ្តាល</v>
+      </c>
+      <c r="H99" t="str">
+        <v>ទូកចម្លង ៥០០ រៀល</v>
+      </c>
+      <c r="I99" t="str">
+        <v>ពេញមួយឆ្នាំ ពិសេសចុងសប្តាហ៍</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="str">
+        <v>dest-99</v>
+      </c>
+      <c r="C100" t="str">
+        <v>ឧទ្យានសួនសត្វ និងមជ្ឈមណ្ឌលសង្គ្រោះសត្វព្រៃភ្នំតាម៉ៅ</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Phnom Tamao Wildlife Rescue Center</v>
+      </c>
+      <c r="E100" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F100" t="str">
+        <v>ខេត្តតាកែវ</v>
+      </c>
+      <c r="G100" t="str">
+        <v>ស្រុកបាទី ចម្ងាយ ៤០ គ.ម ពីរាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="H100" t="str">
+        <v>សំបុត្រ ៤,០០០ រៀល (បរទេស $5)</v>
+      </c>
+      <c r="I100" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៨:០០ ដល់ ១៣:០០</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>dest-100</v>
+      </c>
+      <c r="C101" t="str">
+        <v>ប្រាសាទភ្នំជីសូរ (ប្រាសាទសតវត្សរ៍ទី១១ លើកំពូលភ្នំ)</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Phnom Chisor Ancient Temple</v>
+      </c>
+      <c r="E101" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F101" t="str">
+        <v>ខេត្តតាកែវ</v>
+      </c>
+      <c r="G101" t="str">
+        <v>ស្រុកសំរោង ចម្ងាយ ៦២ គ.ម ពីរាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="H101" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $2)</v>
+      </c>
+      <c r="I101" t="str">
+        <v>ពេលព្រឹកព្រលឹម</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>dest-101</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ប្រាសាទតាព្រហ្មទន្លេបាទី និងបឹងទន្លេបាទី</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Tonle Bati &amp; Ta Prohm of Bati</v>
+      </c>
+      <c r="E102" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F102" t="str">
+        <v>ខេត្តតាកែវ</v>
+      </c>
+      <c r="G102" t="str">
+        <v>ស្រុកបាទី ចម្ងាយ ៣៥ គ.ម ពីរាជធានីភ្នំពេញ</v>
+      </c>
+      <c r="H102" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $3)</v>
+      </c>
+      <c r="I102" t="str">
+        <v>ពេញមួយឆ្នាំ ពិសេសចុងសប្តាហ៍</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>dest-102</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ភ្នំដា និងប្រាសាទអាស្រមមហាឫសី (អរិយធម៌នគរភ្នំ)</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Phnom Da &amp; Asram Maha Rosei (Funan Cradle)</v>
+      </c>
+      <c r="E103" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F103" t="str">
+        <v>ខេត្តតាកែវ</v>
+      </c>
+      <c r="G103" t="str">
+        <v>ស្រុកអង្គរបុរី ចម្ងាយ ២៤ គ.ម ពីក្រុងដូនកែវ</v>
+      </c>
+      <c r="H103" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (ជិះទូកកាណូត $10-$15)</v>
+      </c>
+      <c r="I103" t="str">
+        <v>រដូវទឹកឡើង ខែកញ្ញា ដល់មករា</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>dest-103</v>
+      </c>
+      <c r="C104" t="str">
+        <v>បឹងស្អាងព្រែកតូច និងចម្ការផ្កាឈូក</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Saang Lotus Lake &amp; Agro-Eco Trail</v>
+      </c>
+      <c r="E104" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F104" t="str">
+        <v>ខេត្តកណ្តាល</v>
+      </c>
+      <c r="G104" t="str">
+        <v>ស្រុកស្អាង ខេត្តកណ្តាល</v>
+      </c>
+      <c r="H104" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I104" t="str">
+        <v>ពេលព្រឹកព្រលឹម ម៉ោង ០៦:៣០ ដល់ ០៩:០០</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>dest-104</v>
+      </c>
+      <c r="C105" t="str">
+        <v>អន្លង់ផ្សោតកាំពី ទន្លេមេគង្គ (ជម្រកសត្វផ្សោតកម្រ)</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Kampi Irrawaddy Dolphin Sanctuary</v>
+      </c>
+      <c r="E105" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F105" t="str">
+        <v>ខេត្តក្រចេះ</v>
+      </c>
+      <c r="G105" t="str">
+        <v>ឃុំសំបុក ស្រុកចិត្របុរី ចម្ងាយ ១៥ គ.ម ពីក្រុងក្រចេះ</v>
+      </c>
+      <c r="H105" t="str">
+        <v>ទូកមើលផ្សោត $5-$9 ក្នុងម្នាក់</v>
+      </c>
+      <c r="I105" t="str">
+        <v>រដូវប្រាំង ខែមករា ដល់ឧសភា (ទឹកថ្លាផ្សោតជួបជុំគ្នា)</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>dest-105</v>
+      </c>
+      <c r="C106" t="str">
+        <v>កោះទ្រង់ (កោះអេកូទេសចរណ៍ និងចម្ការក្រូចថ្លុង)</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Koh Trong Island Eco Resort &amp; Pomelo Orchards</v>
+      </c>
+      <c r="E106" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F106" t="str">
+        <v>ខេត្តក្រចេះ</v>
+      </c>
+      <c r="G106" t="str">
+        <v>កោះកណ្តាលទន្លេមេគង្គ ទល់មុខក្រុងក្រចេះ</v>
+      </c>
+      <c r="H106" t="str">
+        <v>ទូកចម្លង ១,០០០ រៀល (ជួលកង់ $1-$2)</v>
+      </c>
+      <c r="I106" t="str">
+        <v>ពេញមួយឆ្នាំ ពិសេសរដូវផ្លែក្រូចថ្លុង</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>dest-106</v>
+      </c>
+      <c r="C107" t="str">
+        <v>វត្តសសរ១០០ សំបូរ (អារាមប្រវត្តិសាស្ត្រសតវត្សរ៍ទី១៩)</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Wat Sorsor Mouy Roy (100-Column Pagoda)</v>
+      </c>
+      <c r="E107" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F107" t="str">
+        <v>ខេត្តក្រចេះ</v>
+      </c>
+      <c r="G107" t="str">
+        <v>ស្រុកសំបូរ ចម្ងាយ ៣៦ គ.ម ពីក្រុងក្រចេះ</v>
+      </c>
+      <c r="H107" t="str">
+        <v>ឥតគិតថ្លៃ (មជ្ឈមណ្ឌលអណ្តើក $2)</v>
+      </c>
+      <c r="I107" t="str">
+        <v>ពេញមួយឆ្នាំ</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>dest-107</v>
+      </c>
+      <c r="C108" t="str">
+        <v>ភ្នំសំបុក (វត្តអារាមលើកំពូលភ្នំព្រៃស្ងប់ស្ងាត់)</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Phnom Sambok Spiritual Hill</v>
+      </c>
+      <c r="E108" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F108" t="str">
+        <v>ខេត្តក្រចេះ</v>
+      </c>
+      <c r="G108" t="str">
+        <v>ឃុំសំបុក ស្រុកចិត្របុរី ចម្ងាយ ១០ គ.ម ពីក្រុងក្រចេះ</v>
+      </c>
+      <c r="H108" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I108" t="str">
+        <v>ពេលព្រឹក ម៉ោង ០៧:០០ ដល់ ១០:០០</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>dest-108</v>
+      </c>
+      <c r="C109" t="str">
+        <v>តំបន់ដីសើមរ៉ាមសារស្ទឹងត្រែង</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Stung Treng Ramsar Wetlands</v>
+      </c>
+      <c r="E109" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F109" t="str">
+        <v>ខេត្តស្ទឹងត្រែង</v>
+      </c>
+      <c r="G109" t="str">
+        <v>តាមដងទន្លេមេគង្គលើ ក្រុងស្ទឹងត្រែង ដល់ព្រំដែនឡាវ</v>
+      </c>
+      <c r="H109" t="str">
+        <v>ទូកទេសចរណ៍ $15-$25</v>
+      </c>
+      <c r="I109" t="str">
+        <v>រដូវប្រាំង ខែមករា ដល់ឧសភា (ឃើញឫសឈើក្នុងទឹក)</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>dest-109</v>
+      </c>
+      <c r="C110" t="str">
+        <v>ព្រះរំកិល និងល្បាក់ខោនស្ទឹងត្រែង</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Preah Rumkel Mekong Canyon &amp; Waterfalls</v>
+      </c>
+      <c r="E110" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F110" t="str">
+        <v>ខេត្តស្ទឹងត្រែង</v>
+      </c>
+      <c r="G110" t="str">
+        <v>ឃុំព្រះរំកិល ស្រុកថាឡាបរិវ៉ាត់</v>
+      </c>
+      <c r="H110" t="str">
+        <v>តាមសេវាទូកសហគមន៍</v>
+      </c>
+      <c r="I110" t="str">
+        <v>ខែវិច្ឆិកា ដល់ខែមេសា</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>dest-110</v>
+      </c>
+      <c r="C111" t="str">
+        <v>ប្រាសាទបន្ទាយឆ្មារ (មហាប្រាសាទលោកេសូរមុខ៨)</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Banteay Chhmar Great Temple Complex</v>
+      </c>
+      <c r="E111" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F111" t="str">
+        <v>ខេត្តបន្ទាយមានជ័យ</v>
+      </c>
+      <c r="G111" t="str">
+        <v>ស្រុកថ្មពួក ចម្ងាយ ៦០ គ.ម ពីក្រុងសិរីសោភ័ណ</v>
+      </c>
+      <c r="H111" t="str">
+        <v>ខ្មែរឥតគិតថ្លៃ (បរទេស $5)</v>
+      </c>
+      <c r="I111" t="str">
+        <v>ពេញមួយឆ្នាំ ពេលព្រឹក</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>dest-111</v>
+      </c>
+      <c r="C112" t="str">
+        <v>អាងត្រពាំងថ្ម (ជម្រកសត្វក្រៀលកម្រ)</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Ang Trapaing Thmor Sarus Crane Reserve</v>
+      </c>
+      <c r="E112" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F112" t="str">
+        <v>ខេត្តបន្ទាយមានជ័យ</v>
+      </c>
+      <c r="G112" t="str">
+        <v>ស្រុកភ្នំស្រុក ខេត្តបន្ទាយមានជ័យ</v>
+      </c>
+      <c r="H112" t="str">
+        <v>ឥតគិតថ្លៃ (ទូកមើលសត្វស្លាប $15)</v>
+      </c>
+      <c r="I112" t="str">
+        <v>ខែមករា ដល់ខែមេសា (រដូវសត្វក្រៀលជួបជុំគ្នា)</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>dest-112</v>
+      </c>
+      <c r="C113" t="str">
+        <v>ប្រាសាទតាមាន់ធំ (ប្រាសាទថ្មលើខ្នងភ្នំដងរែក)</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Prasat Ta Moan Thom</v>
+      </c>
+      <c r="E113" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F113" t="str">
+        <v>ខេត្តឧត្តរមានជ័យ</v>
+      </c>
+      <c r="G113" t="str">
+        <v>ជួរភ្នំដងរែក ស្រុកបន្ទាយអំពិល</v>
+      </c>
+      <c r="H113" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I113" t="str">
+        <v>រដូវប្រាំង ខែវិច្ឆិកា ដល់ឧសភា</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>dest-113</v>
+      </c>
+      <c r="C114" t="str">
+        <v>ភ្នំដងរែក និងរមណីយដ្ឋានអន្លង់វែង</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Dangrek Mountains &amp; Anlong Veng Historical Trail</v>
+      </c>
+      <c r="E114" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F114" t="str">
+        <v>ខេត្តឧត្តរមានជ័យ</v>
+      </c>
+      <c r="G114" t="str">
+        <v>ស្រុកអន្លង់វែង ជួរភ្នំដងរែក</v>
+      </c>
+      <c r="H114" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I114" t="str">
+        <v>ពេលរសៀលទស្សនាថ្ងៃលិចលើជ្រោះ</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>dest-114</v>
+      </c>
+      <c r="C115" t="str">
+        <v>ភ្នំយ៉ាត និងវត្តកូឡាប៉ៃលិន (រមណីយដ្ឋានត្បូងពេជ្រ)</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Phnom Yat &amp; Kola Pagoda Pailin</v>
+      </c>
+      <c r="E115" t="str">
+        <v>ប្រាសាទបុរាណ / បេតិកភណ្ឌ</v>
+      </c>
+      <c r="F115" t="str">
+        <v>ខេត្តប៉ៃលិន</v>
+      </c>
+      <c r="G115" t="str">
+        <v>ក្រុងប៉ៃលិន ខេត្តប៉ៃលិន</v>
+      </c>
+      <c r="H115" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I115" t="str">
+        <v>ពេលរសៀល ម៉ោង ១៦:០០ ដល់ ១៨:០០</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>dest-115</v>
+      </c>
+      <c r="C116" t="str">
+        <v>ទឹកធ្លាក់អូរតាវ៉ៅ (ទឹកធ្លាក់កូហ្គោ)</v>
+      </c>
+      <c r="D116" t="str">
+        <v>O’Tavao Waterfall (Goh Goh Falls)</v>
+      </c>
+      <c r="E116" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F116" t="str">
+        <v>ខេត្តប៉ៃលិន</v>
+      </c>
+      <c r="G116" t="str">
+        <v>សង្កាត់អូរតាវ៉ៅ ក្រុងប៉ៃលិន</v>
+      </c>
+      <c r="H116" t="str">
+        <v>សំបុត្រ ២,០០០ រៀល</v>
+      </c>
+      <c r="I116" t="str">
+        <v>រដូវវស្សា និងដើមរដូវប្រាំង ខែសីហា ដល់មករា</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>dest-116</v>
+      </c>
+      <c r="C117" t="str">
+        <v>ដែនជម្រកសត្វស្លាបទួលពាន់តាឡី (បឹងរំដួល)</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Tuol Poan Talei Stork Sanctuary (Boeung Romduol)</v>
+      </c>
+      <c r="E117" t="str">
+        <v>ធម្មជាតិ &amp; ទឹកធ្លាក់</v>
+      </c>
+      <c r="F117" t="str">
+        <v>ខេត្តស្វាយរៀង</v>
+      </c>
+      <c r="G117" t="str">
+        <v>ស្រុករំដួល ខេត្តស្វាយរៀង</v>
+      </c>
+      <c r="H117" t="str">
+        <v>ឥតគិតថ្លៃ (ជួលទូក $5-$8)</v>
+      </c>
+      <c r="I117" t="str">
+        <v>ខែតុលា ដល់ខែកុម្ភៈ (រដូវសត្វស្លាបជួបជុំគ្នាច្រើន)</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>dest-117</v>
+      </c>
+      <c r="C118" t="str">
+        <v>រមណីយដ្ឋានប្រវត្តិសាស្ត្រព្រៃបាសាក់</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Prey Basak Historic &amp; Cultural Resort</v>
+      </c>
+      <c r="E118" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F118" t="str">
+        <v>ខេត្តស្វាយរៀង</v>
+      </c>
+      <c r="G118" t="str">
+        <v>ស្រុកស្វាយជ្រំ ចម្ងាយ ៨.៥ គ.ម ពីក្រុងស្វាយរៀង</v>
+      </c>
+      <c r="H118" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I118" t="str">
+        <v>ពេញមួយឆ្នាំ ពិសេសចុងសប្តាហ៍</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>dest-118</v>
+      </c>
+      <c r="C119" t="str">
+        <v>ស្ពានត្សឹបាសា (ស្ពានអ្នកលឿង - ស្ពានខ្សែកាបវែងបំផុត)</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Tsubasa Bridge (Neak Loeung Cable-Stayed Bridge)</v>
+      </c>
+      <c r="E119" t="str">
+        <v>រមណីយដ្ឋាន &amp; វប្បធម៌</v>
+      </c>
+      <c r="F119" t="str">
+        <v>ខេត្តព្រៃវែង</v>
+      </c>
+      <c r="G119" t="str">
+        <v>ឆ្លងកាត់ទន្លេមេគង្គ ស្រុកពាមរក៍ ព្រំប្រទល់ខេត្តកណ្តាល</v>
+      </c>
+      <c r="H119" t="str">
+        <v>ឥតគិតថ្លៃធ្វើដំណើរឆ្លងកាត់</v>
+      </c>
+      <c r="I119" t="str">
+        <v>ពេលរសៀល និងពេលរាត្រី (ភ្លើងពណ៌ស្រស់ស្អាត)</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>dest-119</v>
+      </c>
+      <c r="C120" t="str">
+        <v>រមណីយដ្ឋានប្រវត្តិសាស្ត្របាភ្នំ (ភ្នំឈើកាច់)</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Ba Phnom Historical Mountain</v>
+      </c>
+      <c r="E120" t="str">
+        <v>ភ្នំ &amp; ឧទ្យានជាតិ</v>
+      </c>
+      <c r="F120" t="str">
+        <v>ខេត្តព្រៃវែង</v>
+      </c>
+      <c r="G120" t="str">
+        <v>ស្រុកបាភ្នំ ចម្ងាយ ៤៥ គ.ម ពីក្រុងព្រៃវែង</v>
+      </c>
+      <c r="H120" t="str">
+        <v>ឥតគិតថ្លៃ</v>
+      </c>
+      <c r="I120" t="str">
+        <v>ពេលព្រឹកព្រលឹម ឬរសៀល</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I120"/>
   </ignoredErrors>
 </worksheet>
 </file>